--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-15.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-15.xlsx
@@ -869,7 +869,7 @@
         <v>3.2</v>
       </c>
       <c r="J2" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="K2" t="n">
         <v>3.65</v>
@@ -887,10 +887,10 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-13 01:47:23</t>
+          <t>2026-07-13 03:55:13</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-13 01:47:23</t>
+          <t>2026-07-13 03:55:13</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.44</v>
+        <v>2.32</v>
       </c>
       <c r="G4" t="n">
-        <v>2.74</v>
+        <v>2.58</v>
       </c>
       <c r="H4" t="n">
-        <v>2.82</v>
+        <v>3.15</v>
       </c>
       <c r="I4" t="n">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="J4" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="K4" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1395,10 +1395,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.89</v>
+        <v>2.04</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-13 01:47:23</t>
+          <t>2026-07-13 03:55:13</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-15.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-15.xlsx
@@ -860,19 +860,19 @@
         <v>2.56</v>
       </c>
       <c r="G2" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="H2" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="I2" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="J2" t="n">
         <v>3.1</v>
       </c>
       <c r="K2" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-13 03:55:13</t>
+          <t>2026-07-13 06:03:21</t>
         </is>
       </c>
     </row>
@@ -1117,16 +1117,16 @@
         <v>2.72</v>
       </c>
       <c r="H3" t="n">
-        <v>2.98</v>
+        <v>3.25</v>
       </c>
       <c r="I3" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="J3" t="n">
         <v>2.94</v>
       </c>
       <c r="K3" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1141,10 +1141,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-13 03:55:13</t>
+          <t>2026-07-13 06:03:21</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-13 03:55:13</t>
+          <t>2026-07-13 06:03:21</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-15.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-15.xlsx
@@ -857,22 +857,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="G2" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="H2" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="I2" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="J2" t="n">
         <v>3.1</v>
       </c>
       <c r="K2" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -887,10 +887,10 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-13 06:03:21</t>
+          <t>2026-07-13 08:12:39</t>
         </is>
       </c>
     </row>
@@ -1114,10 +1114,10 @@
         <v>2.5</v>
       </c>
       <c r="G3" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="H3" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="I3" t="n">
         <v>3.85</v>
@@ -1141,10 +1141,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-13 06:03:21</t>
+          <t>2026-07-13 08:12:39</t>
         </is>
       </c>
     </row>
@@ -1365,16 +1365,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="G4" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="H4" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="I4" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="J4" t="n">
         <v>3.15</v>
@@ -1395,10 +1395,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-13 06:03:21</t>
+          <t>2026-07-13 08:12:39</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-15.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-15.xlsx
@@ -869,7 +869,7 @@
         <v>3.3</v>
       </c>
       <c r="J2" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K2" t="n">
         <v>3.65</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-13 08:12:39</t>
+          <t>2026-07-13 10:21:51</t>
         </is>
       </c>
     </row>
@@ -1117,16 +1117,16 @@
         <v>2.68</v>
       </c>
       <c r="H3" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="I3" t="n">
         <v>3.85</v>
       </c>
       <c r="J3" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="K3" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1141,10 +1141,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-13 08:12:39</t>
+          <t>2026-07-13 10:21:51</t>
         </is>
       </c>
     </row>
@@ -1365,16 +1365,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="G4" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="H4" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="I4" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="J4" t="n">
         <v>3.15</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-13 08:12:39</t>
+          <t>2026-07-13 10:21:51</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-15.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-15.xlsx
@@ -857,19 +857,19 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.52</v>
+        <v>2.3</v>
       </c>
       <c r="G2" t="n">
-        <v>2.9</v>
+        <v>2.62</v>
       </c>
       <c r="H2" t="n">
-        <v>2.82</v>
+        <v>3.15</v>
       </c>
       <c r="I2" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="J2" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K2" t="n">
         <v>3.65</v>
@@ -890,7 +890,7 @@
         <v>1.72</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-13 10:21:51</t>
+          <t>2026-07-13 12:31:07</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
         <v>2.5</v>
       </c>
       <c r="G3" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="H3" t="n">
         <v>3.25</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-13 10:21:51</t>
+          <t>2026-07-13 12:31:07</t>
         </is>
       </c>
     </row>
@@ -1365,19 +1365,19 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="G4" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="H4" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="J4" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K4" t="n">
         <v>3.7</v>
@@ -1395,7 +1395,7 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="Q4" t="n">
         <v>2.06</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-13 10:21:51</t>
+          <t>2026-07-13 12:31:07</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-15.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-15.xlsx
@@ -857,16 +857,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="G2" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="H2" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="I2" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="J2" t="n">
         <v>3.1</v>
@@ -875,212 +875,212 @@
         <v>3.65</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="P2" t="n">
         <v>1.72</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BH2" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BI2" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BN2" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BO2" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BP2" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BR2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BT2" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BU2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BV2" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BW2" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BX2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-13 12:31:07</t>
+          <t>2026-07-13 14:40:34</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
         <v>2.9</v>
       </c>
       <c r="K3" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1141,10 +1141,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-13 12:31:07</t>
+          <t>2026-07-13 14:40:34</t>
         </is>
       </c>
     </row>
@@ -1368,10 +1368,10 @@
         <v>2.4</v>
       </c>
       <c r="G4" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="I4" t="n">
         <v>3.45</v>
@@ -1398,7 +1398,7 @@
         <v>1.75</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-13 12:31:07</t>
+          <t>2026-07-13 14:40:34</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-15.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-15.xlsx
@@ -974,7 +974,7 @@
         <v>19.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>42</v>
+        <v>7.4</v>
       </c>
       <c r="AT2" t="n">
         <v>7.8</v>
@@ -1001,7 +1001,7 @@
         <v>36</v>
       </c>
       <c r="BB2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BC2" t="n">
         <v>18.5</v>
@@ -1013,7 +1013,7 @@
         <v>7.8</v>
       </c>
       <c r="BF2" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BG2" t="n">
         <v>7.2</v>
@@ -1034,7 +1034,7 @@
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>21</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN2" t="n">
         <v>5.4</v>
@@ -1046,41 +1046,41 @@
         <v>20</v>
       </c>
       <c r="BQ2" t="n">
-        <v>14.5</v>
+        <v>6.8</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>21</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT2" t="n">
         <v>6.8</v>
       </c>
       <c r="BU2" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BV2" t="n">
         <v>40</v>
       </c>
       <c r="BW2" t="n">
-        <v>22</v>
+        <v>7.8</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>21</v>
+        <v>8.6</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-13 14:40:34</t>
+          <t>2026-07-13 16:49:34</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-13 14:40:34</t>
+          <t>2026-07-13 16:49:34</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
         <v>2.4</v>
       </c>
       <c r="G4" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="H4" t="n">
         <v>2.94</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-13 14:40:34</t>
+          <t>2026-07-13 16:49:34</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-15.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-15.xlsx
@@ -857,16 +857,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="G2" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="H2" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="I2" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="J2" t="n">
         <v>3.1</v>
@@ -881,22 +881,22 @@
         <v>1.08</v>
       </c>
       <c r="N2" t="n">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="O2" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P2" t="n">
         <v>1.72</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="R2" t="n">
         <v>1.27</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="T2" t="n">
         <v>1.83</v>
@@ -908,7 +908,7 @@
         <v>1.4</v>
       </c>
       <c r="W2" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="X2" t="n">
         <v>12.5</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-13 16:49:34</t>
+          <t>2026-07-13 18:58:03</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-13 16:49:34</t>
+          <t>2026-07-13 18:58:03</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-13 16:49:34</t>
+          <t>2026-07-13 18:58:03</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-15.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-15.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,406 +413,406 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB4"/>
+  <dimension ref="A1:CB7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>League</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Time</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Home</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Away</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Odd_H_Back</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Odd_H_Lay</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Odd_A_Back</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Odd_A_Lay</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Odd_D_Back</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Odd_D_Lay</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Odd_Over05_HT_Back</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Odd_Over05_FT_Back</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Odd_Under15_FT_Back</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Odd_Over15_FT_Back</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Odd_Under25_FT_Back</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Odd_Over25_FT_Back</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Odd_Under35_FT_Back</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Odd_Over35_FT_Back</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Odd_BTTS_Yes_Back</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Odd_BTTS_No_Back</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Double_Chance_Home_or_Draw_Back</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Double_Chance_Draw_or_Away_Back</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Odd_CS_0x0_Lay</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Odd_CS_0x1_Lay</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Odd_CS_0x2_Lay</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Odd_CS_0x3_Lay</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Odd_CS_1x0_Lay</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Odd_CS_1x1_Lay</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Odd_CS_1x2_Lay</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Odd_CS_1x3_Lay</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Odd_CS_2x0_Lay</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Odd_CS_2x1_Lay</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Odd_CS_2x2_Lay</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>Odd_CS_2x3_Lay</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Odd_CS_3x0_Lay</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>Odd_CS_3x1_Lay</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>Odd_CS_3x2_Lay</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>Odd_CS_3x3_Lay</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>Odd_CS_Goleada_H_Lay</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>Odd_CS_Goleada_A_Lay</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>Odd_CS_0x0_Back</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>Odd_CS_0x1_Back</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>Odd_CS_0x2_Back</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>Odd_CS_0x3_Back</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>Odd_CS_1x0_Back</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>Odd_CS_1x1_Back</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>Odd_CS_1x2_Back</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>Odd_CS_1x3_Back</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>Odd_CS_2x0_Back</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>Odd_CS_2x1_Back</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>Odd_CS_2x2_Back</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>Odd_CS_2x3_Back</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>Odd_CS_3x0_Back</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>Odd_CS_3x1_Back</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>Odd_CS_3x2_Back</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>Odd_CS_3x3_Back</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>Odd_CS_Goleada_H_Back</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>Odd_CS_Goleada_A_Back</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>Odd_HTS_0x0_Lay</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>Odd_HTS_0x0_Back</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>Odd_HTS_1x1_Lay</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>Odd_HTS_1x1_Back</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>Odd_HTS_2x2_Lay</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>Odd_HTS_2x2_Back</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BN1" t="inlineStr">
         <is>
           <t>Odd_HTS_1x0_Lay</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BO1" t="inlineStr">
         <is>
           <t>Odd_HTS_1x0_Back</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BP1" t="inlineStr">
         <is>
           <t>Odd_HTS_2x0_Lay</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BQ1" t="inlineStr">
         <is>
           <t>Odd_HTS_2x0_Back</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BR1" t="inlineStr">
         <is>
           <t>Odd_HTS_2x1_Lay</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BS1" t="inlineStr">
         <is>
           <t>Odd_HTS_2x1_Back</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BT1" t="inlineStr">
         <is>
           <t>Odd_HTS_0x1_Lay</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BU1" t="inlineStr">
         <is>
           <t>Odd_HTS_0x1_Back</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BV1" t="inlineStr">
         <is>
           <t>Odd_HTS_0x2_Lay</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="BW1" t="inlineStr">
         <is>
           <t>Odd_HTS_0x2_Back</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BX1" t="inlineStr">
         <is>
           <t>Odd_HTS_1x2_Lay</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="BY1" t="inlineStr">
         <is>
           <t>Odd_HTS_1x2_Back</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="BZ1" t="inlineStr">
         <is>
           <t>Odd_HTS_Outros_Lay</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CA1" t="inlineStr">
         <is>
           <t>Odd_HTS_Outros_Back</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CB1" t="inlineStr">
         <is>
           <t>SnapshotTS</t>
         </is>
@@ -857,230 +845,230 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.34</v>
+        <v>2.66</v>
       </c>
       <c r="G2" t="n">
-        <v>2.6</v>
+        <v>2.98</v>
       </c>
       <c r="H2" t="n">
-        <v>3.15</v>
+        <v>2.94</v>
       </c>
       <c r="I2" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="J2" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="K2" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="L2" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="M2" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N2" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="O2" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="P2" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.12</v>
+        <v>2.24</v>
       </c>
       <c r="R2" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="S2" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="T2" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="U2" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="V2" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="W2" t="n">
-        <v>1.63</v>
+        <v>1.51</v>
       </c>
       <c r="X2" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="AA2" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AB2" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC2" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AF2" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI2" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AJ2" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AK2" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="AL2" t="n">
         <v>60</v>
       </c>
       <c r="AM2" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AN2" t="n">
+        <v>44</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>50</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>9</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>32</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>38</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>36</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>27</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>32</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BP2" t="n">
         <v>30</v>
       </c>
-      <c r="AO2" t="n">
-        <v>60</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>28</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA2" t="n">
+      <c r="BQ2" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>8</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BV2" t="n">
         <v>36</v>
       </c>
-      <c r="BB2" t="n">
-        <v>27</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>30</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>21</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>20</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>40</v>
-      </c>
       <c r="BW2" t="n">
-        <v>7.8</v>
+        <v>1.71</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>8.6</v>
+        <v>1.74</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="CA2" t="n">
-        <v>8</v>
+        <v>1.73</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-13 18:58:03</t>
+          <t>2026-07-13 22:40:56</t>
         </is>
       </c>
     </row>
@@ -1114,227 +1102,227 @@
         <v>2.5</v>
       </c>
       <c r="G3" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="H3" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="I3" t="n">
         <v>3.85</v>
       </c>
       <c r="J3" t="n">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="K3" t="n">
         <v>3.3</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="P3" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.48</v>
+        <v>2.72</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BH3" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="BI3" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BK3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BL3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BN3" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BO3" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BP3" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BT3" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BU3" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BV3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BX3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-13 18:58:03</t>
+          <t>2026-07-13 22:40:56</t>
         </is>
       </c>
     </row>
@@ -1365,230 +1353,992 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="G4" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="H4" t="n">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="I4" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J4" t="n">
         <v>3.2</v>
       </c>
       <c r="K4" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="P4" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BH4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI4" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BK4" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BL4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BN4" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BO4" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BP4" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BR4" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="BS4" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="BT4" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU4" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BV4" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BW4" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="BX4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="CA4" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-13 18:58:03</t>
+          <t>2026-07-13 22:40:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>US United Soccer League</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Miami FC</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Indy Eleven</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="X5" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>38</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>50</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>28</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>22</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>16</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>20</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>7</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>23</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>17</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>34</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>24</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>14</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>32</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>22</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>26</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
+          <t>2026-07-13 22:40:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>US United Soccer League</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Lexington SC</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>New Mexico United</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="H6" t="n">
+        <v>5</v>
+      </c>
+      <c r="I6" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N6" t="n">
+        <v>4</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="W6" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="X6" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>160</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>90</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>13</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>55</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>2026-07-13 22:40:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>US United Soccer League</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Sporting Club Jacksonvil</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Pittsburgh Riverhounds</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G7" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="K7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N7" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="V7" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X7" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>23</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>23</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>50</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>26</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>160</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>90</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>90</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>100</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>13</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>60</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>2026-07-13 22:40:56</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-15.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-15.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,406 +425,406 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB7"/>
+  <dimension ref="A1:CB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>League</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Time</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Home</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Away</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Odd_H_Back</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Odd_H_Lay</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Odd_A_Back</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Odd_A_Lay</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Odd_D_Back</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Odd_D_Lay</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Odd_Over05_HT_Back</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Odd_Over05_FT_Back</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Odd_Under15_FT_Back</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Odd_Over15_FT_Back</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Odd_Under25_FT_Back</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Odd_Over25_FT_Back</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Odd_Under35_FT_Back</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Odd_Over35_FT_Back</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Odd_BTTS_Yes_Back</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Odd_BTTS_No_Back</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Double_Chance_Home_or_Draw_Back</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Double_Chance_Draw_or_Away_Back</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Odd_CS_0x0_Lay</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Odd_CS_0x1_Lay</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Odd_CS_0x2_Lay</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Odd_CS_0x3_Lay</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Odd_CS_1x0_Lay</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Odd_CS_1x1_Lay</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Odd_CS_1x2_Lay</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Odd_CS_1x3_Lay</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Odd_CS_2x0_Lay</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Odd_CS_2x1_Lay</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Odd_CS_2x2_Lay</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>Odd_CS_2x3_Lay</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>Odd_CS_3x0_Lay</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>Odd_CS_3x1_Lay</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>Odd_CS_3x2_Lay</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>Odd_CS_3x3_Lay</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>Odd_CS_Goleada_H_Lay</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>Odd_CS_Goleada_A_Lay</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>Odd_CS_0x0_Back</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>Odd_CS_0x1_Back</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>Odd_CS_0x2_Back</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>Odd_CS_0x3_Back</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>Odd_CS_1x0_Back</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>Odd_CS_1x1_Back</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>Odd_CS_1x2_Back</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>Odd_CS_1x3_Back</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>Odd_CS_2x0_Back</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>Odd_CS_2x1_Back</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>Odd_CS_2x2_Back</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>Odd_CS_2x3_Back</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>Odd_CS_3x0_Back</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>Odd_CS_3x1_Back</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>Odd_CS_3x2_Back</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>Odd_CS_3x3_Back</t>
         </is>
       </c>
-      <c r="BF1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>Odd_CS_Goleada_H_Back</t>
         </is>
       </c>
-      <c r="BG1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>Odd_CS_Goleada_A_Back</t>
         </is>
       </c>
-      <c r="BH1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>Odd_HTS_0x0_Lay</t>
         </is>
       </c>
-      <c r="BI1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>Odd_HTS_0x0_Back</t>
         </is>
       </c>
-      <c r="BJ1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>Odd_HTS_1x1_Lay</t>
         </is>
       </c>
-      <c r="BK1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>Odd_HTS_1x1_Back</t>
         </is>
       </c>
-      <c r="BL1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>Odd_HTS_2x2_Lay</t>
         </is>
       </c>
-      <c r="BM1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>Odd_HTS_2x2_Back</t>
         </is>
       </c>
-      <c r="BN1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>Odd_HTS_1x0_Lay</t>
         </is>
       </c>
-      <c r="BO1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>Odd_HTS_1x0_Back</t>
         </is>
       </c>
-      <c r="BP1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>Odd_HTS_2x0_Lay</t>
         </is>
       </c>
-      <c r="BQ1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>Odd_HTS_2x0_Back</t>
         </is>
       </c>
-      <c r="BR1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>Odd_HTS_2x1_Lay</t>
         </is>
       </c>
-      <c r="BS1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>Odd_HTS_2x1_Back</t>
         </is>
       </c>
-      <c r="BT1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>Odd_HTS_0x1_Lay</t>
         </is>
       </c>
-      <c r="BU1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>Odd_HTS_0x1_Back</t>
         </is>
       </c>
-      <c r="BV1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>Odd_HTS_0x2_Lay</t>
         </is>
       </c>
-      <c r="BW1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>Odd_HTS_0x2_Back</t>
         </is>
       </c>
-      <c r="BX1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>Odd_HTS_1x2_Lay</t>
         </is>
       </c>
-      <c r="BY1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>Odd_HTS_1x2_Back</t>
         </is>
       </c>
-      <c r="BZ1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>Odd_HTS_Outros_Lay</t>
         </is>
       </c>
-      <c r="CA1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>Odd_HTS_Outros_Back</t>
         </is>
       </c>
-      <c r="CB1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>SnapshotTS</t>
         </is>
@@ -845,237 +857,237 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.66</v>
+        <v>2.56</v>
       </c>
       <c r="G2" t="n">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="H2" t="n">
-        <v>2.94</v>
+        <v>2.72</v>
       </c>
       <c r="I2" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="J2" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="K2" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="L2" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N2" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="O2" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S2" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="V2" t="n">
         <v>1.41</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S2" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.46</v>
       </c>
       <c r="W2" t="n">
         <v>1.51</v>
       </c>
       <c r="X2" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AQ2" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AR2" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS2" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AT2" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AU2" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV2" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW2" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="AX2" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY2" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ2" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA2" t="n">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="BB2" t="n">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BC2" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BD2" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BE2" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BF2" t="n">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BH2" t="n">
         <v>1000</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.79</v>
+        <v>1.01</v>
       </c>
       <c r="BJ2" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BK2" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA2" t="n">
         <v>1.6</v>
       </c>
-      <c r="BL2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>30</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>8</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>36</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>50</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>1.73</v>
-      </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-13 22:40:56</t>
+          <t>2026-07-14 07:32:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Ecuadorian Serie B</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1085,251 +1097,251 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CD Leones del Norte</t>
+          <t>Vinotinto Ecuador</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>El Nacional</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.5</v>
+        <v>1.04</v>
       </c>
       <c r="G3" t="n">
-        <v>2.76</v>
+        <v>1000</v>
       </c>
       <c r="H3" t="n">
-        <v>3.4</v>
+        <v>1.04</v>
       </c>
       <c r="I3" t="n">
-        <v>3.85</v>
+        <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>2.82</v>
+        <v>1.01</v>
       </c>
       <c r="K3" t="n">
-        <v>3.3</v>
+        <v>950</v>
       </c>
       <c r="L3" t="n">
-        <v>1.57</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>2.62</v>
+        <v>1.24</v>
       </c>
       <c r="O3" t="n">
-        <v>1.56</v>
+        <v>1.22</v>
       </c>
       <c r="P3" t="n">
-        <v>1.48</v>
+        <v>1.24</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.72</v>
+        <v>1.01</v>
       </c>
       <c r="R3" t="n">
         <v>1.18</v>
       </c>
       <c r="S3" t="n">
-        <v>5.7</v>
+        <v>1.22</v>
       </c>
       <c r="T3" t="n">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="U3" t="n">
-        <v>1.71</v>
+        <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>1.57</v>
+        <v>1.01</v>
       </c>
       <c r="X3" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Z3" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AA3" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AC3" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AD3" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AE3" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AG3" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AH3" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AI3" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AL3" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AM3" t="n">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="AQ3" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AR3" t="n">
-        <v>19</v>
+        <v>1.03</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.1</v>
+        <v>1.03</v>
       </c>
       <c r="AT3" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="AU3" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="AV3" t="n">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="AW3" t="n">
-        <v>5</v>
+        <v>1.03</v>
       </c>
       <c r="AX3" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY3" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AZ3" t="n">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="BA3" t="n">
-        <v>5.1</v>
+        <v>1.03</v>
       </c>
       <c r="BB3" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="BC3" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="BD3" t="n">
-        <v>5</v>
+        <v>1.03</v>
       </c>
       <c r="BE3" t="n">
-        <v>5.3</v>
+        <v>1.03</v>
       </c>
       <c r="BF3" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BG3" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BH3" t="n">
-        <v>2.74</v>
+        <v>1000</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.26</v>
+        <v>1.01</v>
       </c>
       <c r="BJ3" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BN3" t="n">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BP3" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BT3" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA3" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-13 22:40:56</t>
+          <t>2026-07-14 07:32:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Bolivian Liga de Futbol Profesional</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1344,246 +1356,246 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Univ Catolica (Ecu)</t>
+          <t>Real Potosi</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>LDU</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.48</v>
+        <v>1.44</v>
       </c>
       <c r="G4" t="n">
-        <v>2.68</v>
+        <v>1000</v>
       </c>
       <c r="H4" t="n">
-        <v>3.05</v>
+        <v>1.04</v>
       </c>
       <c r="I4" t="n">
-        <v>3.4</v>
+        <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>3.2</v>
+        <v>1.03</v>
       </c>
       <c r="K4" t="n">
-        <v>3.65</v>
+        <v>1000</v>
       </c>
       <c r="L4" t="n">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="O4" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="P4" t="n">
-        <v>1.81</v>
+        <v>1.25</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.08</v>
+        <v>1.44</v>
       </c>
       <c r="R4" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="S4" t="n">
-        <v>3.75</v>
+        <v>2.16</v>
       </c>
       <c r="T4" t="n">
-        <v>1.8</v>
+        <v>1.01</v>
       </c>
       <c r="U4" t="n">
-        <v>1.99</v>
+        <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="X4" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AD4" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AE4" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AI4" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ4" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AR4" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS4" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="AT4" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU4" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV4" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AW4" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="AX4" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY4" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA4" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BB4" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC4" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BD4" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BE4" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BF4" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BG4" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH4" t="n">
         <v>1000</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.85</v>
+        <v>1.01</v>
       </c>
       <c r="BJ4" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.62</v>
+        <v>1.01</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.85</v>
+        <v>1.01</v>
       </c>
       <c r="BN4" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="BP4" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.74</v>
+        <v>1.01</v>
       </c>
       <c r="BR4" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.78</v>
+        <v>1.01</v>
       </c>
       <c r="BT4" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BV4" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.76</v>
+        <v>1.01</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.79</v>
+        <v>1.01</v>
       </c>
       <c r="BZ4" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.78</v>
+        <v>1.01</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-13 22:40:56</t>
+          <t>2026-07-14 07:32:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>US United Soccer League</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1593,192 +1605,192 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Miami FC</t>
+          <t>CD Leones del Norte</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="G5" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K5" t="n">
         <v>3.2</v>
       </c>
-      <c r="H5" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="I5" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="J5" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="K5" t="n">
-        <v>3.9</v>
-      </c>
       <c r="L5" t="n">
-        <v>1.36</v>
+        <v>1.54</v>
       </c>
       <c r="M5" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>4.1</v>
+        <v>2.46</v>
       </c>
       <c r="O5" t="n">
-        <v>1.28</v>
+        <v>1.52</v>
       </c>
       <c r="P5" t="n">
-        <v>1.99</v>
+        <v>1.45</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.85</v>
+        <v>2.52</v>
       </c>
       <c r="R5" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V5" t="n">
         <v>1.37</v>
       </c>
-      <c r="S5" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.58</v>
-      </c>
       <c r="W5" t="n">
-        <v>1.46</v>
+        <v>1.56</v>
       </c>
       <c r="X5" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AD5" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AE5" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AG5" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AH5" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AI5" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AL5" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AM5" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AQ5" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AR5" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT5" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AU5" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV5" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AW5" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AX5" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AY5" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AZ5" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF5" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BG5" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH5" t="n">
-        <v>3.65</v>
+        <v>1000</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.92</v>
+        <v>1.01</v>
       </c>
       <c r="BJ5" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
@@ -1787,57 +1799,57 @@
         <v>1.01</v>
       </c>
       <c r="BN5" t="n">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BP5" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BR5" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BT5" t="n">
-        <v>5.8</v>
+        <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BV5" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BX5" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BZ5" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-13 22:40:56</t>
+          <t>2026-07-14 07:32:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>US United Soccer League</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1847,244 +1859,244 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Lexington SC</t>
+          <t>Univ Catolica (Ecu)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>LDU</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.71</v>
+        <v>2.38</v>
       </c>
       <c r="G6" t="n">
-        <v>1.81</v>
+        <v>2.8</v>
       </c>
       <c r="H6" t="n">
-        <v>5</v>
+        <v>2.92</v>
       </c>
       <c r="I6" t="n">
-        <v>5.7</v>
+        <v>3.6</v>
       </c>
       <c r="J6" t="n">
-        <v>3.9</v>
+        <v>2.92</v>
       </c>
       <c r="K6" t="n">
-        <v>4.3</v>
+        <v>36</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="N6" t="n">
-        <v>4</v>
+        <v>3.35</v>
       </c>
       <c r="O6" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="P6" t="n">
-        <v>2.08</v>
+        <v>1.79</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.84</v>
+        <v>2.02</v>
       </c>
       <c r="R6" t="n">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="S6" t="n">
-        <v>3.05</v>
+        <v>2.82</v>
       </c>
       <c r="T6" t="n">
-        <v>1.81</v>
+        <v>1.52</v>
       </c>
       <c r="U6" t="n">
-        <v>2.06</v>
+        <v>1.66</v>
       </c>
       <c r="V6" t="n">
-        <v>1.21</v>
+        <v>1.42</v>
       </c>
       <c r="W6" t="n">
-        <v>2.24</v>
+        <v>1.55</v>
       </c>
       <c r="X6" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AD6" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT6" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AU6" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AV6" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX6" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AY6" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB6" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BC6" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF6" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>55</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="n">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.92</v>
+        <v>1.01</v>
       </c>
       <c r="BJ6" t="n">
         <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="BN6" t="n">
         <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="BP6" t="n">
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="BT6" t="n">
         <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-13 22:40:56</t>
+          <t>2026-07-14 07:32:00</t>
         </is>
       </c>
     </row>
@@ -2101,244 +2113,1260 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Miami FC</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Indy Eleven</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G7" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K7" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>2026-07-14 07:32:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>US United Soccer League</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Lexington SC</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>New Mexico United</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="H8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K8" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W8" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>2026-07-14 07:32:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>US United Soccer League</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
           <t>20:30:00</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Sporting Club Jacksonvil</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
-      <c r="F7" t="n">
-        <v>5</v>
-      </c>
-      <c r="G7" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J7" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="K7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N7" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="P7" t="n">
+      <c r="F9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="G9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N9" t="n">
         <v>1.97</v>
       </c>
-      <c r="Q7" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="V7" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X7" t="n">
-        <v>20</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>13</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>23</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>23</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>22</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>50</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>26</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>40</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>160</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>90</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>90</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>100</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>13</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>12</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>13</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>60</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BX7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BZ7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="CB7" t="inlineStr">
-        <is>
-          <t>2026-07-13 22:40:56</t>
+      <c r="O9" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>2026-07-14 07:32:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Bolivian Liga de Futbol Profesional</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>The Strongest</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Oriente Petrolero</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W10" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>2026-07-14 07:32:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Ecuadorian Serie A</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Barcelona (Ecu)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Guayaquil City</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>2026-07-14 07:32:00</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-15.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-15.xlsx
@@ -857,230 +857,230 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.56</v>
+        <v>2.48</v>
       </c>
       <c r="G2" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="H2" t="n">
-        <v>2.72</v>
+        <v>3</v>
       </c>
       <c r="I2" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J2" t="n">
         <v>3.1</v>
       </c>
       <c r="K2" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="L2" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M2" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N2" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="O2" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="P2" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="R2" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="S2" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="T2" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="U2" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="V2" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W2" t="n">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AF2" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI2" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM2" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BH2" t="n">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.01</v>
+        <v>2.54</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.49</v>
+        <v>7.8</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.65</v>
+        <v>10</v>
       </c>
       <c r="BN2" t="n">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.37</v>
+        <v>4.8</v>
       </c>
       <c r="BP2" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.57</v>
+        <v>7.4</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.61</v>
+        <v>8.4</v>
       </c>
       <c r="BT2" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.58</v>
+        <v>7.4</v>
       </c>
       <c r="BX2" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.61</v>
+        <v>8.6</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-14 07:32:00</t>
+          <t>2026-07-14 09:40:53</t>
         </is>
       </c>
     </row>
@@ -1123,10 +1123,10 @@
         <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K3" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L3" t="n">
         <v>1.01</v>
@@ -1135,22 +1135,22 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="O3" t="n">
         <v>1.22</v>
       </c>
       <c r="P3" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="R3" t="n">
         <v>1.18</v>
       </c>
       <c r="S3" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="T3" t="n">
         <v>1.01</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-14 07:32:00</t>
+          <t>2026-07-14 09:40:53</t>
         </is>
       </c>
     </row>
@@ -1398,10 +1398,10 @@
         <v>1.25</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="R4" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S4" t="n">
         <v>2.16</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-14 07:32:00</t>
+          <t>2026-07-14 09:40:53</t>
         </is>
       </c>
     </row>
@@ -1622,49 +1622,49 @@
         <v>2.5</v>
       </c>
       <c r="G5" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="H5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="K5" t="n">
         <v>3.25</v>
       </c>
-      <c r="I5" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="K5" t="n">
-        <v>3.2</v>
-      </c>
       <c r="L5" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="M5" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N5" t="n">
         <v>2.46</v>
       </c>
       <c r="O5" t="n">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="P5" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.52</v>
+        <v>2.7</v>
       </c>
       <c r="R5" t="n">
         <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="T5" t="n">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="U5" t="n">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="V5" t="n">
         <v>1.37</v>
@@ -1673,176 +1673,176 @@
         <v>1.56</v>
       </c>
       <c r="X5" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="Y5" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Z5" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AB5" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AC5" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AD5" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF5" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AI5" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AK5" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AL5" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM5" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AN5" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO5" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BH5" t="n">
-        <v>1000</v>
+        <v>2.74</v>
       </c>
       <c r="BI5" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="BJ5" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BN5" t="n">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BP5" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BT5" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BU5" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-14 07:32:00</t>
+          <t>2026-07-14 09:40:53</t>
         </is>
       </c>
     </row>
@@ -1873,25 +1873,25 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="G6" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="H6" t="n">
         <v>2.92</v>
       </c>
       <c r="I6" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="J6" t="n">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="K6" t="n">
-        <v>36</v>
+        <v>3.65</v>
       </c>
       <c r="L6" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M6" t="n">
         <v>1.08</v>
@@ -1900,203 +1900,203 @@
         <v>3.35</v>
       </c>
       <c r="O6" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="P6" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="Q6" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="U6" t="n">
         <v>2.02</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.66</v>
       </c>
       <c r="V6" t="n">
         <v>1.42</v>
       </c>
       <c r="W6" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AA6" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AE6" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AI6" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL6" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM6" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AO6" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BH6" t="n">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.01</v>
+        <v>2.72</v>
       </c>
       <c r="BJ6" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.51</v>
+        <v>5.1</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.69</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN6" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.39</v>
+        <v>4.3</v>
       </c>
       <c r="BP6" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.61</v>
+        <v>7</v>
       </c>
       <c r="BR6" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.64</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT6" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BU6" t="n">
-        <v>1.42</v>
+        <v>5.3</v>
       </c>
       <c r="BV6" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.62</v>
+        <v>7.4</v>
       </c>
       <c r="BX6" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.65</v>
+        <v>8.4</v>
       </c>
       <c r="BZ6" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.64</v>
+        <v>8</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-14 07:32:00</t>
+          <t>2026-07-14 09:40:53</t>
         </is>
       </c>
     </row>
@@ -2130,142 +2130,142 @@
         <v>2.8</v>
       </c>
       <c r="G7" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="H7" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="I7" t="n">
-        <v>3.05</v>
+        <v>2.7</v>
       </c>
       <c r="J7" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="K7" t="n">
-        <v>5.3</v>
+        <v>3.95</v>
       </c>
       <c r="L7" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="M7" t="n">
         <v>1.06</v>
       </c>
       <c r="N7" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="O7" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="P7" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.24</v>
+        <v>1.81</v>
       </c>
       <c r="R7" t="n">
-        <v>1.18</v>
+        <v>1.39</v>
       </c>
       <c r="S7" t="n">
-        <v>1.69</v>
+        <v>3.05</v>
       </c>
       <c r="T7" t="n">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="U7" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="V7" t="n">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="W7" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AB7" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AC7" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AE7" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF7" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AG7" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AI7" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK7" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AL7" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM7" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AN7" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AO7" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AS7" t="n">
         <v>1.03</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="BA7" t="n">
         <v>1.03</v>
@@ -2283,22 +2283,22 @@
         <v>1.03</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BH7" t="n">
-        <v>1000</v>
+        <v>3.7</v>
       </c>
       <c r="BI7" t="n">
-        <v>1.01</v>
+        <v>2.96</v>
       </c>
       <c r="BJ7" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
@@ -2307,50 +2307,50 @@
         <v>1.01</v>
       </c>
       <c r="BN7" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BP7" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BR7" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BT7" t="n">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BU7" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BV7" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BX7" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BZ7" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-14 07:32:00</t>
+          <t>2026-07-14 09:40:53</t>
         </is>
       </c>
     </row>
@@ -2381,118 +2381,118 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.61</v>
+        <v>1.69</v>
       </c>
       <c r="G8" t="n">
-        <v>1.98</v>
+        <v>1.79</v>
       </c>
       <c r="H8" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="I8" t="n">
-        <v>10.5</v>
+        <v>5.8</v>
       </c>
       <c r="J8" t="n">
-        <v>3.55</v>
+        <v>3.95</v>
       </c>
       <c r="K8" t="n">
-        <v>7.2</v>
+        <v>4.4</v>
       </c>
       <c r="L8" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M8" t="n">
         <v>1.06</v>
       </c>
       <c r="N8" t="n">
-        <v>2.02</v>
+        <v>3.85</v>
       </c>
       <c r="O8" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="P8" t="n">
         <v>2.02</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.68</v>
+        <v>1.84</v>
       </c>
       <c r="R8" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="S8" t="n">
-        <v>2.6</v>
+        <v>3.15</v>
       </c>
       <c r="T8" t="n">
-        <v>1.4</v>
+        <v>1.84</v>
       </c>
       <c r="U8" t="n">
-        <v>1.7</v>
+        <v>2.02</v>
       </c>
       <c r="V8" t="n">
-        <v>1.1</v>
+        <v>1.21</v>
       </c>
       <c r="W8" t="n">
-        <v>2.02</v>
+        <v>2.26</v>
       </c>
       <c r="X8" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Y8" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Z8" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA8" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AB8" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AE8" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AF8" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI8" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AK8" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AL8" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM8" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN8" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AO8" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="AR8" t="n">
         <v>1.03</v>
@@ -2501,34 +2501,34 @@
         <v>1.03</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="AW8" t="n">
         <v>1.03</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="BA8" t="n">
         <v>1.03</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="BD8" t="n">
         <v>1.03</v>
@@ -2537,22 +2537,22 @@
         <v>1.03</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.01</v>
+        <v>55</v>
       </c>
       <c r="BH8" t="n">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="BI8" t="n">
-        <v>1.01</v>
+        <v>2.88</v>
       </c>
       <c r="BJ8" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
@@ -2561,50 +2561,50 @@
         <v>1.01</v>
       </c>
       <c r="BN8" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BP8" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BQ8" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BR8" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BT8" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU8" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BZ8" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="CA8" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-14 07:32:00</t>
+          <t>2026-07-14 09:40:53</t>
         </is>
       </c>
     </row>
@@ -2635,145 +2635,145 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="G9" t="n">
-        <v>7.2</v>
+        <v>5.5</v>
       </c>
       <c r="H9" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="I9" t="n">
-        <v>1.99</v>
+        <v>1.84</v>
       </c>
       <c r="J9" t="n">
-        <v>2.8</v>
+        <v>3.95</v>
       </c>
       <c r="K9" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="L9" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M9" t="n">
         <v>1.06</v>
       </c>
       <c r="N9" t="n">
-        <v>1.97</v>
+        <v>3.85</v>
       </c>
       <c r="O9" t="n">
         <v>1.29</v>
       </c>
       <c r="P9" t="n">
-        <v>1.64</v>
+        <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.53</v>
+        <v>1.83</v>
       </c>
       <c r="R9" t="n">
-        <v>1.18</v>
+        <v>1.39</v>
       </c>
       <c r="S9" t="n">
-        <v>1.53</v>
+        <v>3.1</v>
       </c>
       <c r="T9" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="U9" t="n">
-        <v>1.65</v>
+        <v>2.04</v>
       </c>
       <c r="V9" t="n">
-        <v>1.17</v>
+        <v>2.18</v>
       </c>
       <c r="W9" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="X9" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Y9" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AB9" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AC9" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AE9" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AF9" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AG9" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AH9" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI9" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AK9" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AL9" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM9" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN9" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AO9" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="AX9" t="n">
         <v>1.03</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="BA9" t="n">
         <v>1.03</v>
@@ -2791,22 +2791,22 @@
         <v>1.03</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH9" t="n">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="BJ9" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK9" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
@@ -2815,50 +2815,50 @@
         <v>1.01</v>
       </c>
       <c r="BN9" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BP9" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BQ9" t="n">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="BR9" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BS9" t="n">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BT9" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BU9" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BV9" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BW9" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX9" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BZ9" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="CA9" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-14 07:32:00</t>
+          <t>2026-07-14 09:40:53</t>
         </is>
       </c>
     </row>
@@ -2892,7 +2892,7 @@
         <v>1.04</v>
       </c>
       <c r="G10" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="H10" t="n">
         <v>1.04</v>
@@ -2913,22 +2913,22 @@
         <v>1.03</v>
       </c>
       <c r="N10" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="O10" t="n">
         <v>1.09</v>
       </c>
       <c r="P10" t="n">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="R10" t="n">
         <v>1.39</v>
       </c>
       <c r="S10" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T10" t="n">
         <v>1.01</v>
@@ -2940,7 +2940,7 @@
         <v>1.01</v>
       </c>
       <c r="W10" t="n">
-        <v>2.54</v>
+        <v>2.26</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-14 07:32:00</t>
+          <t>2026-07-14 09:40:53</t>
         </is>
       </c>
     </row>
@@ -3143,230 +3143,230 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.04</v>
+        <v>1.57</v>
       </c>
       <c r="G11" t="n">
-        <v>1000</v>
+        <v>1.67</v>
       </c>
       <c r="H11" t="n">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="I11" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="K11" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="L11" t="n">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="M11" t="n">
         <v>1.08</v>
       </c>
       <c r="N11" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="O11" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="P11" t="n">
-        <v>1.25</v>
+        <v>1.81</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="R11" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="S11" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="T11" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="U11" t="n">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="V11" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="W11" t="n">
-        <v>1.18</v>
+        <v>2.5</v>
       </c>
       <c r="X11" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Z11" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AA11" t="n">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="AB11" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC11" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD11" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AE11" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AF11" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AG11" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AI11" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AK11" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AL11" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM11" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AN11" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AO11" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BH11" t="n">
-        <v>1000</v>
+        <v>3.3</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.01</v>
+        <v>2.98</v>
       </c>
       <c r="BJ11" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK11" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BN11" t="n">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BP11" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BQ11" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BT11" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BU11" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BZ11" t="n">
         <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-14 07:32:00</t>
+          <t>2026-07-14 09:40:53</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-15.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-15.xlsx
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="G2" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="H2" t="n">
         <v>3</v>
@@ -872,16 +872,16 @@
         <v>3.1</v>
       </c>
       <c r="K2" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="L2" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="M2" t="n">
         <v>1.09</v>
       </c>
       <c r="N2" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="O2" t="n">
         <v>1.42</v>
@@ -920,7 +920,7 @@
         <v>22</v>
       </c>
       <c r="AA2" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AB2" t="n">
         <v>10.5</v>
@@ -932,7 +932,7 @@
         <v>15</v>
       </c>
       <c r="AE2" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AF2" t="n">
         <v>17.5</v>
@@ -944,25 +944,25 @@
         <v>21</v>
       </c>
       <c r="AI2" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AJ2" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AK2" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AL2" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM2" t="n">
         <v>140</v>
       </c>
       <c r="AN2" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AO2" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AP2" t="n">
         <v>9.199999999999999</v>
@@ -986,7 +986,7 @@
         <v>12</v>
       </c>
       <c r="AW2" t="n">
-        <v>32</v>
+        <v>6.4</v>
       </c>
       <c r="AX2" t="n">
         <v>14</v>
@@ -1004,19 +1004,19 @@
         <v>6.4</v>
       </c>
       <c r="BC2" t="n">
-        <v>25</v>
+        <v>6.2</v>
       </c>
       <c r="BD2" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BE2" t="n">
         <v>7.2</v>
       </c>
       <c r="BF2" t="n">
-        <v>25</v>
+        <v>6.2</v>
       </c>
       <c r="BG2" t="n">
-        <v>32</v>
+        <v>6.4</v>
       </c>
       <c r="BH2" t="n">
         <v>3.15</v>
@@ -1028,22 +1028,22 @@
         <v>10.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN2" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BO2" t="n">
         <v>4.8</v>
       </c>
       <c r="BP2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BQ2" t="n">
         <v>7.4</v>
@@ -1052,7 +1052,7 @@
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT2" t="n">
         <v>6.2</v>
@@ -1064,23 +1064,23 @@
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BX2" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="BY2" t="n">
+        <v>9</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>48</v>
+      </c>
+      <c r="CA2" t="n">
         <v>8.6</v>
       </c>
-      <c r="BZ2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-14 09:40:53</t>
+          <t>2026-07-14 11:49:16</t>
         </is>
       </c>
     </row>
@@ -1135,16 +1135,16 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="O3" t="n">
         <v>1.22</v>
       </c>
       <c r="P3" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="R3" t="n">
         <v>1.18</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-14 09:40:53</t>
+          <t>2026-07-14 11:49:16</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="O4" t="n">
         <v>1.2</v>
@@ -1401,7 +1401,7 @@
         <v>1.28</v>
       </c>
       <c r="R4" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S4" t="n">
         <v>2.16</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-14 09:40:53</t>
+          <t>2026-07-14 11:49:16</t>
         </is>
       </c>
     </row>
@@ -1628,25 +1628,25 @@
         <v>3.3</v>
       </c>
       <c r="I5" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="J5" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="K5" t="n">
         <v>3.25</v>
       </c>
       <c r="L5" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="M5" t="n">
         <v>1.12</v>
       </c>
       <c r="N5" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="O5" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="P5" t="n">
         <v>1.47</v>
@@ -1658,13 +1658,13 @@
         <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="T5" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="U5" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="V5" t="n">
         <v>1.37</v>
@@ -1673,7 +1673,7 @@
         <v>1.56</v>
       </c>
       <c r="X5" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y5" t="n">
         <v>11</v>
@@ -1682,19 +1682,19 @@
         <v>27</v>
       </c>
       <c r="AA5" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AB5" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC5" t="n">
         <v>8</v>
       </c>
       <c r="AD5" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AE5" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AF5" t="n">
         <v>17.5</v>
@@ -1733,10 +1733,10 @@
         <v>8</v>
       </c>
       <c r="AR5" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="AT5" t="n">
         <v>6.4</v>
@@ -1745,40 +1745,40 @@
         <v>6</v>
       </c>
       <c r="AV5" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX5" t="n">
         <v>12.5</v>
       </c>
-      <c r="AW5" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AY5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ5" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BA5" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="BB5" t="n">
-        <v>32</v>
+        <v>4.7</v>
       </c>
       <c r="BC5" t="n">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="BD5" t="n">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="BF5" t="n">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="BG5" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="BH5" t="n">
         <v>2.74</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-14 09:40:53</t>
+          <t>2026-07-14 11:49:16</t>
         </is>
       </c>
     </row>
@@ -1873,10 +1873,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="G6" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="H6" t="n">
         <v>2.92</v>
@@ -1891,7 +1891,7 @@
         <v>3.65</v>
       </c>
       <c r="L6" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="M6" t="n">
         <v>1.08</v>
@@ -1903,16 +1903,16 @@
         <v>1.36</v>
       </c>
       <c r="P6" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="R6" t="n">
         <v>1.3</v>
       </c>
       <c r="S6" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="T6" t="n">
         <v>1.81</v>
@@ -1924,7 +1924,7 @@
         <v>1.42</v>
       </c>
       <c r="W6" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="X6" t="n">
         <v>14.5</v>
@@ -1975,7 +1975,7 @@
         <v>120</v>
       </c>
       <c r="AN6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AO6" t="n">
         <v>42</v>
@@ -1990,7 +1990,7 @@
         <v>17</v>
       </c>
       <c r="AS6" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AT6" t="n">
         <v>8.4</v>
@@ -2032,7 +2032,7 @@
         <v>21</v>
       </c>
       <c r="BG6" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BH6" t="n">
         <v>3.4</v>
@@ -2050,31 +2050,31 @@
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BN6" t="n">
         <v>5.6</v>
       </c>
       <c r="BO6" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BP6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BQ6" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BR6" t="n">
         <v>36</v>
       </c>
       <c r="BS6" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BT6" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BU6" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="BV6" t="n">
         <v>26</v>
@@ -2086,17 +2086,17 @@
         <v>40</v>
       </c>
       <c r="BY6" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ6" t="n">
         <v>32</v>
       </c>
       <c r="CA6" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-14 09:40:53</t>
+          <t>2026-07-14 11:49:16</t>
         </is>
       </c>
     </row>
@@ -2136,22 +2136,22 @@
         <v>2.4</v>
       </c>
       <c r="I7" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="J7" t="n">
         <v>3.4</v>
       </c>
       <c r="K7" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L7" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="M7" t="n">
         <v>1.06</v>
       </c>
       <c r="N7" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="O7" t="n">
         <v>1.27</v>
@@ -2169,7 +2169,7 @@
         <v>3.05</v>
       </c>
       <c r="T7" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="U7" t="n">
         <v>2.2</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-14 09:40:53</t>
+          <t>2026-07-14 11:49:16</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="G8" t="n">
         <v>1.79</v>
@@ -2390,13 +2390,13 @@
         <v>5.1</v>
       </c>
       <c r="I8" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="J8" t="n">
         <v>3.95</v>
       </c>
       <c r="K8" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L8" t="n">
         <v>1.31</v>
@@ -2492,7 +2492,7 @@
         <v>12</v>
       </c>
       <c r="AQ8" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="AR8" t="n">
         <v>1.03</v>
@@ -2504,7 +2504,7 @@
         <v>6.4</v>
       </c>
       <c r="AU8" t="n">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="AV8" t="n">
         <v>15</v>
@@ -2546,7 +2546,7 @@
         <v>3.65</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="BJ8" t="n">
         <v>10.5</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-14 09:40:53</t>
+          <t>2026-07-14 11:49:16</t>
         </is>
       </c>
     </row>
@@ -2635,19 +2635,19 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="G9" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="H9" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="I9" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="J9" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="K9" t="n">
         <v>4.5</v>
@@ -2659,16 +2659,16 @@
         <v>1.06</v>
       </c>
       <c r="N9" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="O9" t="n">
         <v>1.29</v>
       </c>
       <c r="P9" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="R9" t="n">
         <v>1.39</v>
@@ -2683,10 +2683,10 @@
         <v>2.04</v>
       </c>
       <c r="V9" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="W9" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="X9" t="n">
         <v>20</v>
@@ -2740,7 +2740,7 @@
         <v>85</v>
       </c>
       <c r="AO9" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AP9" t="n">
         <v>12.5</v>
@@ -2800,7 +2800,7 @@
         <v>3.6</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="BJ9" t="n">
         <v>10.5</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-14 09:40:53</t>
+          <t>2026-07-14 11:49:16</t>
         </is>
       </c>
     </row>
@@ -2913,22 +2913,22 @@
         <v>1.03</v>
       </c>
       <c r="N10" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="O10" t="n">
         <v>1.09</v>
       </c>
       <c r="P10" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="R10" t="n">
         <v>1.39</v>
       </c>
       <c r="S10" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T10" t="n">
         <v>1.01</v>
@@ -2940,7 +2940,7 @@
         <v>1.01</v>
       </c>
       <c r="W10" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-14 09:40:53</t>
+          <t>2026-07-14 11:49:16</t>
         </is>
       </c>
     </row>
@@ -3146,13 +3146,13 @@
         <v>1.57</v>
       </c>
       <c r="G11" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="H11" t="n">
         <v>6.8</v>
       </c>
       <c r="I11" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="J11" t="n">
         <v>3.85</v>
@@ -3170,13 +3170,13 @@
         <v>3.35</v>
       </c>
       <c r="O11" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P11" t="n">
         <v>1.81</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="R11" t="n">
         <v>1.3</v>
@@ -3212,7 +3212,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AC11" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="AD11" t="n">
         <v>34</v>
@@ -3221,10 +3221,10 @@
         <v>150</v>
       </c>
       <c r="AF11" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AG11" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH11" t="n">
         <v>29</v>
@@ -3251,58 +3251,58 @@
         <v>230</v>
       </c>
       <c r="AP11" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>17.5</v>
+        <v>4.8</v>
       </c>
       <c r="AR11" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="AT11" t="n">
         <v>6.2</v>
       </c>
       <c r="AU11" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV11" t="n">
-        <v>21</v>
+        <v>5.1</v>
       </c>
       <c r="AW11" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="AX11" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AY11" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ11" t="n">
-        <v>21</v>
+        <v>4.9</v>
       </c>
       <c r="BA11" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="BB11" t="n">
-        <v>11.5</v>
+        <v>4.5</v>
       </c>
       <c r="BC11" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BD11" t="n">
-        <v>34</v>
+        <v>5.4</v>
       </c>
       <c r="BE11" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="BF11" t="n">
         <v>9.6</v>
       </c>
       <c r="BG11" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="BH11" t="n">
         <v>3.3</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-14 09:40:53</t>
+          <t>2026-07-14 11:49:16</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-15.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-15.xlsx
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="G2" t="n">
         <v>2.78</v>
@@ -866,7 +866,7 @@
         <v>3</v>
       </c>
       <c r="I2" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="J2" t="n">
         <v>3.1</v>
@@ -875,7 +875,7 @@
         <v>3.4</v>
       </c>
       <c r="L2" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="M2" t="n">
         <v>1.09</v>
@@ -899,10 +899,10 @@
         <v>4.2</v>
       </c>
       <c r="T2" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="U2" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="V2" t="n">
         <v>1.42</v>
@@ -926,10 +926,10 @@
         <v>10.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AD2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AE2" t="n">
         <v>44</v>
@@ -944,22 +944,22 @@
         <v>21</v>
       </c>
       <c r="AI2" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AJ2" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AK2" t="n">
         <v>36</v>
       </c>
       <c r="AL2" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AM2" t="n">
         <v>140</v>
       </c>
       <c r="AN2" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AO2" t="n">
         <v>46</v>
@@ -986,7 +986,7 @@
         <v>12</v>
       </c>
       <c r="AW2" t="n">
-        <v>6.4</v>
+        <v>30</v>
       </c>
       <c r="AX2" t="n">
         <v>14</v>
@@ -998,25 +998,25 @@
         <v>16</v>
       </c>
       <c r="BA2" t="n">
-        <v>6.6</v>
+        <v>42</v>
       </c>
       <c r="BB2" t="n">
-        <v>6.4</v>
+        <v>34</v>
       </c>
       <c r="BC2" t="n">
-        <v>6.2</v>
+        <v>26</v>
       </c>
       <c r="BD2" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BE2" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BF2" t="n">
-        <v>6.2</v>
+        <v>27</v>
       </c>
       <c r="BG2" t="n">
-        <v>6.4</v>
+        <v>32</v>
       </c>
       <c r="BH2" t="n">
         <v>3.15</v>
@@ -1034,16 +1034,16 @@
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BN2" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BO2" t="n">
         <v>4.8</v>
       </c>
       <c r="BP2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BQ2" t="n">
         <v>7.4</v>
@@ -1052,7 +1052,7 @@
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BT2" t="n">
         <v>6.2</v>
@@ -1061,26 +1061,26 @@
         <v>5.1</v>
       </c>
       <c r="BV2" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BW2" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BX2" t="n">
         <v>55</v>
       </c>
       <c r="BY2" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BZ2" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-14 11:49:16</t>
+          <t>2026-07-14 13:57:32</t>
         </is>
       </c>
     </row>
@@ -1135,22 +1135,22 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="O3" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="P3" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="R3" t="n">
         <v>1.18</v>
       </c>
       <c r="S3" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="T3" t="n">
         <v>1.01</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-14 11:49:16</t>
+          <t>2026-07-14 13:57:32</t>
         </is>
       </c>
     </row>
@@ -1377,7 +1377,7 @@
         <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="K4" t="n">
         <v>1000</v>
@@ -1389,22 +1389,22 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="O4" t="n">
         <v>1.2</v>
       </c>
       <c r="P4" t="n">
-        <v>1.25</v>
+        <v>2.22</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="R4" t="n">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="S4" t="n">
-        <v>2.16</v>
+        <v>1.6</v>
       </c>
       <c r="T4" t="n">
         <v>1.01</v>
@@ -1416,7 +1416,7 @@
         <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>1.71</v>
+        <v>1.83</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-14 11:49:16</t>
+          <t>2026-07-14 13:57:32</t>
         </is>
       </c>
     </row>
@@ -1622,7 +1622,7 @@
         <v>2.5</v>
       </c>
       <c r="G5" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="H5" t="n">
         <v>3.3</v>
@@ -1646,7 +1646,7 @@
         <v>2.48</v>
       </c>
       <c r="O5" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="P5" t="n">
         <v>1.47</v>
@@ -1658,19 +1658,19 @@
         <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="T5" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="U5" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="V5" t="n">
         <v>1.37</v>
       </c>
       <c r="W5" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="X5" t="n">
         <v>9.199999999999999</v>
@@ -1724,16 +1724,16 @@
         <v>55</v>
       </c>
       <c r="AO5" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AP5" t="n">
         <v>6.8</v>
       </c>
       <c r="AQ5" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AR5" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AS5" t="n">
         <v>5</v>
@@ -1745,25 +1745,25 @@
         <v>6</v>
       </c>
       <c r="AV5" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AW5" t="n">
         <v>4.9</v>
       </c>
       <c r="AX5" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AY5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ5" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BA5" t="n">
         <v>5</v>
       </c>
       <c r="BB5" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BC5" t="n">
         <v>4.7</v>
@@ -1772,7 +1772,7 @@
         <v>4.9</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BF5" t="n">
         <v>4.8</v>
@@ -1790,7 +1790,7 @@
         <v>12</v>
       </c>
       <c r="BK5" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-14 11:49:16</t>
+          <t>2026-07-14 13:57:32</t>
         </is>
       </c>
     </row>
@@ -1873,37 +1873,37 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="G6" t="n">
         <v>2.72</v>
       </c>
       <c r="H6" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="I6" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="J6" t="n">
         <v>3.2</v>
       </c>
       <c r="K6" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L6" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="M6" t="n">
         <v>1.08</v>
       </c>
       <c r="N6" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="O6" t="n">
         <v>1.36</v>
       </c>
       <c r="P6" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="Q6" t="n">
         <v>2.06</v>
@@ -1921,7 +1921,7 @@
         <v>2.02</v>
       </c>
       <c r="V6" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W6" t="n">
         <v>1.58</v>
@@ -2056,7 +2056,7 @@
         <v>5.6</v>
       </c>
       <c r="BO6" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BP6" t="n">
         <v>20</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-14 11:49:16</t>
+          <t>2026-07-14 13:57:32</t>
         </is>
       </c>
     </row>
@@ -2127,25 +2127,25 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="G7" t="n">
         <v>3.2</v>
       </c>
       <c r="H7" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="I7" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="J7" t="n">
         <v>3.4</v>
       </c>
       <c r="K7" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L7" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="M7" t="n">
         <v>1.06</v>
@@ -2154,13 +2154,13 @@
         <v>3.9</v>
       </c>
       <c r="O7" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P7" t="n">
         <v>1.99</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="R7" t="n">
         <v>1.39</v>
@@ -2169,19 +2169,19 @@
         <v>3.05</v>
       </c>
       <c r="T7" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="U7" t="n">
         <v>2.2</v>
       </c>
       <c r="V7" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="W7" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="X7" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Y7" t="n">
         <v>13.5</v>
@@ -2193,7 +2193,7 @@
         <v>42</v>
       </c>
       <c r="AB7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AC7" t="n">
         <v>9.6</v>
@@ -2232,13 +2232,13 @@
         <v>32</v>
       </c>
       <c r="AO7" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AP7" t="n">
         <v>12</v>
       </c>
       <c r="AQ7" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR7" t="n">
         <v>13.5</v>
@@ -2286,13 +2286,13 @@
         <v>20</v>
       </c>
       <c r="BG7" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BH7" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="BJ7" t="n">
         <v>9.4</v>
@@ -2316,7 +2316,7 @@
         <v>23</v>
       </c>
       <c r="BQ7" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BR7" t="n">
         <v>34</v>
@@ -2325,7 +2325,7 @@
         <v>24</v>
       </c>
       <c r="BT7" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BU7" t="n">
         <v>4.4</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-14 11:49:16</t>
+          <t>2026-07-14 13:57:32</t>
         </is>
       </c>
     </row>
@@ -2426,7 +2426,7 @@
         <v>1.84</v>
       </c>
       <c r="U8" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="V8" t="n">
         <v>1.21</v>
@@ -2501,7 +2501,7 @@
         <v>1.03</v>
       </c>
       <c r="AT8" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="AU8" t="n">
         <v>7</v>
@@ -2537,7 +2537,7 @@
         <v>1.03</v>
       </c>
       <c r="BF8" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG8" t="n">
         <v>55</v>
@@ -2546,7 +2546,7 @@
         <v>3.65</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="BJ8" t="n">
         <v>10.5</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-14 11:49:16</t>
+          <t>2026-07-14 13:57:32</t>
         </is>
       </c>
     </row>
@@ -2635,22 +2635,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="G9" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="H9" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="I9" t="n">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="J9" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K9" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="L9" t="n">
         <v>1.32</v>
@@ -2659,7 +2659,7 @@
         <v>1.06</v>
       </c>
       <c r="N9" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="O9" t="n">
         <v>1.29</v>
@@ -2671,109 +2671,109 @@
         <v>1.84</v>
       </c>
       <c r="R9" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="S9" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T9" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="U9" t="n">
         <v>2.04</v>
       </c>
       <c r="V9" t="n">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="W9" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="X9" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Z9" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AB9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AC9" t="n">
         <v>11.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF9" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AG9" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AH9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI9" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AJ9" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AK9" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AL9" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AM9" t="n">
         <v>130</v>
       </c>
       <c r="AN9" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AO9" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AP9" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AR9" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AS9" t="n">
+        <v>15</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AW9" t="n">
         <v>14</v>
       </c>
-      <c r="AT9" t="n">
+      <c r="AX9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY9" t="n">
         <v>13.5</v>
       </c>
-      <c r="AU9" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>13</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>15</v>
-      </c>
       <c r="AZ9" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA9" t="n">
         <v>1.03</v>
@@ -2791,16 +2791,16 @@
         <v>1.03</v>
       </c>
       <c r="BF9" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="BG9" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH9" t="n">
         <v>3.6</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="BJ9" t="n">
         <v>10.5</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-14 11:49:16</t>
+          <t>2026-07-14 13:57:32</t>
         </is>
       </c>
     </row>
@@ -2892,7 +2892,7 @@
         <v>1.04</v>
       </c>
       <c r="G10" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="H10" t="n">
         <v>1.04</v>
@@ -2901,7 +2901,7 @@
         <v>1000</v>
       </c>
       <c r="J10" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="K10" t="n">
         <v>1000</v>
@@ -2913,13 +2913,13 @@
         <v>1.03</v>
       </c>
       <c r="N10" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="O10" t="n">
         <v>1.09</v>
       </c>
       <c r="P10" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="Q10" t="n">
         <v>1.29</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-14 11:49:16</t>
+          <t>2026-07-14 13:57:32</t>
         </is>
       </c>
     </row>
@@ -3146,7 +3146,7 @@
         <v>1.57</v>
       </c>
       <c r="G11" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="H11" t="n">
         <v>6.8</v>
@@ -3155,7 +3155,7 @@
         <v>8</v>
       </c>
       <c r="J11" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K11" t="n">
         <v>4.4</v>
@@ -3170,13 +3170,13 @@
         <v>3.35</v>
       </c>
       <c r="O11" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P11" t="n">
         <v>1.81</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.16</v>
+        <v>2.04</v>
       </c>
       <c r="R11" t="n">
         <v>1.3</v>
@@ -3185,7 +3185,7 @@
         <v>3.75</v>
       </c>
       <c r="T11" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U11" t="n">
         <v>1.79</v>
@@ -3194,7 +3194,7 @@
         <v>1.14</v>
       </c>
       <c r="W11" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="X11" t="n">
         <v>15.5</v>
@@ -3212,7 +3212,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AC11" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AD11" t="n">
         <v>34</v>
@@ -3221,10 +3221,10 @@
         <v>150</v>
       </c>
       <c r="AF11" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AG11" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH11" t="n">
         <v>29</v>
@@ -3251,28 +3251,28 @@
         <v>230</v>
       </c>
       <c r="AP11" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AQ11" t="n">
-        <v>4.8</v>
+        <v>17</v>
       </c>
       <c r="AR11" t="n">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="AS11" t="n">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="AT11" t="n">
         <v>6.2</v>
       </c>
       <c r="AU11" t="n">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="AV11" t="n">
-        <v>5.1</v>
+        <v>21</v>
       </c>
       <c r="AW11" t="n">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="AX11" t="n">
         <v>7.8</v>
@@ -3281,28 +3281,28 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ11" t="n">
-        <v>4.9</v>
+        <v>21</v>
       </c>
       <c r="BA11" t="n">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="BB11" t="n">
-        <v>4.5</v>
+        <v>11.5</v>
       </c>
       <c r="BC11" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BD11" t="n">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="BE11" t="n">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="BF11" t="n">
         <v>9.6</v>
       </c>
       <c r="BG11" t="n">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="BH11" t="n">
         <v>3.3</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-14 11:49:16</t>
+          <t>2026-07-14 13:57:32</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-15.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-15.xlsx
@@ -857,16 +857,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="G2" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="H2" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="I2" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="J2" t="n">
         <v>3.1</v>
@@ -881,13 +881,13 @@
         <v>1.09</v>
       </c>
       <c r="N2" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="O2" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P2" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="Q2" t="n">
         <v>2.22</v>
@@ -896,7 +896,7 @@
         <v>1.25</v>
       </c>
       <c r="S2" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T2" t="n">
         <v>1.89</v>
@@ -905,10 +905,10 @@
         <v>1.92</v>
       </c>
       <c r="V2" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W2" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="X2" t="n">
         <v>11.5</v>
@@ -923,31 +923,31 @@
         <v>60</v>
       </c>
       <c r="AB2" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC2" t="n">
         <v>7.8</v>
       </c>
       <c r="AD2" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AE2" t="n">
         <v>44</v>
       </c>
       <c r="AF2" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AG2" t="n">
         <v>13</v>
       </c>
       <c r="AH2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI2" t="n">
         <v>70</v>
       </c>
       <c r="AJ2" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AK2" t="n">
         <v>36</v>
@@ -959,7 +959,7 @@
         <v>140</v>
       </c>
       <c r="AN2" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AO2" t="n">
         <v>46</v>
@@ -974,7 +974,7 @@
         <v>17.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>6.6</v>
+        <v>8.6</v>
       </c>
       <c r="AT2" t="n">
         <v>7.6</v>
@@ -1001,7 +1001,7 @@
         <v>42</v>
       </c>
       <c r="BB2" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="BC2" t="n">
         <v>26</v>
@@ -1010,10 +1010,10 @@
         <v>38</v>
       </c>
       <c r="BE2" t="n">
-        <v>7</v>
+        <v>9.4</v>
       </c>
       <c r="BF2" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="BG2" t="n">
         <v>32</v>
@@ -1022,7 +1022,7 @@
         <v>3.15</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="BJ2" t="n">
         <v>10.5</v>
@@ -1034,43 +1034,43 @@
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN2" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BO2" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BP2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BQ2" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT2" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BU2" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BV2" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BX2" t="n">
         <v>55</v>
       </c>
       <c r="BY2" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-14 13:57:32</t>
+          <t>2026-07-14 16:06:04</t>
         </is>
       </c>
     </row>
@@ -1135,13 +1135,13 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="O3" t="n">
         <v>1.24</v>
       </c>
       <c r="P3" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Q3" t="n">
         <v>1.23</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-14 13:57:32</t>
+          <t>2026-07-14 16:06:04</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
         <v>1.44</v>
       </c>
       <c r="G4" t="n">
-        <v>1000</v>
+        <v>2.2</v>
       </c>
       <c r="H4" t="n">
         <v>1.04</v>
@@ -1380,7 +1380,7 @@
         <v>3.25</v>
       </c>
       <c r="K4" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="L4" t="n">
         <v>1.01</v>
@@ -1389,22 +1389,22 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="O4" t="n">
         <v>1.2</v>
       </c>
       <c r="P4" t="n">
-        <v>2.22</v>
+        <v>2.14</v>
       </c>
       <c r="Q4" t="n">
         <v>1.27</v>
       </c>
       <c r="R4" t="n">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="S4" t="n">
-        <v>1.6</v>
+        <v>2.16</v>
       </c>
       <c r="T4" t="n">
         <v>1.01</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-14 13:57:32</t>
+          <t>2026-07-14 16:06:04</t>
         </is>
       </c>
     </row>
@@ -1658,13 +1658,13 @@
         <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="T5" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="U5" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="V5" t="n">
         <v>1.37</v>
@@ -1673,7 +1673,7 @@
         <v>1.58</v>
       </c>
       <c r="X5" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="Y5" t="n">
         <v>11</v>
@@ -1736,7 +1736,7 @@
         <v>17.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AT5" t="n">
         <v>6.4</v>
@@ -1748,7 +1748,7 @@
         <v>12.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AX5" t="n">
         <v>11.5</v>
@@ -1760,25 +1760,25 @@
         <v>19</v>
       </c>
       <c r="BA5" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BB5" t="n">
         <v>5</v>
       </c>
-      <c r="BB5" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BC5" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BF5" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BG5" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BH5" t="n">
         <v>2.74</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-14 13:57:32</t>
+          <t>2026-07-14 16:06:04</t>
         </is>
       </c>
     </row>
@@ -1873,22 +1873,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.46</v>
+        <v>2.76</v>
       </c>
       <c r="G6" t="n">
-        <v>2.72</v>
+        <v>2.92</v>
       </c>
       <c r="H6" t="n">
-        <v>2.94</v>
+        <v>2.78</v>
       </c>
       <c r="I6" t="n">
-        <v>3.3</v>
+        <v>2.92</v>
       </c>
       <c r="J6" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K6" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="L6" t="n">
         <v>1.41</v>
@@ -1897,206 +1897,206 @@
         <v>1.08</v>
       </c>
       <c r="N6" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O6" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="P6" t="n">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="Q6" t="n">
         <v>2.06</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S6" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="T6" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="U6" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="V6" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="W6" t="n">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="X6" t="n">
         <v>14.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Z6" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="AA6" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AB6" t="n">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="AC6" t="n">
         <v>8</v>
       </c>
       <c r="AD6" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AF6" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="AG6" t="n">
         <v>14.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AI6" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AJ6" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AK6" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="AL6" t="n">
         <v>50</v>
       </c>
       <c r="AM6" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN6" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AO6" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AP6" t="n">
         <v>10.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AR6" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="AT6" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AU6" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AV6" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AW6" t="n">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="AX6" t="n">
         <v>13.5</v>
       </c>
       <c r="AY6" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>5.9</v>
+        <v>5.4</v>
       </c>
       <c r="BB6" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BE6" t="n">
         <v>5.7</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>6.2</v>
       </c>
       <c r="BF6" t="n">
         <v>21</v>
       </c>
       <c r="BG6" t="n">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="BH6" t="n">
         <v>3.4</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="BJ6" t="n">
         <v>10</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BN6" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BO6" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BP6" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BQ6" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BR6" t="n">
         <v>36</v>
       </c>
       <c r="BS6" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT6" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BU6" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="BV6" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BW6" t="n">
         <v>7.4</v>
       </c>
       <c r="BX6" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BY6" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BZ6" t="n">
         <v>32</v>
       </c>
       <c r="CA6" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-14 13:57:32</t>
+          <t>2026-07-14 16:06:04</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
         <v>2.42</v>
       </c>
       <c r="I7" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="J7" t="n">
         <v>3.4</v>
@@ -2175,7 +2175,7 @@
         <v>2.2</v>
       </c>
       <c r="V7" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="W7" t="n">
         <v>1.46</v>
@@ -2289,10 +2289,10 @@
         <v>15</v>
       </c>
       <c r="BH7" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="BJ7" t="n">
         <v>9.4</v>
@@ -2316,7 +2316,7 @@
         <v>23</v>
       </c>
       <c r="BQ7" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BR7" t="n">
         <v>34</v>
@@ -2325,7 +2325,7 @@
         <v>24</v>
       </c>
       <c r="BT7" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BU7" t="n">
         <v>4.4</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-14 13:57:32</t>
+          <t>2026-07-14 16:06:04</t>
         </is>
       </c>
     </row>
@@ -2390,10 +2390,10 @@
         <v>5.1</v>
       </c>
       <c r="I8" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="J8" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="K8" t="n">
         <v>4.3</v>
@@ -2411,7 +2411,7 @@
         <v>1.29</v>
       </c>
       <c r="P8" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q8" t="n">
         <v>1.84</v>
@@ -2426,7 +2426,7 @@
         <v>1.84</v>
       </c>
       <c r="U8" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="V8" t="n">
         <v>1.21</v>
@@ -2456,7 +2456,7 @@
         <v>26</v>
       </c>
       <c r="AE8" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AF8" t="n">
         <v>13.5</v>
@@ -2468,7 +2468,7 @@
         <v>25</v>
       </c>
       <c r="AI8" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AJ8" t="n">
         <v>22</v>
@@ -2486,7 +2486,7 @@
         <v>12.5</v>
       </c>
       <c r="AO8" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AP8" t="n">
         <v>12</v>
@@ -2537,7 +2537,7 @@
         <v>1.03</v>
       </c>
       <c r="BF8" t="n">
-        <v>9.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BG8" t="n">
         <v>55</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-14 13:57:32</t>
+          <t>2026-07-14 16:06:04</t>
         </is>
       </c>
     </row>
@@ -2641,16 +2641,16 @@
         <v>5.1</v>
       </c>
       <c r="H9" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="I9" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="J9" t="n">
         <v>3.8</v>
       </c>
       <c r="K9" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="L9" t="n">
         <v>1.32</v>
@@ -2659,7 +2659,7 @@
         <v>1.06</v>
       </c>
       <c r="N9" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="O9" t="n">
         <v>1.29</v>
@@ -2668,10 +2668,10 @@
         <v>1.98</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="R9" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S9" t="n">
         <v>3.15</v>
@@ -2683,7 +2683,7 @@
         <v>2.04</v>
       </c>
       <c r="V9" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="W9" t="n">
         <v>1.25</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-14 13:57:32</t>
+          <t>2026-07-14 16:06:04</t>
         </is>
       </c>
     </row>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.04</v>
+        <v>1.28</v>
       </c>
       <c r="G10" t="n">
         <v>1.35</v>
@@ -2937,10 +2937,10 @@
         <v>1.01</v>
       </c>
       <c r="V10" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="W10" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-14 13:57:32</t>
+          <t>2026-07-14 16:06:04</t>
         </is>
       </c>
     </row>
@@ -3176,13 +3176,13 @@
         <v>1.81</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R11" t="n">
         <v>1.3</v>
       </c>
       <c r="S11" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="T11" t="n">
         <v>2.1</v>
@@ -3197,7 +3197,7 @@
         <v>2.52</v>
       </c>
       <c r="X11" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Y11" t="n">
         <v>24</v>
@@ -3260,7 +3260,7 @@
         <v>4.9</v>
       </c>
       <c r="AS11" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AT11" t="n">
         <v>6.2</v>
@@ -3272,7 +3272,7 @@
         <v>21</v>
       </c>
       <c r="AW11" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AX11" t="n">
         <v>7.8</v>
@@ -3284,7 +3284,7 @@
         <v>21</v>
       </c>
       <c r="BA11" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BB11" t="n">
         <v>11.5</v>
@@ -3302,7 +3302,7 @@
         <v>9.6</v>
       </c>
       <c r="BG11" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BH11" t="n">
         <v>3.3</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-14 13:57:32</t>
+          <t>2026-07-14 16:06:04</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-15.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-15.xlsx
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="G2" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="H2" t="n">
         <v>3.05</v>
@@ -869,49 +869,49 @@
         <v>3.4</v>
       </c>
       <c r="J2" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K2" t="n">
         <v>3.4</v>
       </c>
       <c r="L2" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="M2" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N2" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="O2" t="n">
         <v>1.41</v>
       </c>
       <c r="P2" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="Q2" t="n">
         <v>2.22</v>
       </c>
       <c r="R2" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S2" t="n">
         <v>4.3</v>
       </c>
       <c r="T2" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="U2" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="V2" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W2" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="X2" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y2" t="n">
         <v>11</v>
@@ -920,7 +920,7 @@
         <v>22</v>
       </c>
       <c r="AA2" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="AB2" t="n">
         <v>9.199999999999999</v>
@@ -932,7 +932,7 @@
         <v>15</v>
       </c>
       <c r="AE2" t="n">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="AF2" t="n">
         <v>17</v>
@@ -947,22 +947,22 @@
         <v>70</v>
       </c>
       <c r="AJ2" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AK2" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL2" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AM2" t="n">
         <v>140</v>
       </c>
       <c r="AN2" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AO2" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="AP2" t="n">
         <v>9.199999999999999</v>
@@ -974,7 +974,7 @@
         <v>17.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT2" t="n">
         <v>7.6</v>
@@ -986,10 +986,10 @@
         <v>12</v>
       </c>
       <c r="AW2" t="n">
-        <v>30</v>
+        <v>8.4</v>
       </c>
       <c r="AX2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AY2" t="n">
         <v>10.5</v>
@@ -1001,25 +1001,25 @@
         <v>42</v>
       </c>
       <c r="BB2" t="n">
-        <v>28</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC2" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="BD2" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BE2" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BF2" t="n">
-        <v>23</v>
+        <v>7.8</v>
       </c>
       <c r="BG2" t="n">
-        <v>32</v>
+        <v>8.4</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BI2" t="n">
         <v>2.56</v>
@@ -1037,19 +1037,19 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BN2" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BO2" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BP2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BQ2" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BR2" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS2" t="n">
         <v>8.199999999999999</v>
@@ -1058,10 +1058,10 @@
         <v>6.4</v>
       </c>
       <c r="BU2" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BV2" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BW2" t="n">
         <v>7.6</v>
@@ -1073,14 +1073,14 @@
         <v>8.4</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="CA2" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-14 16:06:04</t>
+          <t>2026-07-14 18:13:51</t>
         </is>
       </c>
     </row>
@@ -1114,16 +1114,16 @@
         <v>1.04</v>
       </c>
       <c r="G3" t="n">
-        <v>1000</v>
+        <v>1.76</v>
       </c>
       <c r="H3" t="n">
-        <v>1.04</v>
+        <v>2.76</v>
       </c>
       <c r="I3" t="n">
         <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K3" t="n">
         <v>1000</v>
@@ -1135,13 +1135,13 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="O3" t="n">
         <v>1.24</v>
       </c>
       <c r="P3" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Q3" t="n">
         <v>1.23</v>
@@ -1150,7 +1150,7 @@
         <v>1.18</v>
       </c>
       <c r="S3" t="n">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="T3" t="n">
         <v>1.01</v>
@@ -1162,7 +1162,7 @@
         <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-14 16:06:04</t>
+          <t>2026-07-14 18:13:51</t>
         </is>
       </c>
     </row>
@@ -1365,175 +1365,175 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.44</v>
+        <v>1.68</v>
       </c>
       <c r="G4" t="n">
-        <v>2.2</v>
+        <v>1.87</v>
       </c>
       <c r="H4" t="n">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="I4" t="n">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="J4" t="n">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="K4" t="n">
-        <v>4.5</v>
+        <v>950</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="M4" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N4" t="n">
-        <v>2.42</v>
+        <v>1.01</v>
       </c>
       <c r="O4" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="P4" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="W4" t="n">
         <v>2.14</v>
       </c>
-      <c r="Q4" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.83</v>
-      </c>
       <c r="X4" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Y4" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Z4" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AA4" t="n">
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC4" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE4" t="n">
         <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH4" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AK4" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AL4" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AM4" t="n">
         <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AO4" t="n">
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BH4" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BI4" t="n">
         <v>1.01</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK4" t="n">
         <v>1.01</v>
@@ -1545,50 +1545,50 @@
         <v>1.01</v>
       </c>
       <c r="BN4" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="BP4" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BQ4" t="n">
         <v>1.01</v>
       </c>
       <c r="BR4" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BS4" t="n">
         <v>1.01</v>
       </c>
       <c r="BT4" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU4" t="n">
         <v>1.01</v>
       </c>
       <c r="BV4" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BW4" t="n">
         <v>1.01</v>
       </c>
       <c r="BX4" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BY4" t="n">
         <v>1.01</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="CA4" t="n">
         <v>1.01</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-14 16:06:04</t>
+          <t>2026-07-14 18:13:51</t>
         </is>
       </c>
     </row>
@@ -1661,10 +1661,10 @@
         <v>5.7</v>
       </c>
       <c r="T5" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="U5" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="V5" t="n">
         <v>1.37</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-14 16:06:04</t>
+          <t>2026-07-14 18:13:51</t>
         </is>
       </c>
     </row>
@@ -1873,22 +1873,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="G6" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="H6" t="n">
-        <v>2.78</v>
+        <v>2.72</v>
       </c>
       <c r="I6" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="J6" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="K6" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L6" t="n">
         <v>1.41</v>
@@ -1900,31 +1900,31 @@
         <v>3.35</v>
       </c>
       <c r="O6" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="P6" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="R6" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S6" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="T6" t="n">
         <v>1.77</v>
       </c>
       <c r="U6" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V6" t="n">
         <v>1.52</v>
       </c>
       <c r="W6" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="X6" t="n">
         <v>14.5</v>
@@ -1951,7 +1951,7 @@
         <v>38</v>
       </c>
       <c r="AF6" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AG6" t="n">
         <v>14.5</v>
@@ -1966,7 +1966,7 @@
         <v>55</v>
       </c>
       <c r="AK6" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AL6" t="n">
         <v>50</v>
@@ -1975,7 +1975,7 @@
         <v>110</v>
       </c>
       <c r="AN6" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AO6" t="n">
         <v>34</v>
@@ -1990,22 +1990,22 @@
         <v>15.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="AT6" t="n">
         <v>9</v>
       </c>
       <c r="AU6" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV6" t="n">
         <v>11</v>
       </c>
       <c r="AW6" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AY6" t="n">
         <v>11.5</v>
@@ -2014,25 +2014,25 @@
         <v>14.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BB6" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BC6" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BE6" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BF6" t="n">
         <v>21</v>
       </c>
       <c r="BG6" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BH6" t="n">
         <v>3.4</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-14 16:06:04</t>
+          <t>2026-07-14 18:13:51</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
         <v>2.42</v>
       </c>
       <c r="I7" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="J7" t="n">
         <v>3.4</v>
@@ -2154,7 +2154,7 @@
         <v>3.9</v>
       </c>
       <c r="O7" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P7" t="n">
         <v>1.99</v>
@@ -2166,16 +2166,16 @@
         <v>1.39</v>
       </c>
       <c r="S7" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="T7" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="U7" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V7" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="W7" t="n">
         <v>1.46</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-14 16:06:04</t>
+          <t>2026-07-14 18:13:51</t>
         </is>
       </c>
     </row>
@@ -2405,13 +2405,13 @@
         <v>1.06</v>
       </c>
       <c r="N8" t="n">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="O8" t="n">
         <v>1.29</v>
       </c>
       <c r="P8" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q8" t="n">
         <v>1.84</v>
@@ -2426,7 +2426,7 @@
         <v>1.84</v>
       </c>
       <c r="U8" t="n">
-        <v>2.02</v>
+        <v>1.7</v>
       </c>
       <c r="V8" t="n">
         <v>1.21</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-14 16:06:04</t>
+          <t>2026-07-14 18:13:51</t>
         </is>
       </c>
     </row>
@@ -2641,7 +2641,7 @@
         <v>5.1</v>
       </c>
       <c r="H9" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="I9" t="n">
         <v>1.93</v>
@@ -2686,7 +2686,7 @@
         <v>2.06</v>
       </c>
       <c r="W9" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="X9" t="n">
         <v>19.5</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-14 16:06:04</t>
+          <t>2026-07-14 18:13:51</t>
         </is>
       </c>
     </row>
@@ -2892,13 +2892,13 @@
         <v>1.28</v>
       </c>
       <c r="G10" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="H10" t="n">
         <v>1.04</v>
       </c>
       <c r="I10" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="J10" t="n">
         <v>6.4</v>
@@ -2910,25 +2910,25 @@
         <v>1.01</v>
       </c>
       <c r="M10" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N10" t="n">
-        <v>1.44</v>
+        <v>1.05</v>
       </c>
       <c r="O10" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="P10" t="n">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="R10" t="n">
-        <v>1.39</v>
+        <v>1.7</v>
       </c>
       <c r="S10" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="T10" t="n">
         <v>1.01</v>
@@ -2940,7 +2940,7 @@
         <v>1.07</v>
       </c>
       <c r="W10" t="n">
-        <v>2.4</v>
+        <v>4.1</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
@@ -2958,7 +2958,7 @@
         <v>1000</v>
       </c>
       <c r="AC10" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AD10" t="n">
         <v>1000</v>
@@ -2973,7 +2973,7 @@
         <v>1000</v>
       </c>
       <c r="AH10" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AI10" t="n">
         <v>1000</v>
@@ -2982,73 +2982,73 @@
         <v>1000</v>
       </c>
       <c r="AK10" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AL10" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM10" t="n">
         <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="AO10" t="n">
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.01</v>
+        <v>2.84</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="BH10" t="n">
         <v>1000</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-14 16:06:04</t>
+          <t>2026-07-14 18:13:51</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-14 16:06:04</t>
+          <t>2026-07-14 18:13:51</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-15.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-15.xlsx
@@ -860,19 +860,19 @@
         <v>2.48</v>
       </c>
       <c r="G2" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="H2" t="n">
         <v>3.05</v>
       </c>
       <c r="I2" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="J2" t="n">
         <v>3.15</v>
       </c>
       <c r="K2" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L2" t="n">
         <v>1.45</v>
@@ -881,7 +881,7 @@
         <v>1.1</v>
       </c>
       <c r="N2" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="O2" t="n">
         <v>1.41</v>
@@ -893,13 +893,13 @@
         <v>2.22</v>
       </c>
       <c r="R2" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S2" t="n">
         <v>4.3</v>
       </c>
       <c r="T2" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="U2" t="n">
         <v>1.94</v>
@@ -920,7 +920,7 @@
         <v>22</v>
       </c>
       <c r="AA2" t="n">
-        <v>85</v>
+        <v>130</v>
       </c>
       <c r="AB2" t="n">
         <v>9.199999999999999</v>
@@ -941,10 +941,10 @@
         <v>13</v>
       </c>
       <c r="AH2" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>70</v>
+        <v>130</v>
       </c>
       <c r="AJ2" t="n">
         <v>50</v>
@@ -956,13 +956,13 @@
         <v>70</v>
       </c>
       <c r="AM2" t="n">
-        <v>140</v>
+        <v>580</v>
       </c>
       <c r="AN2" t="n">
         <v>32</v>
       </c>
       <c r="AO2" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="AP2" t="n">
         <v>9.199999999999999</v>
@@ -974,7 +974,7 @@
         <v>17.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AT2" t="n">
         <v>7.6</v>
@@ -986,7 +986,7 @@
         <v>12</v>
       </c>
       <c r="AW2" t="n">
-        <v>8.4</v>
+        <v>34</v>
       </c>
       <c r="AX2" t="n">
         <v>13</v>
@@ -1001,22 +1001,22 @@
         <v>42</v>
       </c>
       <c r="BB2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BC2" t="n">
         <v>22</v>
       </c>
       <c r="BD2" t="n">
-        <v>40</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE2" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF2" t="n">
         <v>7.8</v>
       </c>
       <c r="BG2" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BH2" t="n">
         <v>3.2</v>
@@ -1061,26 +1061,26 @@
         <v>5.3</v>
       </c>
       <c r="BV2" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BW2" t="n">
         <v>7.6</v>
       </c>
       <c r="BX2" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY2" t="n">
         <v>8.4</v>
       </c>
       <c r="BZ2" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="CA2" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-14 18:13:51</t>
+          <t>2026-07-14 20:21:48</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
         <v>1.04</v>
       </c>
       <c r="G3" t="n">
-        <v>1.76</v>
+        <v>1.6</v>
       </c>
       <c r="H3" t="n">
         <v>2.76</v>
@@ -1123,7 +1123,7 @@
         <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>1.03</v>
+        <v>3.05</v>
       </c>
       <c r="K3" t="n">
         <v>1000</v>
@@ -1135,13 +1135,13 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="O3" t="n">
         <v>1.24</v>
       </c>
       <c r="P3" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="Q3" t="n">
         <v>1.23</v>
@@ -1219,52 +1219,52 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF3" t="n">
         <v>1.01</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-14 18:13:51</t>
+          <t>2026-07-14 20:21:48</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="G4" t="n">
         <v>1.87</v>
       </c>
       <c r="H4" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I4" t="n">
         <v>5.7</v>
       </c>
       <c r="J4" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K4" t="n">
-        <v>950</v>
+        <v>4.7</v>
       </c>
       <c r="L4" t="n">
         <v>1.28</v>
@@ -1389,28 +1389,28 @@
         <v>1.05</v>
       </c>
       <c r="N4" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="O4" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P4" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="R4" t="n">
         <v>1.45</v>
       </c>
       <c r="S4" t="n">
-        <v>2.68</v>
+        <v>2.56</v>
       </c>
       <c r="T4" t="n">
         <v>1.68</v>
       </c>
       <c r="U4" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V4" t="n">
         <v>1.21</v>
@@ -1425,10 +1425,10 @@
         <v>22</v>
       </c>
       <c r="Z4" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AA4" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB4" t="n">
         <v>11</v>
@@ -1440,7 +1440,7 @@
         <v>22</v>
       </c>
       <c r="AE4" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AF4" t="n">
         <v>12.5</v>
@@ -1464,131 +1464,131 @@
         <v>34</v>
       </c>
       <c r="AM4" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AN4" t="n">
         <v>9.6</v>
       </c>
       <c r="AO4" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AP4" t="n">
-        <v>4.4</v>
+        <v>5.7</v>
       </c>
       <c r="AQ4" t="n">
-        <v>4.4</v>
+        <v>5.8</v>
       </c>
       <c r="AR4" t="n">
-        <v>5</v>
+        <v>6.6</v>
       </c>
       <c r="AS4" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AU4" t="n">
         <v>5.6</v>
       </c>
-      <c r="AT4" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>3.65</v>
-      </c>
       <c r="AV4" t="n">
-        <v>4.4</v>
+        <v>5.8</v>
       </c>
       <c r="AW4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AZ4" t="n">
         <v>5.6</v>
       </c>
-      <c r="AX4" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AZ4" t="n">
+      <c r="BA4" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BF4" t="n">
         <v>4.3</v>
       </c>
-      <c r="BA4" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>3.5</v>
-      </c>
       <c r="BG4" t="n">
-        <v>5.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH4" t="n">
         <v>4.2</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BJ4" t="n">
         <v>10.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BN4" t="n">
         <v>4.8</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BP4" t="n">
         <v>12</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BR4" t="n">
         <v>25</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BT4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BV4" t="n">
         <v>42</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BX4" t="n">
         <v>46</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BZ4" t="n">
         <v>18.5</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-14 18:13:51</t>
+          <t>2026-07-14 20:21:48</t>
         </is>
       </c>
     </row>
@@ -1631,10 +1631,10 @@
         <v>3.8</v>
       </c>
       <c r="J5" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="K5" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L5" t="n">
         <v>1.52</v>
@@ -1643,16 +1643,16 @@
         <v>1.12</v>
       </c>
       <c r="N5" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="O5" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="P5" t="n">
         <v>1.47</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="R5" t="n">
         <v>1.18</v>
@@ -1664,13 +1664,13 @@
         <v>2.14</v>
       </c>
       <c r="U5" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="V5" t="n">
         <v>1.37</v>
       </c>
       <c r="W5" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="X5" t="n">
         <v>8.4</v>
@@ -1679,55 +1679,55 @@
         <v>11</v>
       </c>
       <c r="Z5" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AA5" t="n">
-        <v>90</v>
+        <v>900</v>
       </c>
       <c r="AB5" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AC5" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>70</v>
+        <v>290</v>
       </c>
       <c r="AF5" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AG5" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AH5" t="n">
         <v>29</v>
       </c>
       <c r="AI5" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AJ5" t="n">
-        <v>50</v>
+        <v>220</v>
       </c>
       <c r="AK5" t="n">
-        <v>46</v>
+        <v>95</v>
       </c>
       <c r="AL5" t="n">
-        <v>80</v>
+        <v>460</v>
       </c>
       <c r="AM5" t="n">
-        <v>240</v>
+        <v>500</v>
       </c>
       <c r="AN5" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AO5" t="n">
-        <v>95</v>
+        <v>500</v>
       </c>
       <c r="AP5" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AQ5" t="n">
         <v>7.8</v>
@@ -1736,7 +1736,7 @@
         <v>17.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.2</v>
+        <v>7.4</v>
       </c>
       <c r="AT5" t="n">
         <v>6.4</v>
@@ -1748,7 +1748,7 @@
         <v>12.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>5.2</v>
+        <v>7.2</v>
       </c>
       <c r="AX5" t="n">
         <v>11.5</v>
@@ -1760,31 +1760,31 @@
         <v>19</v>
       </c>
       <c r="BA5" t="n">
-        <v>5.3</v>
+        <v>7.4</v>
       </c>
       <c r="BB5" t="n">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="BC5" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="BD5" t="n">
-        <v>5.2</v>
+        <v>7.4</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.4</v>
+        <v>7.8</v>
       </c>
       <c r="BF5" t="n">
-        <v>5.1</v>
+        <v>7.4</v>
       </c>
       <c r="BG5" t="n">
-        <v>5.3</v>
+        <v>7.4</v>
       </c>
       <c r="BH5" t="n">
         <v>2.74</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="BJ5" t="n">
         <v>12</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-14 18:13:51</t>
+          <t>2026-07-14 20:21:48</t>
         </is>
       </c>
     </row>
@@ -1873,37 +1873,37 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="G6" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="H6" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="I6" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="J6" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="K6" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="L6" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="M6" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N6" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="O6" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="P6" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="Q6" t="n">
         <v>2.04</v>
@@ -1915,61 +1915,61 @@
         <v>3.55</v>
       </c>
       <c r="T6" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="U6" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="V6" t="n">
         <v>1.52</v>
       </c>
       <c r="W6" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="X6" t="n">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="Y6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Z6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA6" t="n">
         <v>55</v>
       </c>
       <c r="AB6" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AC6" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE6" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AF6" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AG6" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AH6" t="n">
         <v>18</v>
       </c>
       <c r="AI6" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AJ6" t="n">
         <v>55</v>
       </c>
       <c r="AK6" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AL6" t="n">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="AM6" t="n">
         <v>110</v>
@@ -1981,19 +1981,19 @@
         <v>34</v>
       </c>
       <c r="AP6" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AQ6" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AR6" t="n">
         <v>15.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="AT6" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AU6" t="n">
         <v>6.4</v>
@@ -2002,7 +2002,7 @@
         <v>11</v>
       </c>
       <c r="AW6" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AX6" t="n">
         <v>15</v>
@@ -2014,37 +2014,37 @@
         <v>14.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="BB6" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="BC6" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BD6" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BE6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BF6" t="n">
         <v>21</v>
       </c>
       <c r="BG6" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="BJ6" t="n">
         <v>10</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
@@ -2065,10 +2065,10 @@
         <v>7.2</v>
       </c>
       <c r="BR6" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BS6" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BT6" t="n">
         <v>6.2</v>
@@ -2077,13 +2077,13 @@
         <v>4.7</v>
       </c>
       <c r="BV6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BW6" t="n">
         <v>7.4</v>
       </c>
       <c r="BX6" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BY6" t="n">
         <v>8.4</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-14 18:13:51</t>
+          <t>2026-07-14 20:21:48</t>
         </is>
       </c>
     </row>
@@ -2127,16 +2127,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="G7" t="n">
         <v>3.2</v>
       </c>
       <c r="H7" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="I7" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="J7" t="n">
         <v>3.4</v>
@@ -2157,7 +2157,7 @@
         <v>1.29</v>
       </c>
       <c r="P7" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="Q7" t="n">
         <v>1.84</v>
@@ -2175,7 +2175,7 @@
         <v>2.22</v>
       </c>
       <c r="V7" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="W7" t="n">
         <v>1.46</v>
@@ -2184,7 +2184,7 @@
         <v>18</v>
       </c>
       <c r="Y7" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z7" t="n">
         <v>21</v>
@@ -2232,7 +2232,7 @@
         <v>32</v>
       </c>
       <c r="AO7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AP7" t="n">
         <v>12</v>
@@ -2325,7 +2325,7 @@
         <v>24</v>
       </c>
       <c r="BT7" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BU7" t="n">
         <v>4.4</v>
@@ -2337,20 +2337,20 @@
         <v>14</v>
       </c>
       <c r="BX7" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BY7" t="n">
         <v>22</v>
       </c>
       <c r="BZ7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="CA7" t="n">
         <v>18</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-14 18:13:51</t>
+          <t>2026-07-14 20:21:48</t>
         </is>
       </c>
     </row>
@@ -2405,10 +2405,10 @@
         <v>1.06</v>
       </c>
       <c r="N8" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="O8" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P8" t="n">
         <v>2.02</v>
@@ -2420,13 +2420,13 @@
         <v>1.39</v>
       </c>
       <c r="S8" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T8" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="U8" t="n">
-        <v>1.7</v>
+        <v>2.04</v>
       </c>
       <c r="V8" t="n">
         <v>1.21</v>
@@ -2435,7 +2435,7 @@
         <v>2.26</v>
       </c>
       <c r="X8" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Y8" t="n">
         <v>23</v>
@@ -2459,7 +2459,7 @@
         <v>85</v>
       </c>
       <c r="AF8" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG8" t="n">
         <v>12.5</v>
@@ -2549,7 +2549,7 @@
         <v>2.88</v>
       </c>
       <c r="BJ8" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BK8" t="n">
         <v>7.4</v>
@@ -2570,7 +2570,7 @@
         <v>12</v>
       </c>
       <c r="BQ8" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BR8" t="n">
         <v>26</v>
@@ -2594,7 +2594,7 @@
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BZ8" t="n">
         <v>21</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-14 18:13:51</t>
+          <t>2026-07-14 20:21:48</t>
         </is>
       </c>
     </row>
@@ -2635,19 +2635,19 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="G9" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="H9" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="I9" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="J9" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K9" t="n">
         <v>4.3</v>
@@ -2665,10 +2665,10 @@
         <v>1.29</v>
       </c>
       <c r="P9" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="R9" t="n">
         <v>1.38</v>
@@ -2677,34 +2677,34 @@
         <v>3.15</v>
       </c>
       <c r="T9" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="U9" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V9" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="W9" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="X9" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Y9" t="n">
         <v>11</v>
       </c>
       <c r="Z9" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AB9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AC9" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD9" t="n">
         <v>12.5</v>
@@ -2716,7 +2716,7 @@
         <v>44</v>
       </c>
       <c r="AG9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AH9" t="n">
         <v>24</v>
@@ -2725,10 +2725,10 @@
         <v>42</v>
       </c>
       <c r="AJ9" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AK9" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AL9" t="n">
         <v>75</v>
@@ -2737,10 +2737,10 @@
         <v>130</v>
       </c>
       <c r="AN9" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AO9" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AP9" t="n">
         <v>11.5</v>
@@ -2749,7 +2749,7 @@
         <v>6.8</v>
       </c>
       <c r="AR9" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS9" t="n">
         <v>15</v>
@@ -2758,7 +2758,7 @@
         <v>12</v>
       </c>
       <c r="AU9" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV9" t="n">
         <v>7.6</v>
@@ -2794,7 +2794,7 @@
         <v>46</v>
       </c>
       <c r="BG9" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BH9" t="n">
         <v>3.6</v>
@@ -2821,44 +2821,44 @@
         <v>6</v>
       </c>
       <c r="BP9" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BQ9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BR9" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BT9" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BU9" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BV9" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BW9" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BX9" t="n">
         <v>28</v>
       </c>
       <c r="BY9" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BZ9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="CA9" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-14 18:13:51</t>
+          <t>2026-07-14 20:21:48</t>
         </is>
       </c>
     </row>
@@ -2892,49 +2892,49 @@
         <v>1.28</v>
       </c>
       <c r="G10" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="H10" t="n">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="I10" t="n">
         <v>16.5</v>
       </c>
       <c r="J10" t="n">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="K10" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="L10" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="M10" t="n">
         <v>1.02</v>
       </c>
       <c r="N10" t="n">
-        <v>1.05</v>
+        <v>3.45</v>
       </c>
       <c r="O10" t="n">
         <v>1.13</v>
       </c>
       <c r="P10" t="n">
-        <v>1.7</v>
+        <v>2.84</v>
       </c>
       <c r="Q10" t="n">
         <v>1.38</v>
       </c>
       <c r="R10" t="n">
-        <v>1.7</v>
+        <v>1.84</v>
       </c>
       <c r="S10" t="n">
-        <v>1.38</v>
+        <v>1.86</v>
       </c>
       <c r="T10" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="U10" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="V10" t="n">
         <v>1.07</v>
@@ -2943,121 +2943,121 @@
         <v>4.1</v>
       </c>
       <c r="X10" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="Y10" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="Z10" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AA10" t="n">
-        <v>1000</v>
+        <v>510</v>
       </c>
       <c r="AB10" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AD10" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AE10" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AF10" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AG10" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH10" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AI10" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AK10" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AL10" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AM10" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN10" t="n">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="AO10" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.7</v>
+        <v>5.9</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.7</v>
+        <v>6.2</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.7</v>
+        <v>6.4</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.7</v>
+        <v>6.6</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.7</v>
+        <v>4.7</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.57</v>
+        <v>4.9</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.7</v>
+        <v>6</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.7</v>
+        <v>6.6</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.7</v>
+        <v>4.3</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.7</v>
+        <v>4.6</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.62</v>
+        <v>5.6</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.7</v>
+        <v>6.4</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.7</v>
+        <v>4.4</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.54</v>
+        <v>4.6</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.63</v>
+        <v>5.7</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.7</v>
+        <v>6.4</v>
       </c>
       <c r="BF10" t="n">
         <v>2.84</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.7</v>
+        <v>6.6</v>
       </c>
       <c r="BH10" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BI10" t="n">
         <v>1.01</v>
       </c>
       <c r="BJ10" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK10" t="n">
         <v>1.01</v>
@@ -3069,25 +3069,25 @@
         <v>1.01</v>
       </c>
       <c r="BN10" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BO10" t="n">
         <v>1.01</v>
       </c>
       <c r="BP10" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BQ10" t="n">
         <v>1.01</v>
       </c>
       <c r="BR10" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BS10" t="n">
         <v>1.01</v>
       </c>
       <c r="BT10" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BU10" t="n">
         <v>1.01</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-14 18:13:51</t>
+          <t>2026-07-14 20:21:48</t>
         </is>
       </c>
     </row>
@@ -3146,7 +3146,7 @@
         <v>1.57</v>
       </c>
       <c r="G11" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="H11" t="n">
         <v>6.8</v>
@@ -3176,7 +3176,7 @@
         <v>1.81</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="R11" t="n">
         <v>1.3</v>
@@ -3194,7 +3194,7 @@
         <v>1.14</v>
       </c>
       <c r="W11" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="X11" t="n">
         <v>15</v>
@@ -3221,7 +3221,7 @@
         <v>150</v>
       </c>
       <c r="AF11" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AG11" t="n">
         <v>10.5</v>
@@ -3233,7 +3233,7 @@
         <v>140</v>
       </c>
       <c r="AJ11" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AK11" t="n">
         <v>22</v>
@@ -3257,10 +3257,10 @@
         <v>17</v>
       </c>
       <c r="AR11" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="AS11" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="AT11" t="n">
         <v>6.2</v>
@@ -3272,7 +3272,7 @@
         <v>21</v>
       </c>
       <c r="AW11" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="AX11" t="n">
         <v>7.8</v>
@@ -3284,7 +3284,7 @@
         <v>21</v>
       </c>
       <c r="BA11" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BB11" t="n">
         <v>11.5</v>
@@ -3293,16 +3293,16 @@
         <v>14</v>
       </c>
       <c r="BD11" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BE11" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BF11" t="n">
         <v>9.6</v>
       </c>
       <c r="BG11" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BH11" t="n">
         <v>3.3</v>
@@ -3311,7 +3311,7 @@
         <v>2.98</v>
       </c>
       <c r="BJ11" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BK11" t="n">
         <v>6.6</v>
@@ -3320,7 +3320,7 @@
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BN11" t="n">
         <v>4</v>
@@ -3332,41 +3332,41 @@
         <v>11</v>
       </c>
       <c r="BQ11" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT11" t="n">
         <v>10.5</v>
       </c>
       <c r="BU11" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BZ11" t="n">
         <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-14 18:13:51</t>
+          <t>2026-07-14 20:21:48</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-15.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-15.xlsx
@@ -857,19 +857,19 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="G2" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="H2" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I2" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="J2" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K2" t="n">
         <v>3.45</v>
@@ -878,10 +878,10 @@
         <v>1.45</v>
       </c>
       <c r="M2" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N2" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="O2" t="n">
         <v>1.41</v>
@@ -893,25 +893,25 @@
         <v>2.22</v>
       </c>
       <c r="R2" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S2" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="T2" t="n">
         <v>1.87</v>
       </c>
       <c r="U2" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="V2" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W2" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="X2" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Y2" t="n">
         <v>11</v>
@@ -974,7 +974,7 @@
         <v>17.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AT2" t="n">
         <v>7.6</v>
@@ -1001,22 +1001,22 @@
         <v>42</v>
       </c>
       <c r="BB2" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC2" t="n">
         <v>22</v>
       </c>
       <c r="BD2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BE2" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BF2" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BG2" t="n">
-        <v>8.6</v>
+        <v>36</v>
       </c>
       <c r="BH2" t="n">
         <v>3.2</v>
@@ -1073,14 +1073,14 @@
         <v>8.4</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="CA2" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-14 20:21:48</t>
+          <t>2026-07-14 22:29:28</t>
         </is>
       </c>
     </row>
@@ -1111,166 +1111,166 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.04</v>
+        <v>1.25</v>
       </c>
       <c r="G3" t="n">
-        <v>1.6</v>
+        <v>1.34</v>
       </c>
       <c r="H3" t="n">
-        <v>2.76</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="J3" t="n">
-        <v>3.05</v>
+        <v>5</v>
       </c>
       <c r="K3" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="L3" t="n">
         <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N3" t="n">
-        <v>1.24</v>
+        <v>1.02</v>
       </c>
       <c r="O3" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P3" t="n">
-        <v>1.25</v>
+        <v>1.92</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.23</v>
+        <v>1.69</v>
       </c>
       <c r="R3" t="n">
-        <v>1.18</v>
+        <v>1.39</v>
       </c>
       <c r="S3" t="n">
-        <v>1.01</v>
+        <v>2.8</v>
       </c>
       <c r="T3" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="U3" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="V3" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W3" t="n">
-        <v>2.3</v>
+        <v>3.85</v>
       </c>
       <c r="X3" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y3" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="Z3" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AA3" t="n">
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AC3" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AD3" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AE3" t="n">
-        <v>1000</v>
+        <v>410</v>
       </c>
       <c r="AF3" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AG3" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH3" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AI3" t="n">
-        <v>1000</v>
+        <v>310</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AK3" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AL3" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM3" t="n">
-        <v>1000</v>
+        <v>340</v>
       </c>
       <c r="AN3" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="AO3" t="n">
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BH3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-14 20:21:48</t>
+          <t>2026-07-14 22:29:28</t>
         </is>
       </c>
     </row>
@@ -1365,10 +1365,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="G4" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="H4" t="n">
         <v>4.3</v>
@@ -1380,10 +1380,10 @@
         <v>3.95</v>
       </c>
       <c r="K4" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="L4" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="M4" t="n">
         <v>1.05</v>
@@ -1395,7 +1395,7 @@
         <v>1.23</v>
       </c>
       <c r="P4" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="Q4" t="n">
         <v>1.64</v>
@@ -1404,19 +1404,19 @@
         <v>1.45</v>
       </c>
       <c r="S4" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="T4" t="n">
         <v>1.68</v>
       </c>
       <c r="U4" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="V4" t="n">
         <v>1.21</v>
       </c>
       <c r="W4" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="X4" t="n">
         <v>21</v>
@@ -1440,7 +1440,7 @@
         <v>22</v>
       </c>
       <c r="AE4" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AF4" t="n">
         <v>12.5</v>
@@ -1521,16 +1521,16 @@
         <v>7.2</v>
       </c>
       <c r="BF4" t="n">
-        <v>4.3</v>
+        <v>5.6</v>
       </c>
       <c r="BG4" t="n">
-        <v>9.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="BH4" t="n">
         <v>4.2</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.15</v>
+        <v>2.8</v>
       </c>
       <c r="BJ4" t="n">
         <v>10.5</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-14 20:21:48</t>
+          <t>2026-07-14 22:29:28</t>
         </is>
       </c>
     </row>
@@ -1655,7 +1655,7 @@
         <v>2.74</v>
       </c>
       <c r="R5" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="S5" t="n">
         <v>5.7</v>
@@ -1820,7 +1820,7 @@
         <v>6.8</v>
       </c>
       <c r="BU5" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-14 20:21:48</t>
+          <t>2026-07-14 22:29:28</t>
         </is>
       </c>
     </row>
@@ -1873,19 +1873,19 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="G6" t="n">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="H6" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="I6" t="n">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="J6" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K6" t="n">
         <v>3.45</v>
@@ -1921,10 +1921,10 @@
         <v>2.04</v>
       </c>
       <c r="V6" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="W6" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="X6" t="n">
         <v>12</v>
@@ -1933,19 +1933,19 @@
         <v>11</v>
       </c>
       <c r="Z6" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AB6" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC6" t="n">
         <v>7.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE6" t="n">
         <v>36</v>
@@ -1960,19 +1960,19 @@
         <v>18</v>
       </c>
       <c r="AI6" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AJ6" t="n">
         <v>55</v>
       </c>
       <c r="AK6" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AL6" t="n">
         <v>120</v>
       </c>
       <c r="AM6" t="n">
-        <v>110</v>
+        <v>580</v>
       </c>
       <c r="AN6" t="n">
         <v>32</v>
@@ -1984,13 +1984,13 @@
         <v>10</v>
       </c>
       <c r="AQ6" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR6" t="n">
         <v>15.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AT6" t="n">
         <v>9.4</v>
@@ -2002,7 +2002,7 @@
         <v>11</v>
       </c>
       <c r="AW6" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AX6" t="n">
         <v>15</v>
@@ -2011,28 +2011,28 @@
         <v>11.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA6" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BB6" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BC6" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BD6" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BE6" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BF6" t="n">
         <v>21</v>
       </c>
       <c r="BG6" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BH6" t="n">
         <v>3.35</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-14 20:21:48</t>
+          <t>2026-07-14 22:29:28</t>
         </is>
       </c>
     </row>
@@ -2136,10 +2136,10 @@
         <v>2.44</v>
       </c>
       <c r="I7" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="J7" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K7" t="n">
         <v>3.85</v>
@@ -2184,16 +2184,16 @@
         <v>18</v>
       </c>
       <c r="Y7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Z7" t="n">
         <v>21</v>
       </c>
       <c r="AA7" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AB7" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AC7" t="n">
         <v>9.6</v>
@@ -2217,10 +2217,10 @@
         <v>44</v>
       </c>
       <c r="AJ7" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AK7" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AL7" t="n">
         <v>48</v>
@@ -2232,7 +2232,7 @@
         <v>32</v>
       </c>
       <c r="AO7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP7" t="n">
         <v>12</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-14 20:21:48</t>
+          <t>2026-07-14 22:29:28</t>
         </is>
       </c>
     </row>
@@ -2384,7 +2384,7 @@
         <v>1.71</v>
       </c>
       <c r="G8" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="H8" t="n">
         <v>5.1</v>
@@ -2393,46 +2393,46 @@
         <v>5.8</v>
       </c>
       <c r="J8" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="K8" t="n">
         <v>4.3</v>
       </c>
       <c r="L8" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="M8" t="n">
         <v>1.06</v>
       </c>
       <c r="N8" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="O8" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="P8" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="R8" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="S8" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="T8" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="U8" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V8" t="n">
         <v>1.21</v>
       </c>
       <c r="W8" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="X8" t="n">
         <v>19.5</v>
@@ -2477,7 +2477,7 @@
         <v>22</v>
       </c>
       <c r="AL8" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM8" t="n">
         <v>130</v>
@@ -2543,10 +2543,10 @@
         <v>55</v>
       </c>
       <c r="BH8" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.88</v>
+        <v>3.35</v>
       </c>
       <c r="BJ8" t="n">
         <v>10</v>
@@ -2567,16 +2567,16 @@
         <v>3.4</v>
       </c>
       <c r="BP8" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BQ8" t="n">
         <v>8.4</v>
       </c>
       <c r="BR8" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BS8" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BT8" t="n">
         <v>8.800000000000001</v>
@@ -2597,14 +2597,14 @@
         <v>34</v>
       </c>
       <c r="BZ8" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="CA8" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-14 20:21:48</t>
+          <t>2026-07-14 22:29:28</t>
         </is>
       </c>
     </row>
@@ -2638,16 +2638,16 @@
         <v>4.2</v>
       </c>
       <c r="G9" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H9" t="n">
         <v>1.85</v>
       </c>
       <c r="I9" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="J9" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K9" t="n">
         <v>4.3</v>
@@ -2662,13 +2662,13 @@
         <v>3.75</v>
       </c>
       <c r="O9" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P9" t="n">
         <v>1.99</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="R9" t="n">
         <v>1.38</v>
@@ -2683,7 +2683,7 @@
         <v>2.06</v>
       </c>
       <c r="V9" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="W9" t="n">
         <v>1.25</v>
@@ -2719,7 +2719,7 @@
         <v>22</v>
       </c>
       <c r="AH9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI9" t="n">
         <v>42</v>
@@ -2803,7 +2803,7 @@
         <v>2.8</v>
       </c>
       <c r="BJ9" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BK9" t="n">
         <v>7.2</v>
@@ -2815,7 +2815,7 @@
         <v>1.01</v>
       </c>
       <c r="BN9" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BO9" t="n">
         <v>6</v>
@@ -2851,14 +2851,14 @@
         <v>19.5</v>
       </c>
       <c r="BZ9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="CA9" t="n">
         <v>16.5</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-14 20:21:48</t>
+          <t>2026-07-14 22:29:28</t>
         </is>
       </c>
     </row>
@@ -2889,19 +2889,19 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="G10" t="n">
         <v>1.3</v>
       </c>
       <c r="H10" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="I10" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="J10" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="K10" t="n">
         <v>8</v>
@@ -2928,16 +2928,16 @@
         <v>1.84</v>
       </c>
       <c r="S10" t="n">
-        <v>1.86</v>
+        <v>1.96</v>
       </c>
       <c r="T10" t="n">
         <v>1.86</v>
       </c>
       <c r="U10" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="V10" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W10" t="n">
         <v>4.1</v>
@@ -2991,118 +2991,118 @@
         <v>140</v>
       </c>
       <c r="AN10" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="AO10" t="n">
         <v>200</v>
       </c>
       <c r="AP10" t="n">
-        <v>5.9</v>
+        <v>5.2</v>
       </c>
       <c r="AQ10" t="n">
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
       <c r="AR10" t="n">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="AS10" t="n">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="AT10" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="AU10" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="AV10" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="AW10" t="n">
-        <v>6.6</v>
+        <v>5.7</v>
       </c>
       <c r="AX10" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="AY10" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="AZ10" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="BA10" t="n">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="BB10" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="BD10" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE10" t="n">
         <v>5.7</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>6.4</v>
       </c>
       <c r="BF10" t="n">
         <v>2.84</v>
       </c>
       <c r="BG10" t="n">
-        <v>6.6</v>
+        <v>5.7</v>
       </c>
       <c r="BH10" t="n">
         <v>5.6</v>
       </c>
       <c r="BI10" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BJ10" t="n">
         <v>12.5</v>
       </c>
       <c r="BK10" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN10" t="n">
         <v>4.3</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="BP10" t="n">
         <v>7</v>
       </c>
       <c r="BQ10" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BR10" t="n">
         <v>20</v>
       </c>
       <c r="BS10" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BT10" t="n">
         <v>16</v>
       </c>
       <c r="BU10" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-14 20:21:48</t>
+          <t>2026-07-14 22:29:28</t>
         </is>
       </c>
     </row>
@@ -3146,7 +3146,7 @@
         <v>1.57</v>
       </c>
       <c r="G11" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="H11" t="n">
         <v>6.8</v>
@@ -3179,7 +3179,7 @@
         <v>2.12</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S11" t="n">
         <v>3.8</v>
@@ -3188,7 +3188,7 @@
         <v>2.1</v>
       </c>
       <c r="U11" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="V11" t="n">
         <v>1.14</v>
@@ -3221,7 +3221,7 @@
         <v>150</v>
       </c>
       <c r="AF11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG11" t="n">
         <v>10.5</v>
@@ -3257,10 +3257,10 @@
         <v>17</v>
       </c>
       <c r="AR11" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AS11" t="n">
         <v>5.4</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>5.7</v>
       </c>
       <c r="AT11" t="n">
         <v>6.2</v>
@@ -3272,7 +3272,7 @@
         <v>21</v>
       </c>
       <c r="AW11" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="AX11" t="n">
         <v>7.8</v>
@@ -3284,7 +3284,7 @@
         <v>21</v>
       </c>
       <c r="BA11" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="BB11" t="n">
         <v>11.5</v>
@@ -3293,25 +3293,25 @@
         <v>14</v>
       </c>
       <c r="BD11" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE11" t="n">
         <v>5.3</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>5.7</v>
       </c>
       <c r="BF11" t="n">
         <v>9.6</v>
       </c>
       <c r="BG11" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="BH11" t="n">
         <v>3.3</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="BJ11" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK11" t="n">
         <v>6.6</v>
@@ -3320,10 +3320,10 @@
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BN11" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BO11" t="n">
         <v>3.55</v>
@@ -3332,41 +3332,41 @@
         <v>11</v>
       </c>
       <c r="BQ11" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BT11" t="n">
         <v>10.5</v>
       </c>
       <c r="BU11" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BZ11" t="n">
         <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-14 20:21:48</t>
+          <t>2026-07-14 22:29:28</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-15.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-15.xlsx
@@ -860,13 +860,13 @@
         <v>2.44</v>
       </c>
       <c r="G2" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="H2" t="n">
         <v>3.1</v>
       </c>
       <c r="I2" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="J2" t="n">
         <v>3.2</v>
@@ -875,7 +875,7 @@
         <v>3.45</v>
       </c>
       <c r="L2" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M2" t="n">
         <v>1.09</v>
@@ -905,10 +905,10 @@
         <v>1.95</v>
       </c>
       <c r="V2" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W2" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="X2" t="n">
         <v>11.5</v>
@@ -917,7 +917,7 @@
         <v>11</v>
       </c>
       <c r="Z2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AA2" t="n">
         <v>130</v>
@@ -929,7 +929,7 @@
         <v>7.8</v>
       </c>
       <c r="AD2" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE2" t="n">
         <v>60</v>
@@ -953,16 +953,16 @@
         <v>34</v>
       </c>
       <c r="AL2" t="n">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="AM2" t="n">
         <v>580</v>
       </c>
       <c r="AN2" t="n">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="AO2" t="n">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="AP2" t="n">
         <v>9.199999999999999</v>
@@ -971,10 +971,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AR2" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AS2" t="n">
-        <v>8.6</v>
+        <v>20</v>
       </c>
       <c r="AT2" t="n">
         <v>7.6</v>
@@ -1001,13 +1001,13 @@
         <v>42</v>
       </c>
       <c r="BB2" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BC2" t="n">
         <v>22</v>
       </c>
       <c r="BD2" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BE2" t="n">
         <v>9.4</v>
@@ -1019,7 +1019,7 @@
         <v>36</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BI2" t="n">
         <v>2.56</v>
@@ -1028,59 +1028,59 @@
         <v>10.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>6.8</v>
+        <v>5.7</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>21</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>14</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>32</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY2" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="BN2" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>22</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>7</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>40</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BZ2" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-14 22:29:28</t>
+          <t>2026-07-15 00:38:13</t>
         </is>
       </c>
     </row>
@@ -1135,22 +1135,22 @@
         <v>1.05</v>
       </c>
       <c r="N3" t="n">
-        <v>1.02</v>
+        <v>3.6</v>
       </c>
       <c r="O3" t="n">
         <v>1.25</v>
       </c>
       <c r="P3" t="n">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="R3" t="n">
         <v>1.39</v>
       </c>
       <c r="S3" t="n">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="T3" t="n">
         <v>2.32</v>
@@ -1162,10 +1162,10 @@
         <v>1.05</v>
       </c>
       <c r="W3" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="X3" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Y3" t="n">
         <v>44</v>
@@ -1177,7 +1177,7 @@
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AC3" t="n">
         <v>15</v>
@@ -1186,7 +1186,7 @@
         <v>65</v>
       </c>
       <c r="AE3" t="n">
-        <v>410</v>
+        <v>420</v>
       </c>
       <c r="AF3" t="n">
         <v>7.6</v>
@@ -1198,79 +1198,79 @@
         <v>44</v>
       </c>
       <c r="AI3" t="n">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="AJ3" t="n">
         <v>10</v>
       </c>
       <c r="AK3" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AL3" t="n">
         <v>60</v>
       </c>
       <c r="AM3" t="n">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="AN3" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AO3" t="n">
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AQ3" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AR3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AV3" t="n">
         <v>6.8</v>
       </c>
-      <c r="AS3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>6.4</v>
-      </c>
       <c r="AW3" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AX3" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="AY3" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AZ3" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BA3" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BB3" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BC3" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BD3" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BE3" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BF3" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="BG3" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BH3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-14 22:29:28</t>
+          <t>2026-07-15 00:38:13</t>
         </is>
       </c>
     </row>
@@ -1365,25 +1365,25 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="G4" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="H4" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="I4" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="J4" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="K4" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L4" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="M4" t="n">
         <v>1.05</v>
@@ -1398,25 +1398,25 @@
         <v>2.16</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="R4" t="n">
         <v>1.45</v>
       </c>
       <c r="S4" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="T4" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="U4" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="V4" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="W4" t="n">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="X4" t="n">
         <v>21</v>
@@ -1425,7 +1425,7 @@
         <v>22</v>
       </c>
       <c r="Z4" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AA4" t="n">
         <v>900</v>
@@ -1440,10 +1440,10 @@
         <v>22</v>
       </c>
       <c r="AE4" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AF4" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG4" t="n">
         <v>11</v>
@@ -1455,10 +1455,10 @@
         <v>65</v>
       </c>
       <c r="AJ4" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AK4" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AL4" t="n">
         <v>34</v>
@@ -1467,22 +1467,22 @@
         <v>95</v>
       </c>
       <c r="AN4" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO4" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AP4" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AQ4" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AR4" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AS4" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AT4" t="n">
         <v>5.8</v>
@@ -1491,10 +1491,10 @@
         <v>5.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AW4" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AX4" t="n">
         <v>6.2</v>
@@ -1503,28 +1503,28 @@
         <v>5.8</v>
       </c>
       <c r="AZ4" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BC4" t="n">
         <v>5.6</v>
       </c>
-      <c r="BA4" t="n">
-        <v>7</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>5.5</v>
-      </c>
       <c r="BD4" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BE4" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BF4" t="n">
-        <v>5.6</v>
+        <v>4.3</v>
       </c>
       <c r="BG4" t="n">
-        <v>7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH4" t="n">
         <v>4.2</v>
@@ -1536,7 +1536,7 @@
         <v>10.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
@@ -1545,16 +1545,16 @@
         <v>7.8</v>
       </c>
       <c r="BN4" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>3</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BQ4" t="n">
         <v>4.8</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>12</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>4.9</v>
       </c>
       <c r="BR4" t="n">
         <v>25</v>
@@ -1563,32 +1563,32 @@
         <v>6.2</v>
       </c>
       <c r="BT4" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BU4" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BV4" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="BW4" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BX4" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BY4" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BZ4" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="CA4" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-14 22:29:28</t>
+          <t>2026-07-15 00:38:13</t>
         </is>
       </c>
     </row>
@@ -1622,7 +1622,7 @@
         <v>2.5</v>
       </c>
       <c r="G5" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="H5" t="n">
         <v>3.3</v>
@@ -1667,10 +1667,10 @@
         <v>1.72</v>
       </c>
       <c r="V5" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W5" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="X5" t="n">
         <v>8.4</v>
@@ -1703,7 +1703,7 @@
         <v>14</v>
       </c>
       <c r="AH5" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AI5" t="n">
         <v>500</v>
@@ -1727,7 +1727,7 @@
         <v>500</v>
       </c>
       <c r="AP5" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AQ5" t="n">
         <v>7.8</v>
@@ -1760,10 +1760,10 @@
         <v>19</v>
       </c>
       <c r="BA5" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB5" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BC5" t="n">
         <v>16</v>
@@ -1772,16 +1772,16 @@
         <v>7.4</v>
       </c>
       <c r="BE5" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BF5" t="n">
         <v>7.4</v>
       </c>
       <c r="BG5" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH5" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="BI5" t="n">
         <v>2.24</v>
@@ -1814,35 +1814,35 @@
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT5" t="n">
         <v>6.8</v>
       </c>
       <c r="BU5" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-14 22:29:28</t>
+          <t>2026-07-15 00:38:13</t>
         </is>
       </c>
     </row>
@@ -1873,37 +1873,37 @@
         </is>
       </c>
       <c r="F6" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="H6" t="n">
         <v>2.8</v>
       </c>
-      <c r="G6" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="H6" t="n">
-        <v>2.78</v>
-      </c>
       <c r="I6" t="n">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="J6" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K6" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L6" t="n">
         <v>1.43</v>
       </c>
       <c r="M6" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N6" t="n">
         <v>3.2</v>
       </c>
       <c r="O6" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P6" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="Q6" t="n">
         <v>2.04</v>
@@ -1915,46 +1915,46 @@
         <v>3.55</v>
       </c>
       <c r="T6" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="U6" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="V6" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="W6" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="X6" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AA6" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AB6" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AD6" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AE6" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AF6" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AG6" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AH6" t="n">
         <v>18</v>
@@ -1963,19 +1963,19 @@
         <v>46</v>
       </c>
       <c r="AJ6" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AK6" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL6" t="n">
-        <v>120</v>
+        <v>42</v>
       </c>
       <c r="AM6" t="n">
         <v>580</v>
       </c>
       <c r="AN6" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AO6" t="n">
         <v>34</v>
@@ -1993,7 +1993,7 @@
         <v>7.2</v>
       </c>
       <c r="AT6" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU6" t="n">
         <v>6.4</v>
@@ -2008,7 +2008,7 @@
         <v>15</v>
       </c>
       <c r="AY6" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AZ6" t="n">
         <v>15</v>
@@ -2017,16 +2017,16 @@
         <v>7</v>
       </c>
       <c r="BB6" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BC6" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BD6" t="n">
         <v>7</v>
       </c>
       <c r="BE6" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BF6" t="n">
         <v>21</v>
@@ -2035,40 +2035,40 @@
         <v>6.6</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="BJ6" t="n">
         <v>10</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BN6" t="n">
         <v>5.8</v>
       </c>
       <c r="BO6" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BP6" t="n">
         <v>22</v>
       </c>
       <c r="BQ6" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BR6" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BS6" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BT6" t="n">
         <v>6.2</v>
@@ -2077,26 +2077,26 @@
         <v>4.7</v>
       </c>
       <c r="BV6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BW6" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BX6" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BY6" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BZ6" t="n">
         <v>32</v>
       </c>
       <c r="CA6" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-14 22:29:28</t>
+          <t>2026-07-15 00:38:13</t>
         </is>
       </c>
     </row>
@@ -2136,16 +2136,16 @@
         <v>2.44</v>
       </c>
       <c r="I7" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="J7" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="K7" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="L7" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="M7" t="n">
         <v>1.06</v>
@@ -2160,34 +2160,34 @@
         <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="R7" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="S7" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="T7" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="U7" t="n">
-        <v>2.22</v>
+        <v>2.12</v>
       </c>
       <c r="V7" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="W7" t="n">
         <v>1.46</v>
       </c>
       <c r="X7" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Y7" t="n">
         <v>12</v>
       </c>
       <c r="Z7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AA7" t="n">
         <v>38</v>
@@ -2196,7 +2196,7 @@
         <v>13.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD7" t="n">
         <v>14</v>
@@ -2232,7 +2232,7 @@
         <v>32</v>
       </c>
       <c r="AO7" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AP7" t="n">
         <v>12</v>
@@ -2289,16 +2289,16 @@
         <v>15</v>
       </c>
       <c r="BH7" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.96</v>
+        <v>2.84</v>
       </c>
       <c r="BJ7" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BK7" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
@@ -2307,22 +2307,22 @@
         <v>1.01</v>
       </c>
       <c r="BN7" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BO7" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BP7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BQ7" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BR7" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BS7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BT7" t="n">
         <v>5.7</v>
@@ -2331,26 +2331,26 @@
         <v>4.4</v>
       </c>
       <c r="BV7" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BW7" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BX7" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BY7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BZ7" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="CA7" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-14 22:29:28</t>
+          <t>2026-07-15 00:38:13</t>
         </is>
       </c>
     </row>
@@ -2546,7 +2546,7 @@
         <v>3.7</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="BJ8" t="n">
         <v>10</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-14 22:29:28</t>
+          <t>2026-07-15 00:38:13</t>
         </is>
       </c>
     </row>
@@ -2644,7 +2644,7 @@
         <v>1.85</v>
       </c>
       <c r="I9" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="J9" t="n">
         <v>3.8</v>
@@ -2665,10 +2665,10 @@
         <v>1.3</v>
       </c>
       <c r="P9" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="R9" t="n">
         <v>1.38</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-14 22:29:28</t>
+          <t>2026-07-15 00:38:13</t>
         </is>
       </c>
     </row>
@@ -2898,10 +2898,10 @@
         <v>10</v>
       </c>
       <c r="I10" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="J10" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="K10" t="n">
         <v>8</v>
@@ -2913,7 +2913,7 @@
         <v>1.02</v>
       </c>
       <c r="N10" t="n">
-        <v>3.45</v>
+        <v>1.02</v>
       </c>
       <c r="O10" t="n">
         <v>1.13</v>
@@ -2934,7 +2934,7 @@
         <v>1.86</v>
       </c>
       <c r="U10" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="V10" t="n">
         <v>1.08</v>
@@ -2955,7 +2955,7 @@
         <v>510</v>
       </c>
       <c r="AB10" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AC10" t="n">
         <v>18</v>
@@ -2991,64 +2991,64 @@
         <v>140</v>
       </c>
       <c r="AN10" t="n">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="AO10" t="n">
         <v>200</v>
       </c>
       <c r="AP10" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="AQ10" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="AR10" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="AS10" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AZ10" t="n">
         <v>5.8</v>
       </c>
-      <c r="AT10" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>5</v>
-      </c>
       <c r="BA10" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="BB10" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="BD10" t="n">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="BE10" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.84</v>
+        <v>2.4</v>
       </c>
       <c r="BG10" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="BH10" t="n">
         <v>5.6</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-14 22:29:28</t>
+          <t>2026-07-15 00:38:13</t>
         </is>
       </c>
     </row>
@@ -3149,40 +3149,40 @@
         <v>1.63</v>
       </c>
       <c r="H11" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="I11" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K11" t="n">
         <v>4.4</v>
       </c>
       <c r="L11" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="M11" t="n">
         <v>1.08</v>
       </c>
       <c r="N11" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O11" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="P11" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R11" t="n">
         <v>1.31</v>
       </c>
       <c r="S11" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="T11" t="n">
         <v>2.1</v>
@@ -3212,7 +3212,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AC11" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD11" t="n">
         <v>34</v>
@@ -3233,7 +3233,7 @@
         <v>140</v>
       </c>
       <c r="AJ11" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AK11" t="n">
         <v>22</v>
@@ -3245,7 +3245,7 @@
         <v>200</v>
       </c>
       <c r="AN11" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AO11" t="n">
         <v>230</v>
@@ -3257,10 +3257,10 @@
         <v>17</v>
       </c>
       <c r="AR11" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="AS11" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="AT11" t="n">
         <v>6.2</v>
@@ -3272,7 +3272,7 @@
         <v>21</v>
       </c>
       <c r="AW11" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="AX11" t="n">
         <v>7.8</v>
@@ -3284,7 +3284,7 @@
         <v>21</v>
       </c>
       <c r="BA11" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="BB11" t="n">
         <v>11.5</v>
@@ -3293,19 +3293,19 @@
         <v>14</v>
       </c>
       <c r="BD11" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="BE11" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="BF11" t="n">
         <v>9.6</v>
       </c>
       <c r="BG11" t="n">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="BH11" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BI11" t="n">
         <v>3</v>
@@ -3314,13 +3314,13 @@
         <v>11.5</v>
       </c>
       <c r="BK11" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BN11" t="n">
         <v>3.95</v>
@@ -3332,41 +3332,41 @@
         <v>11</v>
       </c>
       <c r="BQ11" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BT11" t="n">
         <v>10.5</v>
       </c>
       <c r="BU11" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BZ11" t="n">
         <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-14 22:29:28</t>
+          <t>2026-07-15 00:38:13</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-15.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-15.xlsx
@@ -857,16 +857,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="G2" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="H2" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="I2" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J2" t="n">
         <v>3.2</v>
@@ -875,37 +875,37 @@
         <v>3.45</v>
       </c>
       <c r="L2" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="M2" t="n">
         <v>1.09</v>
       </c>
       <c r="N2" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="O2" t="n">
         <v>1.41</v>
       </c>
       <c r="P2" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="R2" t="n">
         <v>1.26</v>
       </c>
       <c r="S2" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="T2" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="U2" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="V2" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W2" t="n">
         <v>1.6</v>
@@ -917,10 +917,10 @@
         <v>11</v>
       </c>
       <c r="Z2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA2" t="n">
-        <v>130</v>
+        <v>80</v>
       </c>
       <c r="AB2" t="n">
         <v>9.199999999999999</v>
@@ -929,10 +929,10 @@
         <v>7.8</v>
       </c>
       <c r="AD2" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AE2" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF2" t="n">
         <v>17</v>
@@ -944,52 +944,52 @@
         <v>19.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>130</v>
+        <v>80</v>
       </c>
       <c r="AJ2" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AK2" t="n">
         <v>34</v>
       </c>
       <c r="AL2" t="n">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="AM2" t="n">
         <v>580</v>
       </c>
       <c r="AN2" t="n">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="AO2" t="n">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="AP2" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AQ2" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AS2" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="AT2" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AU2" t="n">
         <v>6.4</v>
       </c>
       <c r="AV2" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AW2" t="n">
         <v>34</v>
       </c>
       <c r="AX2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AY2" t="n">
         <v>10.5</v>
@@ -1001,40 +1001,40 @@
         <v>42</v>
       </c>
       <c r="BB2" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="BC2" t="n">
+        <v>24</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>90</v>
+      </c>
+      <c r="BF2" t="n">
         <v>22</v>
       </c>
-      <c r="BD2" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BG2" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BH2" t="n">
         <v>3.15</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="BJ2" t="n">
         <v>10.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BN2" t="n">
         <v>5.5</v>
@@ -1052,35 +1052,35 @@
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BT2" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BU2" t="n">
         <v>5.2</v>
       </c>
       <c r="BV2" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="BW2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BX2" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BY2" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-15 00:38:13</t>
+          <t>2026-07-15 02:46:45</t>
         </is>
       </c>
     </row>
@@ -1111,13 +1111,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="G3" t="n">
         <v>1.34</v>
       </c>
       <c r="H3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="I3" t="n">
         <v>18.5</v>
@@ -1129,28 +1129,28 @@
         <v>6.8</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M3" t="n">
         <v>1.05</v>
       </c>
       <c r="N3" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="O3" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P3" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="R3" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S3" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="T3" t="n">
         <v>2.32</v>
@@ -1162,10 +1162,10 @@
         <v>1.05</v>
       </c>
       <c r="W3" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="X3" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Y3" t="n">
         <v>44</v>
@@ -1222,55 +1222,55 @@
         <v>5.6</v>
       </c>
       <c r="AQ3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV3" t="n">
         <v>6.6</v>
       </c>
-      <c r="AR3" t="n">
+      <c r="AW3" t="n">
         <v>7.4</v>
       </c>
-      <c r="AS3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>7.6</v>
-      </c>
       <c r="AX3" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="AY3" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AZ3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BD3" t="n">
         <v>6.6</v>
       </c>
-      <c r="BA3" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BE3" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BF3" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="BG3" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BH3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-15 00:38:13</t>
+          <t>2026-07-15 02:46:45</t>
         </is>
       </c>
     </row>
@@ -1365,46 +1365,46 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="G4" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="H4" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="I4" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="J4" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="K4" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L4" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="M4" t="n">
         <v>1.05</v>
       </c>
       <c r="N4" t="n">
-        <v>3.75</v>
+        <v>4.6</v>
       </c>
       <c r="O4" t="n">
         <v>1.23</v>
       </c>
       <c r="P4" t="n">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="R4" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="S4" t="n">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
       <c r="T4" t="n">
         <v>1.7</v>
@@ -1413,16 +1413,16 @@
         <v>2.08</v>
       </c>
       <c r="V4" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="W4" t="n">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="X4" t="n">
         <v>21</v>
       </c>
       <c r="Y4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z4" t="n">
         <v>48</v>
@@ -1437,10 +1437,10 @@
         <v>10.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AE4" t="n">
-        <v>85</v>
+        <v>150</v>
       </c>
       <c r="AF4" t="n">
         <v>12</v>
@@ -1449,10 +1449,10 @@
         <v>11</v>
       </c>
       <c r="AH4" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AI4" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AJ4" t="n">
         <v>18.5</v>
@@ -1464,25 +1464,25 @@
         <v>34</v>
       </c>
       <c r="AM4" t="n">
-        <v>95</v>
+        <v>580</v>
       </c>
       <c r="AN4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AO4" t="n">
-        <v>85</v>
+        <v>310</v>
       </c>
       <c r="AP4" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="AQ4" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="AR4" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AS4" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AT4" t="n">
         <v>5.8</v>
@@ -1491,10 +1491,10 @@
         <v>5.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="AW4" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AX4" t="n">
         <v>6.2</v>
@@ -1503,28 +1503,28 @@
         <v>5.8</v>
       </c>
       <c r="AZ4" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BA4" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BB4" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="BC4" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="BD4" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BE4" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BF4" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="BG4" t="n">
-        <v>9.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="BH4" t="n">
         <v>4.2</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-15 00:38:13</t>
+          <t>2026-07-15 02:46:45</t>
         </is>
       </c>
     </row>
@@ -1619,73 +1619,73 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="G5" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="H5" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I5" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="J5" t="n">
         <v>2.92</v>
       </c>
       <c r="K5" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="L5" t="n">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="M5" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="N5" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="O5" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="P5" t="n">
         <v>1.47</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="R5" t="n">
         <v>1.17</v>
       </c>
       <c r="S5" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="T5" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="U5" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="V5" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W5" t="n">
         <v>1.58</v>
       </c>
       <c r="X5" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="Y5" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z5" t="n">
-        <v>24</v>
+        <v>90</v>
       </c>
       <c r="AA5" t="n">
         <v>900</v>
       </c>
       <c r="AB5" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AC5" t="n">
         <v>7.4</v>
@@ -1697,7 +1697,7 @@
         <v>290</v>
       </c>
       <c r="AF5" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AG5" t="n">
         <v>14</v>
@@ -1709,7 +1709,7 @@
         <v>500</v>
       </c>
       <c r="AJ5" t="n">
-        <v>220</v>
+        <v>170</v>
       </c>
       <c r="AK5" t="n">
         <v>95</v>
@@ -1721,13 +1721,13 @@
         <v>500</v>
       </c>
       <c r="AN5" t="n">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AO5" t="n">
         <v>500</v>
       </c>
       <c r="AP5" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AQ5" t="n">
         <v>7.8</v>
@@ -1736,7 +1736,7 @@
         <v>17.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="AT5" t="n">
         <v>6.4</v>
@@ -1748,7 +1748,7 @@
         <v>12.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX5" t="n">
         <v>11.5</v>
@@ -1760,89 +1760,89 @@
         <v>19</v>
       </c>
       <c r="BA5" t="n">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB5" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="BC5" t="n">
         <v>16</v>
       </c>
       <c r="BD5" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="BE5" t="n">
-        <v>8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF5" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BG5" t="n">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH5" t="n">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="BJ5" t="n">
         <v>12</v>
       </c>
       <c r="BK5" t="n">
-        <v>8.800000000000001</v>
+        <v>6</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BN5" t="n">
         <v>5.4</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BP5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BQ5" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT5" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BU5" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-15 00:38:13</t>
+          <t>2026-07-15 02:46:45</t>
         </is>
       </c>
     </row>
@@ -1873,31 +1873,31 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="G6" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="H6" t="n">
         <v>2.88</v>
-      </c>
-      <c r="H6" t="n">
-        <v>2.8</v>
       </c>
       <c r="I6" t="n">
         <v>3.1</v>
       </c>
       <c r="J6" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="K6" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L6" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="M6" t="n">
         <v>1.08</v>
       </c>
       <c r="N6" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="O6" t="n">
         <v>1.37</v>
@@ -1906,25 +1906,25 @@
         <v>1.81</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="R6" t="n">
         <v>1.32</v>
       </c>
       <c r="S6" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="T6" t="n">
         <v>1.8</v>
       </c>
       <c r="U6" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V6" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W6" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="X6" t="n">
         <v>12.5</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-15 00:38:13</t>
+          <t>2026-07-15 02:46:45</t>
         </is>
       </c>
     </row>
@@ -2127,67 +2127,67 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="G7" t="n">
         <v>3.2</v>
       </c>
       <c r="H7" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="I7" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="J7" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K7" t="n">
         <v>3.7</v>
       </c>
       <c r="L7" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="M7" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N7" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="O7" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="P7" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.83</v>
+        <v>1.98</v>
       </c>
       <c r="R7" t="n">
         <v>1.35</v>
       </c>
       <c r="S7" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="T7" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="U7" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="V7" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="W7" t="n">
         <v>1.46</v>
       </c>
       <c r="X7" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y7" t="n">
         <v>12</v>
       </c>
       <c r="Z7" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AA7" t="n">
         <v>38</v>
@@ -2196,7 +2196,7 @@
         <v>13.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AD7" t="n">
         <v>14</v>
@@ -2205,7 +2205,7 @@
         <v>32</v>
       </c>
       <c r="AF7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG7" t="n">
         <v>15.5</v>
@@ -2217,10 +2217,10 @@
         <v>44</v>
       </c>
       <c r="AJ7" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AK7" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AL7" t="n">
         <v>48</v>
@@ -2229,13 +2229,13 @@
         <v>95</v>
       </c>
       <c r="AN7" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AO7" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AP7" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AQ7" t="n">
         <v>9.199999999999999</v>
@@ -2289,10 +2289,10 @@
         <v>15</v>
       </c>
       <c r="BH7" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="BJ7" t="n">
         <v>9.6</v>
@@ -2316,13 +2316,13 @@
         <v>24</v>
       </c>
       <c r="BQ7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BR7" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BS7" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BT7" t="n">
         <v>5.7</v>
@@ -2331,26 +2331,26 @@
         <v>4.4</v>
       </c>
       <c r="BV7" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BW7" t="n">
         <v>14.5</v>
       </c>
       <c r="BX7" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BY7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BZ7" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="CA7" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-15 00:38:13</t>
+          <t>2026-07-15 02:46:45</t>
         </is>
       </c>
     </row>
@@ -2384,115 +2384,115 @@
         <v>1.71</v>
       </c>
       <c r="G8" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="H8" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="I8" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="J8" t="n">
         <v>4</v>
       </c>
       <c r="K8" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L8" t="n">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="M8" t="n">
         <v>1.06</v>
       </c>
       <c r="N8" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="O8" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="P8" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="R8" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="S8" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="T8" t="n">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="U8" t="n">
-        <v>2.06</v>
+        <v>1.98</v>
       </c>
       <c r="V8" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W8" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="X8" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="Y8" t="n">
         <v>23</v>
       </c>
       <c r="Z8" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AA8" t="n">
         <v>160</v>
       </c>
       <c r="AB8" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC8" t="n">
         <v>11.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AE8" t="n">
         <v>85</v>
       </c>
       <c r="AF8" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AG8" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AI8" t="n">
         <v>85</v>
       </c>
       <c r="AJ8" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AK8" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AL8" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AM8" t="n">
         <v>130</v>
       </c>
       <c r="AN8" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AO8" t="n">
         <v>95</v>
       </c>
       <c r="AP8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AQ8" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AR8" t="n">
         <v>1.03</v>
@@ -2501,7 +2501,7 @@
         <v>1.03</v>
       </c>
       <c r="AT8" t="n">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="AU8" t="n">
         <v>7</v>
@@ -2519,16 +2519,16 @@
         <v>7.4</v>
       </c>
       <c r="AZ8" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA8" t="n">
         <v>1.03</v>
       </c>
       <c r="BB8" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BC8" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BD8" t="n">
         <v>1.03</v>
@@ -2537,22 +2537,22 @@
         <v>1.03</v>
       </c>
       <c r="BF8" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG8" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BH8" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="BI8" t="n">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="BJ8" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
@@ -2561,10 +2561,10 @@
         <v>1.01</v>
       </c>
       <c r="BN8" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BO8" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BP8" t="n">
         <v>11.5</v>
@@ -2573,38 +2573,38 @@
         <v>8.4</v>
       </c>
       <c r="BR8" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BS8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BT8" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BU8" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BX8" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY8" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BZ8" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="CA8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-15 00:38:13</t>
+          <t>2026-07-15 02:46:45</t>
         </is>
       </c>
     </row>
@@ -2635,64 +2635,64 @@
         </is>
       </c>
       <c r="F9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="G9" t="n">
+        <v>5</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K9" t="n">
         <v>4.2</v>
       </c>
-      <c r="G9" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="J9" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K9" t="n">
-        <v>4.3</v>
-      </c>
       <c r="L9" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="M9" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N9" t="n">
         <v>3.75</v>
       </c>
       <c r="O9" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="P9" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.86</v>
+        <v>1.98</v>
       </c>
       <c r="R9" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="S9" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="T9" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="U9" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="V9" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="W9" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="X9" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z9" t="n">
         <v>13.5</v>
@@ -2701,7 +2701,7 @@
         <v>23</v>
       </c>
       <c r="AB9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AC9" t="n">
         <v>11</v>
@@ -2713,7 +2713,7 @@
         <v>23</v>
       </c>
       <c r="AF9" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AG9" t="n">
         <v>22</v>
@@ -2722,34 +2722,34 @@
         <v>23</v>
       </c>
       <c r="AI9" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AJ9" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AK9" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL9" t="n">
         <v>70</v>
       </c>
-      <c r="AL9" t="n">
-        <v>75</v>
-      </c>
       <c r="AM9" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN9" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AO9" t="n">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="AP9" t="n">
         <v>11.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AR9" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS9" t="n">
         <v>15</v>
@@ -2794,19 +2794,19 @@
         <v>46</v>
       </c>
       <c r="BG9" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BH9" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="BJ9" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BK9" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
@@ -2818,47 +2818,47 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BO9" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BP9" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BQ9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BT9" t="n">
         <v>4.7</v>
       </c>
       <c r="BU9" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BV9" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BW9" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX9" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BY9" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BZ9" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="CA9" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-15 00:38:13</t>
+          <t>2026-07-15 02:46:45</t>
         </is>
       </c>
     </row>
@@ -2889,61 +2889,61 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="G10" t="n">
         <v>1.3</v>
       </c>
       <c r="H10" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="I10" t="n">
         <v>14</v>
       </c>
       <c r="J10" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="K10" t="n">
         <v>8</v>
       </c>
       <c r="L10" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="M10" t="n">
         <v>1.02</v>
       </c>
       <c r="N10" t="n">
-        <v>1.02</v>
+        <v>7.2</v>
       </c>
       <c r="O10" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="P10" t="n">
-        <v>2.84</v>
+        <v>3.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="R10" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="S10" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="T10" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="U10" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="V10" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="W10" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="X10" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Y10" t="n">
         <v>65</v>
@@ -2952,19 +2952,19 @@
         <v>150</v>
       </c>
       <c r="AA10" t="n">
-        <v>510</v>
+        <v>460</v>
       </c>
       <c r="AB10" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AD10" t="n">
         <v>55</v>
       </c>
       <c r="AE10" t="n">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="AF10" t="n">
         <v>12</v>
@@ -2973,94 +2973,94 @@
         <v>14</v>
       </c>
       <c r="AH10" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AI10" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AJ10" t="n">
         <v>12.5</v>
       </c>
       <c r="AK10" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AL10" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AM10" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN10" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="AO10" t="n">
-        <v>200</v>
+        <v>170</v>
       </c>
       <c r="AP10" t="n">
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
       <c r="AQ10" t="n">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="AR10" t="n">
-        <v>6.8</v>
+        <v>5.9</v>
       </c>
       <c r="AS10" t="n">
-        <v>2.36</v>
+        <v>6</v>
       </c>
       <c r="AT10" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AU10" t="n">
         <v>4.7</v>
       </c>
-      <c r="AU10" t="n">
+      <c r="AV10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AZ10" t="n">
         <v>5.1</v>
       </c>
-      <c r="AV10" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AZ10" t="n">
+      <c r="BA10" t="n">
         <v>5.8</v>
       </c>
-      <c r="BA10" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BB10" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="BD10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="BG10" t="n">
         <v>5.9</v>
       </c>
-      <c r="BE10" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BH10" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK10" t="n">
         <v>5.6</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>5.5</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
@@ -3072,25 +3072,25 @@
         <v>4.3</v>
       </c>
       <c r="BO10" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BP10" t="n">
         <v>7</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BR10" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BS10" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BT10" t="n">
         <v>16</v>
       </c>
       <c r="BU10" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-15 00:38:13</t>
+          <t>2026-07-15 02:46:45</t>
         </is>
       </c>
     </row>
@@ -3143,19 +3143,19 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="G11" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="H11" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="I11" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K11" t="n">
         <v>4.4</v>
@@ -3167,10 +3167,10 @@
         <v>1.08</v>
       </c>
       <c r="N11" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="O11" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="P11" t="n">
         <v>1.82</v>
@@ -3182,19 +3182,19 @@
         <v>1.31</v>
       </c>
       <c r="S11" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="T11" t="n">
         <v>2.1</v>
       </c>
       <c r="U11" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="V11" t="n">
         <v>1.14</v>
       </c>
       <c r="W11" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="X11" t="n">
         <v>15</v>
@@ -3221,7 +3221,7 @@
         <v>150</v>
       </c>
       <c r="AF11" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG11" t="n">
         <v>10.5</v>
@@ -3236,7 +3236,7 @@
         <v>16</v>
       </c>
       <c r="AK11" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AL11" t="n">
         <v>55</v>
@@ -3254,25 +3254,25 @@
         <v>10</v>
       </c>
       <c r="AQ11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AR11" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AS11" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AT11" t="n">
         <v>6.2</v>
       </c>
       <c r="AU11" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV11" t="n">
         <v>21</v>
       </c>
       <c r="AW11" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AX11" t="n">
         <v>7.8</v>
@@ -3284,25 +3284,25 @@
         <v>21</v>
       </c>
       <c r="BA11" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BB11" t="n">
         <v>11.5</v>
       </c>
       <c r="BC11" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BD11" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BE11" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BF11" t="n">
         <v>9.6</v>
       </c>
       <c r="BG11" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BH11" t="n">
         <v>3.25</v>
@@ -3314,22 +3314,22 @@
         <v>11.5</v>
       </c>
       <c r="BK11" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>16</v>
+        <v>2.74</v>
       </c>
       <c r="BN11" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BO11" t="n">
         <v>3.55</v>
       </c>
       <c r="BP11" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BQ11" t="n">
         <v>6.8</v>
@@ -3338,35 +3338,35 @@
         <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BT11" t="n">
         <v>10.5</v>
       </c>
       <c r="BU11" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>14</v>
+        <v>2.7</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BZ11" t="n">
         <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-15 00:38:13</t>
+          <t>2026-07-15 02:46:45</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-15.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-15.xlsx
@@ -857,16 +857,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.48</v>
+        <v>2.62</v>
       </c>
       <c r="G2" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="H2" t="n">
-        <v>3.15</v>
+        <v>2.94</v>
       </c>
       <c r="I2" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="J2" t="n">
         <v>3.2</v>
@@ -878,22 +878,22 @@
         <v>1.48</v>
       </c>
       <c r="M2" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N2" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="O2" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P2" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="Q2" t="n">
         <v>2.28</v>
       </c>
       <c r="R2" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S2" t="n">
         <v>4.4</v>
@@ -905,10 +905,10 @@
         <v>1.96</v>
       </c>
       <c r="V2" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="W2" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="X2" t="n">
         <v>11.5</v>
@@ -917,25 +917,25 @@
         <v>11</v>
       </c>
       <c r="Z2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA2" t="n">
         <v>80</v>
       </c>
       <c r="AB2" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AC2" t="n">
         <v>7.8</v>
       </c>
       <c r="AD2" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE2" t="n">
         <v>55</v>
       </c>
       <c r="AF2" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AG2" t="n">
         <v>13</v>
@@ -947,49 +947,49 @@
         <v>80</v>
       </c>
       <c r="AJ2" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AK2" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="AL2" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AM2" t="n">
         <v>580</v>
       </c>
       <c r="AN2" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AO2" t="n">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="AP2" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AQ2" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR2" t="n">
         <v>18</v>
       </c>
       <c r="AS2" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AT2" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU2" t="n">
         <v>6.4</v>
       </c>
       <c r="AV2" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AW2" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AX2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AY2" t="n">
         <v>10.5</v>
@@ -1004,16 +1004,16 @@
         <v>27</v>
       </c>
       <c r="BC2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BD2" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BE2" t="n">
         <v>90</v>
       </c>
       <c r="BF2" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="BG2" t="n">
         <v>34</v>
@@ -1022,65 +1022,65 @@
         <v>3.15</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="BJ2" t="n">
         <v>10.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BN2" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BO2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BP2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BQ2" t="n">
-        <v>14</v>
+        <v>7.4</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BT2" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BU2" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BV2" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="BX2" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="CA2" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-15 02:46:45</t>
+          <t>2026-07-15 04:55:19</t>
         </is>
       </c>
     </row>
@@ -1111,220 +1111,220 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="G3" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="H3" t="n">
-        <v>8.4</v>
+        <v>12.5</v>
       </c>
       <c r="I3" t="n">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="J3" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="K3" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="L3" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="M3" t="n">
         <v>1.05</v>
       </c>
       <c r="N3" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="O3" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P3" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="Q3" t="n">
         <v>1.78</v>
       </c>
       <c r="R3" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="S3" t="n">
         <v>3</v>
       </c>
       <c r="T3" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="U3" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="V3" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W3" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="X3" t="n">
         <v>22</v>
       </c>
       <c r="Y3" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="Z3" t="n">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="AA3" t="n">
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AD3" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AE3" t="n">
-        <v>420</v>
+        <v>330</v>
       </c>
       <c r="AF3" t="n">
         <v>7.6</v>
       </c>
       <c r="AG3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>38</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>240</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>270</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>540</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>36</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ3" t="n">
         <v>12</v>
       </c>
-      <c r="AH3" t="n">
-        <v>44</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>300</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>10</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>330</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>6</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AQ3" t="n">
+      <c r="BA3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>15</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BK3" t="n">
         <v>6.4</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>1.01</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BN3" t="n">
-        <v>1000</v>
+        <v>3.7</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.01</v>
+        <v>2.98</v>
       </c>
       <c r="BP3" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BR3" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BT3" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BU3" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-15 02:46:45</t>
+          <t>2026-07-15 04:55:19</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="G4" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="H4" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="I4" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="J4" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K4" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="L4" t="n">
         <v>1.33</v>
@@ -1389,7 +1389,7 @@
         <v>1.05</v>
       </c>
       <c r="N4" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O4" t="n">
         <v>1.23</v>
@@ -1398,91 +1398,91 @@
         <v>2.26</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="R4" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="S4" t="n">
         <v>2.8</v>
       </c>
       <c r="T4" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="U4" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="V4" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="W4" t="n">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="X4" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Y4" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Z4" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AA4" t="n">
         <v>900</v>
       </c>
       <c r="AB4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC4" t="n">
         <v>11</v>
       </c>
-      <c r="AC4" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AD4" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AE4" t="n">
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="AF4" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG4" t="n">
         <v>11</v>
       </c>
       <c r="AH4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI4" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AJ4" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AK4" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AL4" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AM4" t="n">
         <v>580</v>
       </c>
       <c r="AN4" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO4" t="n">
-        <v>310</v>
+        <v>95</v>
       </c>
       <c r="AP4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AQ4" t="n">
         <v>5.6</v>
       </c>
-      <c r="AQ4" t="n">
-        <v>5.7</v>
-      </c>
       <c r="AR4" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AS4" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AT4" t="n">
         <v>5.8</v>
@@ -1491,10 +1491,10 @@
         <v>5.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AW4" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AX4" t="n">
         <v>6.2</v>
@@ -1503,28 +1503,28 @@
         <v>5.8</v>
       </c>
       <c r="AZ4" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BA4" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BB4" t="n">
         <v>5.4</v>
       </c>
       <c r="BC4" t="n">
-        <v>5.3</v>
+        <v>8.4</v>
       </c>
       <c r="BD4" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BE4" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BF4" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="BG4" t="n">
-        <v>6.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH4" t="n">
         <v>4.2</v>
@@ -1533,28 +1533,28 @@
         <v>2.8</v>
       </c>
       <c r="BJ4" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BK4" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BN4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BQ4" t="n">
         <v>4.7</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>3</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>4.8</v>
       </c>
       <c r="BR4" t="n">
         <v>25</v>
@@ -1563,32 +1563,32 @@
         <v>6.2</v>
       </c>
       <c r="BT4" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BU4" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BV4" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="BW4" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BX4" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="BY4" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BZ4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="CA4" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-15 02:46:45</t>
+          <t>2026-07-15 04:55:19</t>
         </is>
       </c>
     </row>
@@ -1619,64 +1619,64 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="G5" t="n">
-        <v>2.72</v>
+        <v>2.62</v>
       </c>
       <c r="H5" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="I5" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="J5" t="n">
-        <v>2.92</v>
+        <v>2.74</v>
       </c>
       <c r="K5" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="L5" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="M5" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N5" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="O5" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="P5" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="R5" t="n">
         <v>1.17</v>
       </c>
       <c r="S5" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="T5" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="U5" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="V5" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="W5" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="X5" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="Y5" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="Z5" t="n">
         <v>90</v>
@@ -1685,25 +1685,25 @@
         <v>900</v>
       </c>
       <c r="AB5" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AC5" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AE5" t="n">
-        <v>290</v>
+        <v>500</v>
       </c>
       <c r="AF5" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AG5" t="n">
         <v>14</v>
       </c>
       <c r="AH5" t="n">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="AI5" t="n">
         <v>500</v>
@@ -1715,134 +1715,134 @@
         <v>95</v>
       </c>
       <c r="AL5" t="n">
-        <v>460</v>
+        <v>500</v>
       </c>
       <c r="AM5" t="n">
         <v>500</v>
       </c>
       <c r="AN5" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AO5" t="n">
         <v>500</v>
       </c>
       <c r="AP5" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="AQ5" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AR5" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AS5" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT5" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AU5" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AV5" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AX5" t="n">
         <v>12.5</v>
       </c>
-      <c r="AW5" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AY5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ5" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BA5" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB5" t="n">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="BC5" t="n">
-        <v>16</v>
+        <v>7.4</v>
       </c>
       <c r="BD5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BE5" t="n">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BF5" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="BG5" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BH5" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="BJ5" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BN5" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="BP5" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT5" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BU5" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-15 02:46:45</t>
+          <t>2026-07-15 04:55:19</t>
         </is>
       </c>
     </row>
@@ -1873,100 +1873,100 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.64</v>
+        <v>2.72</v>
       </c>
       <c r="G6" t="n">
-        <v>2.74</v>
+        <v>2.92</v>
       </c>
       <c r="H6" t="n">
-        <v>2.88</v>
+        <v>2.72</v>
       </c>
       <c r="I6" t="n">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="J6" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K6" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="L6" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="M6" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N6" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="O6" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="P6" t="n">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="R6" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="S6" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="T6" t="n">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="U6" t="n">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="V6" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="W6" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="X6" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y6" t="n">
         <v>12.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AB6" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AC6" t="n">
         <v>8</v>
       </c>
       <c r="AD6" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AF6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AG6" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI6" t="n">
         <v>46</v>
       </c>
       <c r="AJ6" t="n">
-        <v>46</v>
+        <v>120</v>
       </c>
       <c r="AK6" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL6" t="n">
         <v>42</v>
@@ -1978,22 +1978,22 @@
         <v>30</v>
       </c>
       <c r="AO6" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AP6" t="n">
         <v>10</v>
       </c>
       <c r="AQ6" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR6" t="n">
         <v>15.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AT6" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AU6" t="n">
         <v>6.4</v>
@@ -2011,92 +2011,92 @@
         <v>11</v>
       </c>
       <c r="AZ6" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BB6" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BC6" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BD6" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BE6" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BF6" t="n">
         <v>21</v>
       </c>
       <c r="BG6" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="BJ6" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BN6" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BO6" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BP6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BQ6" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BR6" t="n">
         <v>36</v>
       </c>
       <c r="BS6" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="BT6" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BU6" t="n">
         <v>4.7</v>
       </c>
       <c r="BV6" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BW6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>36</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>29</v>
+      </c>
+      <c r="CA6" t="n">
         <v>8</v>
       </c>
-      <c r="BX6" t="n">
-        <v>38</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>9</v>
-      </c>
-      <c r="BZ6" t="n">
-        <v>32</v>
-      </c>
-      <c r="CA6" t="n">
-        <v>8.6</v>
-      </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-15 02:46:45</t>
+          <t>2026-07-15 04:55:19</t>
         </is>
       </c>
     </row>
@@ -2130,58 +2130,58 @@
         <v>2.9</v>
       </c>
       <c r="G7" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="H7" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="I7" t="n">
         <v>2.66</v>
       </c>
       <c r="J7" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K7" t="n">
         <v>3.7</v>
       </c>
       <c r="L7" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="M7" t="n">
         <v>1.07</v>
       </c>
       <c r="N7" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="O7" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="P7" t="n">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.98</v>
+        <v>1.89</v>
       </c>
       <c r="R7" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="S7" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="T7" t="n">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="U7" t="n">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="V7" t="n">
         <v>1.6</v>
       </c>
       <c r="W7" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="X7" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="Y7" t="n">
         <v>12</v>
@@ -2217,7 +2217,7 @@
         <v>44</v>
       </c>
       <c r="AJ7" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AK7" t="n">
         <v>38</v>
@@ -2229,10 +2229,10 @@
         <v>95</v>
       </c>
       <c r="AN7" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AO7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP7" t="n">
         <v>10</v>
@@ -2250,7 +2250,7 @@
         <v>10</v>
       </c>
       <c r="AU7" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV7" t="n">
         <v>9.199999999999999</v>
@@ -2289,13 +2289,13 @@
         <v>15</v>
       </c>
       <c r="BH7" t="n">
-        <v>3.45</v>
+        <v>1000</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.78</v>
+        <v>2.94</v>
       </c>
       <c r="BJ7" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BK7" t="n">
         <v>7.2</v>
@@ -2313,16 +2313,16 @@
         <v>4.8</v>
       </c>
       <c r="BP7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BQ7" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BR7" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="BS7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BT7" t="n">
         <v>5.7</v>
@@ -2331,26 +2331,26 @@
         <v>4.4</v>
       </c>
       <c r="BV7" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BW7" t="n">
         <v>14.5</v>
       </c>
       <c r="BX7" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BY7" t="n">
         <v>24</v>
       </c>
       <c r="BZ7" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="CA7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-15 02:46:45</t>
+          <t>2026-07-15 04:55:19</t>
         </is>
       </c>
     </row>
@@ -2381,58 +2381,58 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="G8" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="H8" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="I8" t="n">
         <v>6</v>
       </c>
       <c r="J8" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K8" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="L8" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="M8" t="n">
         <v>1.06</v>
       </c>
       <c r="N8" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="O8" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="P8" t="n">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="R8" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="S8" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="T8" t="n">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="U8" t="n">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="V8" t="n">
         <v>1.2</v>
       </c>
       <c r="W8" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="X8" t="n">
         <v>18</v>
@@ -2480,16 +2480,16 @@
         <v>36</v>
       </c>
       <c r="AM8" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN8" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO8" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AP8" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AQ8" t="n">
         <v>13</v>
@@ -2501,10 +2501,10 @@
         <v>1.03</v>
       </c>
       <c r="AT8" t="n">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU8" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AV8" t="n">
         <v>15</v>
@@ -2537,22 +2537,22 @@
         <v>1.03</v>
       </c>
       <c r="BF8" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BG8" t="n">
         <v>60</v>
       </c>
       <c r="BH8" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="BJ8" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BK8" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
@@ -2561,22 +2561,22 @@
         <v>1.01</v>
       </c>
       <c r="BN8" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BO8" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BP8" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BQ8" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BR8" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="BS8" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="BT8" t="n">
         <v>9</v>
@@ -2588,23 +2588,23 @@
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
+        <v>30</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY8" t="n">
         <v>34</v>
       </c>
-      <c r="BX8" t="n">
-        <v>55</v>
-      </c>
-      <c r="BY8" t="n">
-        <v>38</v>
-      </c>
       <c r="BZ8" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="CA8" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-15 02:46:45</t>
+          <t>2026-07-15 04:55:19</t>
         </is>
       </c>
     </row>
@@ -2638,61 +2638,61 @@
         <v>4.3</v>
       </c>
       <c r="G9" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="H9" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="I9" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="J9" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K9" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L9" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M9" t="n">
         <v>1.07</v>
       </c>
       <c r="N9" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="O9" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="P9" t="n">
         <v>1.93</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="R9" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="S9" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="T9" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="U9" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="V9" t="n">
         <v>2.02</v>
-      </c>
-      <c r="V9" t="n">
-        <v>2.04</v>
       </c>
       <c r="W9" t="n">
         <v>1.26</v>
       </c>
       <c r="X9" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="Y9" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Z9" t="n">
         <v>13.5</v>
@@ -2701,10 +2701,10 @@
         <v>23</v>
       </c>
       <c r="AB9" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD9" t="n">
         <v>12.5</v>
@@ -2734,10 +2734,10 @@
         <v>70</v>
       </c>
       <c r="AM9" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="AN9" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="AO9" t="n">
         <v>16.5</v>
@@ -2794,19 +2794,19 @@
         <v>46</v>
       </c>
       <c r="BG9" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BH9" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="BJ9" t="n">
         <v>10.5</v>
       </c>
       <c r="BK9" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
@@ -2818,22 +2818,22 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BO9" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BP9" t="n">
         <v>42</v>
       </c>
       <c r="BQ9" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BR9" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS9" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BT9" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BU9" t="n">
         <v>3.5</v>
@@ -2842,23 +2842,23 @@
         <v>14</v>
       </c>
       <c r="BW9" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BX9" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BY9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BZ9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="CA9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-15 02:46:45</t>
+          <t>2026-07-15 04:55:19</t>
         </is>
       </c>
     </row>
@@ -2895,10 +2895,10 @@
         <v>1.3</v>
       </c>
       <c r="H10" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="I10" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="J10" t="n">
         <v>6.4</v>
@@ -2916,7 +2916,7 @@
         <v>7.2</v>
       </c>
       <c r="O10" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="P10" t="n">
         <v>3.2</v>
@@ -2931,136 +2931,136 @@
         <v>2</v>
       </c>
       <c r="T10" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="U10" t="n">
         <v>2</v>
       </c>
       <c r="V10" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W10" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="X10" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="Y10" t="n">
         <v>65</v>
       </c>
       <c r="Z10" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AA10" t="n">
-        <v>460</v>
+        <v>430</v>
       </c>
       <c r="AB10" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AC10" t="n">
         <v>20</v>
       </c>
       <c r="AD10" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AE10" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AF10" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AG10" t="n">
         <v>14</v>
       </c>
       <c r="AH10" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AI10" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AJ10" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AK10" t="n">
         <v>15.5</v>
       </c>
       <c r="AL10" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM10" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN10" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="AO10" t="n">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="AP10" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AZ10" t="n">
         <v>5.4</v>
       </c>
-      <c r="AQ10" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>6</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BA10" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BB10" t="n">
         <v>4.1</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BD10" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BE10" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.86</v>
+        <v>2.96</v>
       </c>
       <c r="BG10" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BH10" t="n">
         <v>5.7</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BJ10" t="n">
         <v>12</v>
       </c>
       <c r="BK10" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
@@ -3069,28 +3069,28 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BN10" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BO10" t="n">
         <v>3.05</v>
       </c>
       <c r="BP10" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BQ10" t="n">
         <v>4.2</v>
       </c>
       <c r="BR10" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BS10" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BT10" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BU10" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-15 02:46:45</t>
+          <t>2026-07-15 04:55:19</t>
         </is>
       </c>
     </row>
@@ -3143,10 +3143,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="G11" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="H11" t="n">
         <v>7.2</v>
@@ -3155,7 +3155,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K11" t="n">
         <v>4.4</v>
@@ -3182,19 +3182,19 @@
         <v>1.31</v>
       </c>
       <c r="S11" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="T11" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="U11" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="V11" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="W11" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="X11" t="n">
         <v>15</v>
@@ -3305,68 +3305,68 @@
         <v>6.8</v>
       </c>
       <c r="BH11" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BI11" t="n">
         <v>3</v>
       </c>
       <c r="BJ11" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BK11" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>2.74</v>
+        <v>14.5</v>
       </c>
       <c r="BN11" t="n">
         <v>3.9</v>
       </c>
       <c r="BO11" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BP11" t="n">
         <v>10.5</v>
       </c>
       <c r="BQ11" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="BT11" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BU11" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>2.7</v>
+        <v>13</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="BZ11" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="CA11" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-15 02:46:45</t>
+          <t>2026-07-15 04:55:19</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-15.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-15.xlsx
@@ -857,37 +857,37 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="G2" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="H2" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="I2" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="J2" t="n">
         <v>3.2</v>
       </c>
       <c r="K2" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L2" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="M2" t="n">
         <v>1.1</v>
       </c>
       <c r="N2" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="O2" t="n">
         <v>1.42</v>
       </c>
       <c r="P2" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="Q2" t="n">
         <v>2.28</v>
@@ -899,28 +899,28 @@
         <v>4.4</v>
       </c>
       <c r="T2" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="U2" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="V2" t="n">
         <v>1.45</v>
       </c>
       <c r="W2" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="X2" t="n">
         <v>11.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z2" t="n">
         <v>22</v>
       </c>
       <c r="AA2" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AB2" t="n">
         <v>9.6</v>
@@ -935,7 +935,7 @@
         <v>55</v>
       </c>
       <c r="AF2" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AG2" t="n">
         <v>13</v>
@@ -944,16 +944,16 @@
         <v>19.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AJ2" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AK2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AL2" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="AM2" t="n">
         <v>580</v>
@@ -968,13 +968,13 @@
         <v>9.6</v>
       </c>
       <c r="AQ2" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AR2" t="n">
         <v>18</v>
       </c>
       <c r="AS2" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AT2" t="n">
         <v>8.199999999999999</v>
@@ -986,7 +986,7 @@
         <v>12</v>
       </c>
       <c r="AW2" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AX2" t="n">
         <v>15</v>
@@ -995,13 +995,13 @@
         <v>10.5</v>
       </c>
       <c r="AZ2" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA2" t="n">
         <v>42</v>
       </c>
       <c r="BB2" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="BC2" t="n">
         <v>25</v>
@@ -1010,7 +1010,7 @@
         <v>36</v>
       </c>
       <c r="BE2" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="BF2" t="n">
         <v>26</v>
@@ -1028,16 +1028,16 @@
         <v>10.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.4</v>
+        <v>8</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN2" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BO2" t="n">
         <v>4.8</v>
@@ -1046,13 +1046,13 @@
         <v>23</v>
       </c>
       <c r="BQ2" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT2" t="n">
         <v>6.2</v>
@@ -1064,23 +1064,23 @@
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BZ2" t="n">
         <v>38</v>
       </c>
       <c r="CA2" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-15 04:55:19</t>
+          <t>2026-07-15 07:03:56</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="G3" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="H3" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="I3" t="n">
         <v>15.5</v>
       </c>
       <c r="J3" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="K3" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="L3" t="n">
         <v>1.35</v>
@@ -1150,10 +1150,10 @@
         <v>1.43</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="T3" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="U3" t="n">
         <v>1.64</v>
@@ -1162,31 +1162,31 @@
         <v>1.06</v>
       </c>
       <c r="W3" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="X3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y3" t="n">
         <v>38</v>
       </c>
       <c r="Z3" t="n">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="AA3" t="n">
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AC3" t="n">
         <v>14</v>
       </c>
       <c r="AD3" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AE3" t="n">
-        <v>330</v>
+        <v>290</v>
       </c>
       <c r="AF3" t="n">
         <v>7.6</v>
@@ -1195,43 +1195,43 @@
         <v>11.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AI3" t="n">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="AJ3" t="n">
         <v>10.5</v>
       </c>
       <c r="AK3" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AL3" t="n">
         <v>50</v>
       </c>
       <c r="AM3" t="n">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="AN3" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AO3" t="n">
-        <v>540</v>
+        <v>460</v>
       </c>
       <c r="AP3" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AQ3" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AR3" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS3" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="AT3" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AU3" t="n">
         <v>11</v>
@@ -1240,7 +1240,7 @@
         <v>36</v>
       </c>
       <c r="AW3" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AX3" t="n">
         <v>6.2</v>
@@ -1249,28 +1249,28 @@
         <v>9.4</v>
       </c>
       <c r="AZ3" t="n">
-        <v>12</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BA3" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BB3" t="n">
         <v>8.4</v>
       </c>
       <c r="BC3" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>9.199999999999999</v>
+        <v>15.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BF3" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BG3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="BH3" t="n">
         <v>4</v>
@@ -1279,10 +1279,10 @@
         <v>3.2</v>
       </c>
       <c r="BJ3" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
@@ -1297,7 +1297,7 @@
         <v>2.98</v>
       </c>
       <c r="BP3" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BQ3" t="n">
         <v>6</v>
@@ -1309,22 +1309,22 @@
         <v>8</v>
       </c>
       <c r="BT3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BU3" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-15 04:55:19</t>
+          <t>2026-07-15 07:03:56</t>
         </is>
       </c>
     </row>
@@ -1365,19 +1365,19 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="G4" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="H4" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="I4" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="J4" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="K4" t="n">
         <v>4.7</v>
@@ -1395,37 +1395,37 @@
         <v>1.23</v>
       </c>
       <c r="P4" t="n">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="Q4" t="n">
         <v>1.72</v>
       </c>
       <c r="R4" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="S4" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="T4" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="U4" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="V4" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W4" t="n">
-        <v>2.42</v>
+        <v>2.52</v>
       </c>
       <c r="X4" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Y4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Z4" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AA4" t="n">
         <v>900</v>
@@ -1437,158 +1437,158 @@
         <v>11</v>
       </c>
       <c r="AD4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AE4" t="n">
-        <v>90</v>
+        <v>230</v>
       </c>
       <c r="AF4" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AG4" t="n">
         <v>11</v>
       </c>
       <c r="AH4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI4" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="AJ4" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AK4" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AL4" t="n">
         <v>36</v>
       </c>
       <c r="AM4" t="n">
-        <v>580</v>
+        <v>700</v>
       </c>
       <c r="AN4" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AO4" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AP4" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AQ4" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="AR4" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="AS4" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="AT4" t="n">
-        <v>5.8</v>
+        <v>7.4</v>
       </c>
       <c r="AU4" t="n">
         <v>5.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="AW4" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AX4" t="n">
         <v>6.6</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>6.2</v>
       </c>
       <c r="AY4" t="n">
         <v>5.8</v>
       </c>
       <c r="AZ4" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="BA4" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB4" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BC4" t="n">
-        <v>8.4</v>
+        <v>5.7</v>
       </c>
       <c r="BD4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BE4" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="BF4" t="n">
-        <v>3.8</v>
+        <v>5.9</v>
       </c>
       <c r="BG4" t="n">
-        <v>9.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BH4" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="BJ4" t="n">
         <v>11</v>
       </c>
       <c r="BK4" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN4" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BO4" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="BP4" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BR4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BS4" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BT4" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BU4" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="BV4" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BW4" t="n">
-        <v>7.4</v>
+        <v>2.8</v>
       </c>
       <c r="BX4" t="n">
         <v>60</v>
       </c>
       <c r="BY4" t="n">
-        <v>7.4</v>
+        <v>2.8</v>
       </c>
       <c r="BZ4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="CA4" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-15 04:55:19</t>
+          <t>2026-07-15 07:03:56</t>
         </is>
       </c>
     </row>
@@ -1622,58 +1622,58 @@
         <v>2.5</v>
       </c>
       <c r="G5" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="H5" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="I5" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="J5" t="n">
-        <v>2.74</v>
+        <v>2.82</v>
       </c>
       <c r="K5" t="n">
         <v>2.96</v>
       </c>
       <c r="L5" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="M5" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="N5" t="n">
-        <v>2.48</v>
+        <v>2.66</v>
       </c>
       <c r="O5" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="P5" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.94</v>
+        <v>2.74</v>
       </c>
       <c r="R5" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="S5" t="n">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="T5" t="n">
-        <v>2.24</v>
+        <v>2.06</v>
       </c>
       <c r="U5" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="V5" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W5" t="n">
         <v>1.62</v>
       </c>
       <c r="X5" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="Y5" t="n">
         <v>10.5</v>
@@ -1685,25 +1685,25 @@
         <v>900</v>
       </c>
       <c r="AB5" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AC5" t="n">
         <v>7.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>500</v>
+        <v>290</v>
       </c>
       <c r="AF5" t="n">
         <v>15</v>
       </c>
       <c r="AG5" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="AI5" t="n">
         <v>500</v>
@@ -1715,134 +1715,134 @@
         <v>95</v>
       </c>
       <c r="AL5" t="n">
-        <v>500</v>
+        <v>460</v>
       </c>
       <c r="AM5" t="n">
         <v>500</v>
       </c>
       <c r="AN5" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO5" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP5" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="AQ5" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AR5" t="n">
         <v>19</v>
       </c>
       <c r="AS5" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AT5" t="n">
         <v>6</v>
       </c>
       <c r="AU5" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AV5" t="n">
         <v>14</v>
       </c>
       <c r="AW5" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AX5" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AY5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ5" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB5" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BC5" t="n">
-        <v>7.4</v>
+        <v>16</v>
       </c>
       <c r="BD5" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BF5" t="n">
         <v>8</v>
       </c>
-      <c r="BE5" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BG5" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BH5" t="n">
-        <v>2.64</v>
+        <v>2.74</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.18</v>
+        <v>2.32</v>
       </c>
       <c r="BJ5" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BN5" t="n">
         <v>5.3</v>
       </c>
       <c r="BO5" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BP5" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BQ5" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BT5" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BU5" t="n">
         <v>5.2</v>
       </c>
       <c r="BV5" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BW5" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-15 04:55:19</t>
+          <t>2026-07-15 07:03:56</t>
         </is>
       </c>
     </row>
@@ -1873,13 +1873,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="G6" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="H6" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="I6" t="n">
         <v>2.96</v>
@@ -1897,16 +1897,16 @@
         <v>1.07</v>
       </c>
       <c r="N6" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="O6" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P6" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="R6" t="n">
         <v>1.36</v>
@@ -1915,16 +1915,16 @@
         <v>3.6</v>
       </c>
       <c r="T6" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="U6" t="n">
         <v>2.16</v>
       </c>
       <c r="V6" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="W6" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="X6" t="n">
         <v>14.5</v>
@@ -1936,7 +1936,7 @@
         <v>19.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AB6" t="n">
         <v>12</v>
@@ -1951,7 +1951,7 @@
         <v>32</v>
       </c>
       <c r="AF6" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AG6" t="n">
         <v>14.5</v>
@@ -1975,13 +1975,13 @@
         <v>580</v>
       </c>
       <c r="AN6" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AO6" t="n">
         <v>32</v>
       </c>
       <c r="AP6" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AQ6" t="n">
         <v>9.199999999999999</v>
@@ -1990,10 +1990,10 @@
         <v>15.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AT6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AU6" t="n">
         <v>6.4</v>
@@ -2002,10 +2002,10 @@
         <v>11</v>
       </c>
       <c r="AW6" t="n">
-        <v>6.8</v>
+        <v>12</v>
       </c>
       <c r="AX6" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AY6" t="n">
         <v>11</v>
@@ -2014,25 +2014,25 @@
         <v>13.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BB6" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BC6" t="n">
-        <v>6.8</v>
+        <v>12</v>
       </c>
       <c r="BD6" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BE6" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF6" t="n">
         <v>21</v>
       </c>
       <c r="BG6" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BH6" t="n">
         <v>3.45</v>
@@ -2044,59 +2044,59 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN6" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BO6" t="n">
         <v>5.1</v>
       </c>
       <c r="BP6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BQ6" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BR6" t="n">
         <v>36</v>
       </c>
       <c r="BS6" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BT6" t="n">
         <v>5.9</v>
       </c>
       <c r="BU6" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BV6" t="n">
         <v>22</v>
       </c>
       <c r="BW6" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BX6" t="n">
         <v>36</v>
       </c>
       <c r="BY6" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BZ6" t="n">
         <v>29</v>
       </c>
       <c r="CA6" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-15 04:55:19</t>
+          <t>2026-07-15 07:03:56</t>
         </is>
       </c>
     </row>
@@ -2130,10 +2130,10 @@
         <v>2.9</v>
       </c>
       <c r="G7" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="H7" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="I7" t="n">
         <v>2.66</v>
@@ -2142,37 +2142,37 @@
         <v>3.45</v>
       </c>
       <c r="K7" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L7" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="M7" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N7" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O7" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P7" t="n">
         <v>2.04</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="R7" t="n">
         <v>1.41</v>
       </c>
       <c r="S7" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="T7" t="n">
         <v>1.68</v>
       </c>
       <c r="U7" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V7" t="n">
         <v>1.6</v>
@@ -2184,7 +2184,7 @@
         <v>16.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Z7" t="n">
         <v>19.5</v>
@@ -2211,10 +2211,10 @@
         <v>15.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI7" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AJ7" t="n">
         <v>50</v>
@@ -2223,19 +2223,19 @@
         <v>38</v>
       </c>
       <c r="AL7" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM7" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AN7" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AO7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP7" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AQ7" t="n">
         <v>9.199999999999999</v>
@@ -2289,16 +2289,16 @@
         <v>15</v>
       </c>
       <c r="BH7" t="n">
-        <v>1000</v>
+        <v>3.7</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="BJ7" t="n">
         <v>9.4</v>
       </c>
       <c r="BK7" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
@@ -2328,29 +2328,29 @@
         <v>5.7</v>
       </c>
       <c r="BU7" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BV7" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BW7" t="n">
         <v>14.5</v>
       </c>
       <c r="BX7" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BY7" t="n">
         <v>24</v>
       </c>
       <c r="BZ7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="CA7" t="n">
         <v>20</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-15 04:55:19</t>
+          <t>2026-07-15 07:03:56</t>
         </is>
       </c>
     </row>
@@ -2390,19 +2390,19 @@
         <v>5.3</v>
       </c>
       <c r="I8" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="J8" t="n">
         <v>4.1</v>
       </c>
       <c r="K8" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L8" t="n">
         <v>1.36</v>
       </c>
       <c r="M8" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N8" t="n">
         <v>4.3</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-15 04:55:19</t>
+          <t>2026-07-15 07:03:56</t>
         </is>
       </c>
     </row>
@@ -2635,16 +2635,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="G9" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="H9" t="n">
         <v>1.87</v>
       </c>
       <c r="I9" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="J9" t="n">
         <v>3.65</v>
@@ -2659,7 +2659,7 @@
         <v>1.07</v>
       </c>
       <c r="N9" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="O9" t="n">
         <v>1.34</v>
@@ -2668,22 +2668,22 @@
         <v>1.93</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="R9" t="n">
         <v>1.32</v>
       </c>
       <c r="S9" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="T9" t="n">
         <v>1.86</v>
       </c>
       <c r="U9" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="V9" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="W9" t="n">
         <v>1.26</v>
@@ -2734,13 +2734,13 @@
         <v>70</v>
       </c>
       <c r="AM9" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN9" t="n">
         <v>85</v>
       </c>
       <c r="AO9" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AP9" t="n">
         <v>11.5</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-15 04:55:19</t>
+          <t>2026-07-15 07:03:56</t>
         </is>
       </c>
     </row>
@@ -2895,16 +2895,16 @@
         <v>1.3</v>
       </c>
       <c r="H10" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="I10" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="J10" t="n">
         <v>6.4</v>
       </c>
       <c r="K10" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="L10" t="n">
         <v>1.22</v>
@@ -2913,34 +2913,34 @@
         <v>1.02</v>
       </c>
       <c r="N10" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="O10" t="n">
         <v>1.13</v>
       </c>
       <c r="P10" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="R10" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="S10" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="T10" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="U10" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="V10" t="n">
         <v>1.08</v>
       </c>
       <c r="W10" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="X10" t="n">
         <v>48</v>
@@ -2952,13 +2952,13 @@
         <v>140</v>
       </c>
       <c r="AA10" t="n">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="AB10" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AC10" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AD10" t="n">
         <v>48</v>
@@ -2973,100 +2973,100 @@
         <v>14</v>
       </c>
       <c r="AH10" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AI10" t="n">
         <v>120</v>
       </c>
       <c r="AJ10" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AK10" t="n">
         <v>15.5</v>
       </c>
       <c r="AL10" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM10" t="n">
         <v>120</v>
       </c>
       <c r="AN10" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="AO10" t="n">
         <v>150</v>
       </c>
       <c r="AP10" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AQ10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BD10" t="n">
         <v>5.9</v>
       </c>
-      <c r="AR10" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>5.5</v>
-      </c>
       <c r="BE10" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="BG10" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BH10" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BJ10" t="n">
         <v>12</v>
       </c>
       <c r="BK10" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN10" t="n">
         <v>4.4</v>
@@ -3078,13 +3078,13 @@
         <v>7.2</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BR10" t="n">
         <v>19</v>
       </c>
       <c r="BS10" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BT10" t="n">
         <v>15.5</v>
@@ -3102,7 +3102,7 @@
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BZ10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-15 04:55:19</t>
+          <t>2026-07-15 07:03:56</t>
         </is>
       </c>
     </row>
@@ -3143,10 +3143,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="G11" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="H11" t="n">
         <v>7.2</v>
@@ -3167,10 +3167,10 @@
         <v>1.08</v>
       </c>
       <c r="N11" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="O11" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P11" t="n">
         <v>1.82</v>
@@ -3182,37 +3182,37 @@
         <v>1.31</v>
       </c>
       <c r="S11" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="T11" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="U11" t="n">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="V11" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W11" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="X11" t="n">
         <v>15</v>
       </c>
       <c r="Y11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Z11" t="n">
         <v>70</v>
       </c>
       <c r="AA11" t="n">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="AB11" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AC11" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AD11" t="n">
         <v>34</v>
@@ -3233,7 +3233,7 @@
         <v>140</v>
       </c>
       <c r="AJ11" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AK11" t="n">
         <v>19</v>
@@ -3242,13 +3242,13 @@
         <v>55</v>
       </c>
       <c r="AM11" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AN11" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AO11" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AP11" t="n">
         <v>10</v>
@@ -3257,25 +3257,25 @@
         <v>18</v>
       </c>
       <c r="AR11" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AS11" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AT11" t="n">
         <v>6.2</v>
       </c>
       <c r="AU11" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AV11" t="n">
         <v>21</v>
       </c>
       <c r="AW11" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AX11" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AY11" t="n">
         <v>8.800000000000001</v>
@@ -3284,7 +3284,7 @@
         <v>21</v>
       </c>
       <c r="BA11" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BB11" t="n">
         <v>11.5</v>
@@ -3293,16 +3293,16 @@
         <v>16</v>
       </c>
       <c r="BD11" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BE11" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BF11" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="BG11" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BH11" t="n">
         <v>3.3</v>
@@ -3311,16 +3311,16 @@
         <v>3</v>
       </c>
       <c r="BJ11" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK11" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BN11" t="n">
         <v>3.9</v>
@@ -3332,41 +3332,41 @@
         <v>10.5</v>
       </c>
       <c r="BQ11" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BT11" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BU11" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>13</v>
+        <v>9.6</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>13</v>
+        <v>2.78</v>
       </c>
       <c r="BZ11" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-15 04:55:19</t>
+          <t>2026-07-15 07:03:56</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-15.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-15.xlsx
@@ -857,16 +857,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.58</v>
+        <v>2.9</v>
       </c>
       <c r="G2" t="n">
-        <v>2.76</v>
+        <v>3</v>
       </c>
       <c r="H2" t="n">
-        <v>2.96</v>
+        <v>2.74</v>
       </c>
       <c r="I2" t="n">
-        <v>3.25</v>
+        <v>2.86</v>
       </c>
       <c r="J2" t="n">
         <v>3.2</v>
@@ -878,19 +878,19 @@
         <v>1.49</v>
       </c>
       <c r="M2" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N2" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="O2" t="n">
         <v>1.42</v>
       </c>
       <c r="P2" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R2" t="n">
         <v>1.27</v>
@@ -899,16 +899,16 @@
         <v>4.4</v>
       </c>
       <c r="T2" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="U2" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="V2" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="W2" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="X2" t="n">
         <v>11.5</v>
@@ -917,28 +917,28 @@
         <v>10.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB2" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AC2" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AF2" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AH2" t="n">
         <v>19.5</v>
@@ -947,7 +947,7 @@
         <v>70</v>
       </c>
       <c r="AJ2" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AK2" t="n">
         <v>40</v>
@@ -959,37 +959,37 @@
         <v>580</v>
       </c>
       <c r="AN2" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AO2" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AP2" t="n">
         <v>9.6</v>
       </c>
       <c r="AQ2" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AR2" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AS2" t="n">
         <v>36</v>
       </c>
       <c r="AT2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AU2" t="n">
         <v>6.4</v>
       </c>
       <c r="AV2" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AX2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AY2" t="n">
         <v>10.5</v>
@@ -1004,19 +1004,19 @@
         <v>32</v>
       </c>
       <c r="BC2" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BD2" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="BE2" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="BF2" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BG2" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="BH2" t="n">
         <v>3.15</v>
@@ -1028,59 +1028,59 @@
         <v>10.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>8</v>
+        <v>5.3</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BN2" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BO2" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BP2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BQ2" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BT2" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BU2" t="n">
         <v>5.1</v>
       </c>
       <c r="BV2" t="n">
+        <v>24</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>42</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BZ2" t="n">
         <v>1000</v>
       </c>
-      <c r="BW2" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>9</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>38</v>
-      </c>
       <c r="CA2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-15 07:03:56</t>
+          <t>2026-07-15 09:14:49</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="G3" t="n">
         <v>1.36</v>
@@ -1123,10 +1123,10 @@
         <v>15.5</v>
       </c>
       <c r="J3" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="K3" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="L3" t="n">
         <v>1.35</v>
@@ -1138,46 +1138,46 @@
         <v>4.3</v>
       </c>
       <c r="O3" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P3" t="n">
         <v>2.12</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="R3" t="n">
         <v>1.43</v>
       </c>
       <c r="S3" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="T3" t="n">
         <v>2.22</v>
       </c>
       <c r="U3" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="V3" t="n">
         <v>1.06</v>
       </c>
       <c r="W3" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="X3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y3" t="n">
         <v>38</v>
       </c>
       <c r="Z3" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AA3" t="n">
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC3" t="n">
         <v>14</v>
@@ -1213,7 +1213,7 @@
         <v>250</v>
       </c>
       <c r="AN3" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AO3" t="n">
         <v>460</v>
@@ -1240,10 +1240,10 @@
         <v>36</v>
       </c>
       <c r="AW3" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX3" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AY3" t="n">
         <v>9.4</v>
@@ -1255,7 +1255,7 @@
         <v>9</v>
       </c>
       <c r="BB3" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC3" t="n">
         <v>12.5</v>
@@ -1264,37 +1264,37 @@
         <v>15.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF3" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BG3" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BH3" t="n">
         <v>4</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="BJ3" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BK3" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN3" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BO3" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="BP3" t="n">
         <v>8</v>
@@ -1306,25 +1306,25 @@
         <v>28</v>
       </c>
       <c r="BS3" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="BT3" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BU3" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-15 07:03:56</t>
+          <t>2026-07-15 09:14:49</t>
         </is>
       </c>
     </row>
@@ -1365,230 +1365,230 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.58</v>
+        <v>1.68</v>
       </c>
       <c r="G4" t="n">
-        <v>1.64</v>
+        <v>1.74</v>
       </c>
       <c r="H4" t="n">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="I4" t="n">
-        <v>7</v>
+        <v>5.6</v>
       </c>
       <c r="J4" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K4" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="L4" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="M4" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N4" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="O4" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="P4" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="W4" t="n">
         <v>2.34</v>
       </c>
-      <c r="Q4" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="W4" t="n">
-        <v>2.52</v>
-      </c>
       <c r="X4" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="Y4" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="Z4" t="n">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="AA4" t="n">
         <v>900</v>
       </c>
       <c r="AB4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC4" t="n">
         <v>10.5</v>
       </c>
-      <c r="AC4" t="n">
-        <v>11</v>
-      </c>
       <c r="AD4" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="AE4" t="n">
-        <v>230</v>
+        <v>65</v>
       </c>
       <c r="AF4" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH4" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>19</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>32</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>17</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>40</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA4" t="n">
         <v>23</v>
       </c>
-      <c r="AI4" t="n">
-        <v>95</v>
-      </c>
-      <c r="AJ4" t="n">
+      <c r="BB4" t="n">
         <v>15</v>
       </c>
-      <c r="AK4" t="n">
-        <v>17</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>700</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>110</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>5.5</v>
-      </c>
       <c r="BC4" t="n">
-        <v>5.7</v>
+        <v>14</v>
       </c>
       <c r="BD4" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="BE4" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="BF4" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="BG4" t="n">
-        <v>7.8</v>
+        <v>34</v>
       </c>
       <c r="BH4" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.92</v>
+        <v>3.35</v>
       </c>
       <c r="BJ4" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>4</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>11</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>23</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>5</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>40</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>44</v>
+      </c>
+      <c r="BY4" t="n">
         <v>8.800000000000001</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>3</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>10</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>5</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>24</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>11</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>60</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BX4" t="n">
-        <v>60</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>2.8</v>
       </c>
       <c r="BZ4" t="n">
         <v>16</v>
       </c>
       <c r="CA4" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-15 07:03:56</t>
+          <t>2026-07-15 09:14:49</t>
         </is>
       </c>
     </row>
@@ -1622,34 +1622,34 @@
         <v>2.5</v>
       </c>
       <c r="G5" t="n">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="H5" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="I5" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="J5" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="K5" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="L5" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="M5" t="n">
         <v>1.14</v>
       </c>
       <c r="N5" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="O5" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="P5" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="Q5" t="n">
         <v>2.74</v>
@@ -1658,64 +1658,64 @@
         <v>1.19</v>
       </c>
       <c r="S5" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="T5" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="U5" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="V5" t="n">
         <v>1.34</v>
       </c>
       <c r="W5" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="X5" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="Y5" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Z5" t="n">
-        <v>90</v>
+        <v>28</v>
       </c>
       <c r="AA5" t="n">
-        <v>900</v>
+        <v>170</v>
       </c>
       <c r="AB5" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC5" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AE5" t="n">
-        <v>290</v>
+        <v>150</v>
       </c>
       <c r="AF5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AG5" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH5" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AI5" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="AJ5" t="n">
-        <v>170</v>
+        <v>46</v>
       </c>
       <c r="AK5" t="n">
-        <v>95</v>
+        <v>46</v>
       </c>
       <c r="AL5" t="n">
-        <v>460</v>
+        <v>160</v>
       </c>
       <c r="AM5" t="n">
         <v>500</v>
@@ -1727,28 +1727,28 @@
         <v>600</v>
       </c>
       <c r="AP5" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AQ5" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AR5" t="n">
         <v>19</v>
       </c>
       <c r="AS5" t="n">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="AT5" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AU5" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AV5" t="n">
         <v>14</v>
       </c>
       <c r="AW5" t="n">
-        <v>9.4</v>
+        <v>40</v>
       </c>
       <c r="AX5" t="n">
         <v>11.5</v>
@@ -1757,92 +1757,92 @@
         <v>10</v>
       </c>
       <c r="AZ5" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BA5" t="n">
-        <v>8.800000000000001</v>
+        <v>55</v>
       </c>
       <c r="BB5" t="n">
-        <v>8.4</v>
+        <v>27</v>
       </c>
       <c r="BC5" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="BD5" t="n">
-        <v>8.6</v>
+        <v>44</v>
       </c>
       <c r="BE5" t="n">
-        <v>9.4</v>
+        <v>28</v>
       </c>
       <c r="BF5" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="BG5" t="n">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="BH5" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="BJ5" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BK5" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BN5" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="BP5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BQ5" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT5" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BU5" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BV5" t="n">
         <v>38</v>
       </c>
       <c r="BW5" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="CA5" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-15 07:03:56</t>
+          <t>2026-07-15 09:14:49</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="G6" t="n">
         <v>2.9</v>
@@ -1882,61 +1882,61 @@
         <v>2.74</v>
       </c>
       <c r="I6" t="n">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="J6" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K6" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="L6" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="M6" t="n">
         <v>1.07</v>
       </c>
       <c r="N6" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="O6" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="P6" t="n">
         <v>1.96</v>
       </c>
       <c r="Q6" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R6" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S6" t="n">
         <v>3.6</v>
       </c>
       <c r="T6" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="U6" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="V6" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="W6" t="n">
         <v>1.53</v>
       </c>
       <c r="X6" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z6" t="n">
         <v>19.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AB6" t="n">
         <v>12</v>
@@ -1948,13 +1948,13 @@
         <v>13.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AF6" t="n">
         <v>19.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AH6" t="n">
         <v>17</v>
@@ -1963,13 +1963,13 @@
         <v>46</v>
       </c>
       <c r="AJ6" t="n">
-        <v>120</v>
+        <v>48</v>
       </c>
       <c r="AK6" t="n">
         <v>32</v>
       </c>
       <c r="AL6" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AM6" t="n">
         <v>580</v>
@@ -1978,70 +1978,70 @@
         <v>29</v>
       </c>
       <c r="AO6" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AP6" t="n">
         <v>11.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AR6" t="n">
         <v>15.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>7.6</v>
+        <v>30</v>
       </c>
       <c r="AT6" t="n">
         <v>10</v>
       </c>
       <c r="AU6" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AV6" t="n">
         <v>11</v>
       </c>
       <c r="AW6" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="AX6" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AY6" t="n">
         <v>11</v>
       </c>
       <c r="AZ6" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA6" t="n">
-        <v>7.6</v>
+        <v>32</v>
       </c>
       <c r="BB6" t="n">
-        <v>7.6</v>
+        <v>30</v>
       </c>
       <c r="BC6" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="BD6" t="n">
-        <v>7.6</v>
+        <v>30</v>
       </c>
       <c r="BE6" t="n">
-        <v>8.199999999999999</v>
+        <v>65</v>
       </c>
       <c r="BF6" t="n">
         <v>21</v>
       </c>
       <c r="BG6" t="n">
-        <v>7.2</v>
+        <v>18</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="BJ6" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BK6" t="n">
         <v>5.4</v>
@@ -2050,7 +2050,7 @@
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BN6" t="n">
         <v>6</v>
@@ -2062,13 +2062,13 @@
         <v>22</v>
       </c>
       <c r="BQ6" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BR6" t="n">
         <v>36</v>
       </c>
       <c r="BS6" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT6" t="n">
         <v>5.9</v>
@@ -2077,26 +2077,26 @@
         <v>5</v>
       </c>
       <c r="BV6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BW6" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BX6" t="n">
         <v>36</v>
       </c>
       <c r="BY6" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ6" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="CA6" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-15 07:03:56</t>
+          <t>2026-07-15 09:14:49</t>
         </is>
       </c>
     </row>
@@ -2127,16 +2127,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="G7" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="H7" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="I7" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="J7" t="n">
         <v>3.45</v>
@@ -2145,106 +2145,106 @@
         <v>3.75</v>
       </c>
       <c r="L7" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="M7" t="n">
         <v>1.06</v>
       </c>
       <c r="N7" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O7" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P7" t="n">
         <v>2.04</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="R7" t="n">
         <v>1.41</v>
       </c>
       <c r="S7" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T7" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="U7" t="n">
         <v>2.24</v>
       </c>
       <c r="V7" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="W7" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="X7" t="n">
         <v>16.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Z7" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AA7" t="n">
         <v>38</v>
       </c>
       <c r="AB7" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AC7" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD7" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AE7" t="n">
         <v>32</v>
       </c>
       <c r="AF7" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AG7" t="n">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="AH7" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AI7" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AJ7" t="n">
         <v>50</v>
       </c>
       <c r="AK7" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AL7" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AM7" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AN7" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AO7" t="n">
         <v>23</v>
       </c>
       <c r="AP7" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AQ7" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AR7" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.03</v>
+        <v>26</v>
       </c>
       <c r="AT7" t="n">
         <v>10</v>
@@ -2259,7 +2259,7 @@
         <v>20</v>
       </c>
       <c r="AX7" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AY7" t="n">
         <v>10</v>
@@ -2268,19 +2268,19 @@
         <v>12.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.03</v>
+        <v>27</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.03</v>
+        <v>30</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.03</v>
+        <v>23</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.03</v>
+        <v>29</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.03</v>
+        <v>55</v>
       </c>
       <c r="BF7" t="n">
         <v>20</v>
@@ -2289,16 +2289,16 @@
         <v>15</v>
       </c>
       <c r="BH7" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.98</v>
+        <v>3.15</v>
       </c>
       <c r="BJ7" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK7" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
@@ -2310,10 +2310,10 @@
         <v>6.2</v>
       </c>
       <c r="BO7" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BP7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BQ7" t="n">
         <v>17.5</v>
@@ -2325,32 +2325,32 @@
         <v>26</v>
       </c>
       <c r="BT7" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BU7" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BV7" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BW7" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="BX7" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BY7" t="n">
         <v>24</v>
       </c>
       <c r="BZ7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="CA7" t="n">
         <v>20</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-15 07:03:56</t>
+          <t>2026-07-15 09:14:49</t>
         </is>
       </c>
     </row>
@@ -2411,16 +2411,16 @@
         <v>1.27</v>
       </c>
       <c r="P8" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="R8" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S8" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="T8" t="n">
         <v>1.82</v>
@@ -2429,7 +2429,7 @@
         <v>2.08</v>
       </c>
       <c r="V8" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W8" t="n">
         <v>2.34</v>
@@ -2438,25 +2438,25 @@
         <v>18</v>
       </c>
       <c r="Y8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Z8" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AA8" t="n">
         <v>160</v>
       </c>
       <c r="AB8" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AC8" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AD8" t="n">
         <v>22</v>
       </c>
       <c r="AE8" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AF8" t="n">
         <v>11</v>
@@ -2465,82 +2465,82 @@
         <v>10.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI8" t="n">
         <v>85</v>
       </c>
       <c r="AJ8" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AK8" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AL8" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AM8" t="n">
         <v>120</v>
       </c>
       <c r="AN8" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AO8" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AP8" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.03</v>
+        <v>34</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AT8" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AU8" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV8" t="n">
+        <v>19</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>46</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>42</v>
+      </c>
+      <c r="BB8" t="n">
         <v>15</v>
       </c>
-      <c r="AW8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AZ8" t="n">
+      <c r="BC8" t="n">
         <v>15</v>
       </c>
-      <c r="BA8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>13.5</v>
-      </c>
       <c r="BD8" t="n">
-        <v>1.03</v>
+        <v>24</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="BF8" t="n">
         <v>8</v>
       </c>
       <c r="BG8" t="n">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="BH8" t="n">
         <v>3.8</v>
@@ -2549,7 +2549,7 @@
         <v>3</v>
       </c>
       <c r="BJ8" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK8" t="n">
         <v>7.2</v>
@@ -2576,7 +2576,7 @@
         <v>24</v>
       </c>
       <c r="BS8" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BT8" t="n">
         <v>9</v>
@@ -2597,14 +2597,14 @@
         <v>34</v>
       </c>
       <c r="BZ8" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="CA8" t="n">
         <v>13</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-15 07:03:56</t>
+          <t>2026-07-15 09:14:49</t>
         </is>
       </c>
     </row>
@@ -2635,31 +2635,31 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="G9" t="n">
         <v>4.9</v>
       </c>
       <c r="H9" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="I9" t="n">
         <v>1.95</v>
       </c>
       <c r="J9" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K9" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L9" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="M9" t="n">
         <v>1.07</v>
       </c>
       <c r="N9" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="O9" t="n">
         <v>1.34</v>
@@ -2668,16 +2668,16 @@
         <v>1.93</v>
       </c>
       <c r="Q9" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="R9" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S9" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="T9" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="U9" t="n">
         <v>2</v>
@@ -2686,22 +2686,22 @@
         <v>2.04</v>
       </c>
       <c r="W9" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="X9" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Y9" t="n">
         <v>10</v>
       </c>
       <c r="Z9" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AA9" t="n">
         <v>23</v>
       </c>
       <c r="AB9" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AC9" t="n">
         <v>10.5</v>
@@ -2716,10 +2716,10 @@
         <v>42</v>
       </c>
       <c r="AG9" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AH9" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AI9" t="n">
         <v>40</v>
@@ -2740,64 +2740,64 @@
         <v>85</v>
       </c>
       <c r="AO9" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AP9" t="n">
         <v>11.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AR9" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AS9" t="n">
-        <v>15</v>
+        <v>19.5</v>
       </c>
       <c r="AT9" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AU9" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AV9" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="AW9" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="AY9" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AZ9" t="n">
-        <v>14</v>
+        <v>17.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="BF9" t="n">
-        <v>46</v>
+        <v>5.1</v>
       </c>
       <c r="BG9" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BH9" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BI9" t="n">
         <v>2.64</v>
@@ -2815,7 +2815,7 @@
         <v>1.01</v>
       </c>
       <c r="BN9" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BO9" t="n">
         <v>6</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-15 07:03:56</t>
+          <t>2026-07-15 09:14:49</t>
         </is>
       </c>
     </row>
@@ -2889,169 +2889,169 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="G10" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="H10" t="n">
         <v>11.5</v>
       </c>
       <c r="I10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J10" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="K10" t="n">
         <v>7.8</v>
       </c>
       <c r="L10" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="M10" t="n">
         <v>1.02</v>
       </c>
       <c r="N10" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="O10" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="P10" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="R10" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="S10" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="T10" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="U10" t="n">
-        <v>2.06</v>
+        <v>1.99</v>
       </c>
       <c r="V10" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="W10" t="n">
         <v>4.3</v>
       </c>
       <c r="X10" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="Y10" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="Z10" t="n">
         <v>140</v>
       </c>
       <c r="AA10" t="n">
-        <v>420</v>
+        <v>480</v>
       </c>
       <c r="AB10" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AC10" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AD10" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AE10" t="n">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="AF10" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AG10" t="n">
         <v>14</v>
       </c>
       <c r="AH10" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AI10" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AJ10" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AK10" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AL10" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AM10" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AN10" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AO10" t="n">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="AP10" t="n">
-        <v>6.2</v>
+        <v>4.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>6.4</v>
+        <v>4.6</v>
       </c>
       <c r="AR10" t="n">
-        <v>6.8</v>
+        <v>4.9</v>
       </c>
       <c r="AS10" t="n">
-        <v>2.34</v>
+        <v>5</v>
       </c>
       <c r="AT10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AW10" t="n">
         <v>4.9</v>
       </c>
-      <c r="AU10" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>6.8</v>
-      </c>
       <c r="AX10" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="AY10" t="n">
-        <v>4.7</v>
+        <v>3.9</v>
       </c>
       <c r="AZ10" t="n">
-        <v>5.8</v>
+        <v>4.4</v>
       </c>
       <c r="BA10" t="n">
-        <v>6.8</v>
+        <v>4.8</v>
       </c>
       <c r="BB10" t="n">
-        <v>4.6</v>
+        <v>3.75</v>
       </c>
       <c r="BC10" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG10" t="n">
         <v>4.9</v>
       </c>
-      <c r="BD10" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BH10" t="n">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="BI10" t="n">
         <v>3.7</v>
@@ -3060,7 +3060,7 @@
         <v>12</v>
       </c>
       <c r="BK10" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
@@ -3069,40 +3069,40 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BN10" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BO10" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BP10" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BR10" t="n">
         <v>19</v>
       </c>
       <c r="BS10" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BT10" t="n">
         <v>15.5</v>
       </c>
       <c r="BU10" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-15 07:03:56</t>
+          <t>2026-07-15 09:14:49</t>
         </is>
       </c>
     </row>
@@ -3143,34 +3143,34 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="G11" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="H11" t="n">
         <v>7.2</v>
       </c>
       <c r="I11" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="J11" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K11" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L11" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="M11" t="n">
         <v>1.08</v>
       </c>
       <c r="N11" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O11" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P11" t="n">
         <v>1.82</v>
@@ -3179,34 +3179,34 @@
         <v>2.14</v>
       </c>
       <c r="R11" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S11" t="n">
         <v>3.95</v>
       </c>
       <c r="T11" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="U11" t="n">
         <v>1.84</v>
       </c>
       <c r="V11" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W11" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="X11" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Z11" t="n">
         <v>70</v>
       </c>
       <c r="AA11" t="n">
-        <v>280</v>
+        <v>340</v>
       </c>
       <c r="AB11" t="n">
         <v>8.199999999999999</v>
@@ -3221,7 +3221,7 @@
         <v>150</v>
       </c>
       <c r="AF11" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG11" t="n">
         <v>10.5</v>
@@ -3236,7 +3236,7 @@
         <v>15.5</v>
       </c>
       <c r="AK11" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AL11" t="n">
         <v>55</v>
@@ -3245,10 +3245,10 @@
         <v>190</v>
       </c>
       <c r="AN11" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AO11" t="n">
-        <v>220</v>
+        <v>250</v>
       </c>
       <c r="AP11" t="n">
         <v>10</v>
@@ -3263,7 +3263,7 @@
         <v>7.2</v>
       </c>
       <c r="AT11" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AU11" t="n">
         <v>8.4</v>
@@ -3272,7 +3272,7 @@
         <v>21</v>
       </c>
       <c r="AW11" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AX11" t="n">
         <v>7.6</v>
@@ -3296,22 +3296,22 @@
         <v>6.4</v>
       </c>
       <c r="BE11" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BF11" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="BG11" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BH11" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BI11" t="n">
         <v>3</v>
       </c>
       <c r="BJ11" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BK11" t="n">
         <v>7.2</v>
@@ -3320,53 +3320,53 @@
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BN11" t="n">
         <v>3.9</v>
       </c>
       <c r="BO11" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BP11" t="n">
         <v>10.5</v>
       </c>
       <c r="BQ11" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BT11" t="n">
         <v>10.5</v>
       </c>
       <c r="BU11" t="n">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>9.6</v>
+        <v>3.05</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>2.78</v>
+        <v>14.5</v>
       </c>
       <c r="BZ11" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="CA11" t="n">
         <v>10</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-15 07:03:56</t>
+          <t>2026-07-15 09:14:49</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-15.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-15.xlsx
@@ -857,112 +857,112 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="G2" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="H2" t="n">
-        <v>2.74</v>
+        <v>2.58</v>
       </c>
       <c r="I2" t="n">
-        <v>2.86</v>
+        <v>2.7</v>
       </c>
       <c r="J2" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K2" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="L2" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="M2" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N2" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="O2" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P2" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="Q2" t="n">
         <v>2.3</v>
       </c>
       <c r="R2" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S2" t="n">
         <v>4.4</v>
       </c>
       <c r="T2" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="U2" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="V2" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="W2" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="X2" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y2" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>44</v>
+      </c>
+      <c r="AB2" t="n">
         <v>10.5</v>
       </c>
-      <c r="Z2" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AA2" t="n">
+      <c r="AC2" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI2" t="n">
         <v>55</v>
       </c>
-      <c r="AB2" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AE2" t="n">
+      <c r="AJ2" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK2" t="n">
         <v>44</v>
       </c>
-      <c r="AF2" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ2" t="n">
+      <c r="AL2" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN2" t="n">
         <v>55</v>
       </c>
-      <c r="AK2" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>40</v>
-      </c>
       <c r="AO2" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AP2" t="n">
         <v>9.6</v>
@@ -971,116 +971,116 @@
         <v>8.4</v>
       </c>
       <c r="AR2" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AS2" t="n">
+        <v>30</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>27</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>18</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>46</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>48</v>
+      </c>
+      <c r="BC2" t="n">
         <v>36</v>
       </c>
-      <c r="AT2" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>24</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>16</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>42</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>32</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>27</v>
-      </c>
       <c r="BD2" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="BE2" t="n">
         <v>90</v>
       </c>
       <c r="BF2" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="BG2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="BJ2" t="n">
         <v>10.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN2" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BO2" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BP2" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="BQ2" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR2" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BS2" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT2" t="n">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="BU2" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="BV2" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BW2" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BX2" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BY2" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="CA2" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-15 09:14:49</t>
+          <t>2026-07-15 11:24:42</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="G3" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="H3" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="I3" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="J3" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="K3" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="L3" t="n">
         <v>1.35</v>
@@ -1147,31 +1147,31 @@
         <v>1.79</v>
       </c>
       <c r="R3" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S3" t="n">
         <v>3</v>
       </c>
       <c r="T3" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="U3" t="n">
         <v>1.66</v>
       </c>
       <c r="V3" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W3" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="X3" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Y3" t="n">
         <v>38</v>
       </c>
       <c r="Z3" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AA3" t="n">
         <v>1000</v>
@@ -1180,13 +1180,13 @@
         <v>8.4</v>
       </c>
       <c r="AC3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AD3" t="n">
         <v>50</v>
       </c>
       <c r="AE3" t="n">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="AF3" t="n">
         <v>7.6</v>
@@ -1195,7 +1195,7 @@
         <v>11.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AI3" t="n">
         <v>220</v>
@@ -1207,55 +1207,55 @@
         <v>16</v>
       </c>
       <c r="AL3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AM3" t="n">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="AN3" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AO3" t="n">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="AP3" t="n">
         <v>16</v>
       </c>
       <c r="AQ3" t="n">
-        <v>9.199999999999999</v>
+        <v>24</v>
       </c>
       <c r="AR3" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AS3" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AT3" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AU3" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AV3" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AW3" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AX3" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AY3" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ3" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA3" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BA3" t="n">
-        <v>9</v>
-      </c>
       <c r="BB3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BC3" t="n">
         <v>12.5</v>
@@ -1264,25 +1264,25 @@
         <v>15.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BF3" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BG3" t="n">
-        <v>10.5</v>
+        <v>15</v>
       </c>
       <c r="BH3" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BI3" t="n">
         <v>3.1</v>
       </c>
       <c r="BJ3" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
@@ -1291,16 +1291,16 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BN3" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BO3" t="n">
-        <v>2.96</v>
+        <v>3.2</v>
       </c>
       <c r="BP3" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BQ3" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="BR3" t="n">
         <v>28</v>
@@ -1309,16 +1309,16 @@
         <v>7.4</v>
       </c>
       <c r="BT3" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BU3" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-15 09:14:49</t>
+          <t>2026-07-15 11:24:42</t>
         </is>
       </c>
     </row>
@@ -1365,16 +1365,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="G4" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="H4" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="I4" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="J4" t="n">
         <v>4.1</v>
@@ -1386,46 +1386,46 @@
         <v>1.3</v>
       </c>
       <c r="M4" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N4" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O4" t="n">
         <v>1.21</v>
       </c>
       <c r="P4" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="R4" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="S4" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="T4" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="U4" t="n">
         <v>2.22</v>
       </c>
       <c r="V4" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W4" t="n">
         <v>2.34</v>
       </c>
       <c r="X4" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y4" t="n">
         <v>25</v>
       </c>
-      <c r="Y4" t="n">
-        <v>24</v>
-      </c>
       <c r="Z4" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AA4" t="n">
         <v>900</v>
@@ -1440,7 +1440,7 @@
         <v>21</v>
       </c>
       <c r="AE4" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AF4" t="n">
         <v>12.5</v>
@@ -1455,40 +1455,40 @@
         <v>60</v>
       </c>
       <c r="AJ4" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AK4" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AL4" t="n">
         <v>32</v>
       </c>
       <c r="AM4" t="n">
-        <v>90</v>
+        <v>200</v>
       </c>
       <c r="AN4" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AO4" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AP4" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AQ4" t="n">
         <v>19</v>
       </c>
       <c r="AR4" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AS4" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AT4" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU4" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AV4" t="n">
         <v>17</v>
@@ -1497,7 +1497,7 @@
         <v>40</v>
       </c>
       <c r="AX4" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY4" t="n">
         <v>8.800000000000001</v>
@@ -1515,13 +1515,13 @@
         <v>14</v>
       </c>
       <c r="BD4" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="BE4" t="n">
         <v>29</v>
       </c>
       <c r="BF4" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BG4" t="n">
         <v>34</v>
@@ -1560,7 +1560,7 @@
         <v>23</v>
       </c>
       <c r="BS4" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BT4" t="n">
         <v>9.199999999999999</v>
@@ -1569,26 +1569,26 @@
         <v>5</v>
       </c>
       <c r="BV4" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BW4" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX4" t="n">
         <v>44</v>
       </c>
       <c r="BY4" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BZ4" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="CA4" t="n">
         <v>6.4</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-15 09:14:49</t>
+          <t>2026-07-15 11:24:42</t>
         </is>
       </c>
     </row>
@@ -1622,97 +1622,97 @@
         <v>2.5</v>
       </c>
       <c r="G5" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="H5" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="I5" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="J5" t="n">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="K5" t="n">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="L5" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="M5" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N5" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="O5" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="P5" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="R5" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="T5" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="U5" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="V5" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="W5" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="X5" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="Y5" t="n">
         <v>11</v>
       </c>
       <c r="Z5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AA5" t="n">
-        <v>170</v>
+        <v>500</v>
       </c>
       <c r="AB5" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AC5" t="n">
         <v>6.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AE5" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AF5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AG5" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AI5" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="AJ5" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AK5" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AL5" t="n">
         <v>160</v>
@@ -1721,34 +1721,34 @@
         <v>500</v>
       </c>
       <c r="AN5" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AO5" t="n">
         <v>600</v>
       </c>
       <c r="AP5" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AQ5" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR5" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AS5" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="AT5" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AU5" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="AV5" t="n">
         <v>14</v>
       </c>
       <c r="AW5" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AX5" t="n">
         <v>11.5</v>
@@ -1757,7 +1757,7 @@
         <v>10</v>
       </c>
       <c r="AZ5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BA5" t="n">
         <v>55</v>
@@ -1778,25 +1778,25 @@
         <v>30</v>
       </c>
       <c r="BG5" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="BH5" t="n">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="BJ5" t="n">
         <v>12</v>
       </c>
       <c r="BK5" t="n">
-        <v>7.6</v>
+        <v>6</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BN5" t="n">
         <v>5.2</v>
@@ -1808,41 +1808,41 @@
         <v>22</v>
       </c>
       <c r="BQ5" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BR5" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BS5" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BT5" t="n">
         <v>7</v>
       </c>
       <c r="BU5" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BV5" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BW5" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BZ5" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-15 09:14:49</t>
+          <t>2026-07-15 11:24:42</t>
         </is>
       </c>
     </row>
@@ -1873,22 +1873,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="G6" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="H6" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="I6" t="n">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="J6" t="n">
         <v>3.35</v>
       </c>
       <c r="K6" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L6" t="n">
         <v>1.44</v>
@@ -1897,34 +1897,34 @@
         <v>1.07</v>
       </c>
       <c r="N6" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="O6" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P6" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R6" t="n">
         <v>1.35</v>
       </c>
       <c r="S6" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="T6" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="U6" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="V6" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W6" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="X6" t="n">
         <v>13.5</v>
@@ -1933,22 +1933,22 @@
         <v>12</v>
       </c>
       <c r="Z6" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AA6" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AB6" t="n">
         <v>12</v>
       </c>
       <c r="AC6" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD6" t="n">
         <v>13.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF6" t="n">
         <v>19.5</v>
@@ -1966,7 +1966,7 @@
         <v>48</v>
       </c>
       <c r="AK6" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AL6" t="n">
         <v>44</v>
@@ -1978,7 +1978,7 @@
         <v>29</v>
       </c>
       <c r="AO6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AP6" t="n">
         <v>11.5</v>
@@ -2017,13 +2017,13 @@
         <v>32</v>
       </c>
       <c r="BB6" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BC6" t="n">
         <v>25</v>
       </c>
       <c r="BD6" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BE6" t="n">
         <v>65</v>
@@ -2032,71 +2032,71 @@
         <v>21</v>
       </c>
       <c r="BG6" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.86</v>
+        <v>2.74</v>
       </c>
       <c r="BJ6" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="BN6" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BO6" t="n">
         <v>5.1</v>
       </c>
       <c r="BP6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BQ6" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="BR6" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BS6" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT6" t="n">
         <v>5.9</v>
       </c>
       <c r="BU6" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BV6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BW6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BX6" t="n">
         <v>36</v>
       </c>
       <c r="BY6" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BZ6" t="n">
         <v>30</v>
       </c>
       <c r="CA6" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-15 09:14:49</t>
+          <t>2026-07-15 11:24:42</t>
         </is>
       </c>
     </row>
@@ -2127,10 +2127,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="G7" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="H7" t="n">
         <v>2.54</v>
@@ -2145,31 +2145,31 @@
         <v>3.75</v>
       </c>
       <c r="L7" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="M7" t="n">
         <v>1.06</v>
       </c>
       <c r="N7" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O7" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P7" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="R7" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S7" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="T7" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="U7" t="n">
         <v>2.24</v>
@@ -2184,7 +2184,7 @@
         <v>16.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Z7" t="n">
         <v>19</v>
@@ -2193,7 +2193,7 @@
         <v>38</v>
       </c>
       <c r="AB7" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AC7" t="n">
         <v>8.800000000000001</v>
@@ -2223,13 +2223,13 @@
         <v>32</v>
       </c>
       <c r="AL7" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="AM7" t="n">
         <v>95</v>
       </c>
       <c r="AN7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO7" t="n">
         <v>23</v>
@@ -2244,7 +2244,7 @@
         <v>15.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AT7" t="n">
         <v>10</v>
@@ -2289,22 +2289,22 @@
         <v>15</v>
       </c>
       <c r="BH7" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BJ7" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BK7" t="n">
-        <v>8</v>
+        <v>5.8</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BN7" t="n">
         <v>6.2</v>
@@ -2316,13 +2316,13 @@
         <v>22</v>
       </c>
       <c r="BQ7" t="n">
-        <v>17.5</v>
+        <v>8.4</v>
       </c>
       <c r="BR7" t="n">
         <v>34</v>
       </c>
       <c r="BS7" t="n">
-        <v>26</v>
+        <v>9.6</v>
       </c>
       <c r="BT7" t="n">
         <v>5.8</v>
@@ -2334,23 +2334,23 @@
         <v>19.5</v>
       </c>
       <c r="BW7" t="n">
-        <v>16.5</v>
+        <v>8</v>
       </c>
       <c r="BX7" t="n">
         <v>32</v>
       </c>
       <c r="BY7" t="n">
-        <v>24</v>
+        <v>9.4</v>
       </c>
       <c r="BZ7" t="n">
         <v>25</v>
       </c>
       <c r="CA7" t="n">
-        <v>20</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-15 09:14:49</t>
+          <t>2026-07-15 11:24:42</t>
         </is>
       </c>
     </row>
@@ -2384,22 +2384,22 @@
         <v>1.68</v>
       </c>
       <c r="G8" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="H8" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="I8" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="J8" t="n">
         <v>4.1</v>
       </c>
       <c r="K8" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L8" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="M8" t="n">
         <v>1.05</v>
@@ -2426,13 +2426,13 @@
         <v>1.82</v>
       </c>
       <c r="U8" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V8" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W8" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="X8" t="n">
         <v>18</v>
@@ -2483,7 +2483,7 @@
         <v>120</v>
       </c>
       <c r="AN8" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO8" t="n">
         <v>95</v>
@@ -2492,7 +2492,7 @@
         <v>15.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AR8" t="n">
         <v>34</v>
@@ -2510,7 +2510,7 @@
         <v>19</v>
       </c>
       <c r="AW8" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AX8" t="n">
         <v>9.6</v>
@@ -2522,7 +2522,7 @@
         <v>17.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BB8" t="n">
         <v>15</v>
@@ -2534,13 +2534,13 @@
         <v>24</v>
       </c>
       <c r="BE8" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BF8" t="n">
         <v>8</v>
       </c>
       <c r="BG8" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="BH8" t="n">
         <v>3.8</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-15 09:14:49</t>
+          <t>2026-07-15 11:24:42</t>
         </is>
       </c>
     </row>
@@ -2635,22 +2635,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="G9" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H9" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="I9" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="J9" t="n">
         <v>3.7</v>
       </c>
       <c r="K9" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L9" t="n">
         <v>1.43</v>
@@ -2683,7 +2683,7 @@
         <v>2</v>
       </c>
       <c r="V9" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="W9" t="n">
         <v>1.27</v>
@@ -2701,7 +2701,7 @@
         <v>23</v>
       </c>
       <c r="AB9" t="n">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="AC9" t="n">
         <v>10.5</v>
@@ -2719,7 +2719,7 @@
         <v>19</v>
       </c>
       <c r="AH9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI9" t="n">
         <v>40</v>
@@ -2752,7 +2752,7 @@
         <v>10</v>
       </c>
       <c r="AS9" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AT9" t="n">
         <v>13.5</v>
@@ -2767,7 +2767,7 @@
         <v>18</v>
       </c>
       <c r="AX9" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="AY9" t="n">
         <v>15.5</v>
@@ -2776,22 +2776,22 @@
         <v>17.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BB9" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BC9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BE9" t="n">
         <v>5</v>
       </c>
-      <c r="BD9" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>5.2</v>
-      </c>
       <c r="BF9" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BG9" t="n">
         <v>12.5</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-15 09:14:49</t>
+          <t>2026-07-15 11:24:42</t>
         </is>
       </c>
     </row>
@@ -2889,94 +2889,94 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="G10" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="H10" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="I10" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="J10" t="n">
         <v>6.2</v>
       </c>
       <c r="K10" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="L10" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="M10" t="n">
         <v>1.02</v>
       </c>
       <c r="N10" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="O10" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="P10" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="R10" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="S10" t="n">
-        <v>2.06</v>
+        <v>1.98</v>
       </c>
       <c r="T10" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="U10" t="n">
-        <v>1.99</v>
+        <v>2.12</v>
       </c>
       <c r="V10" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="W10" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="X10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Y10" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="Z10" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AA10" t="n">
-        <v>480</v>
+        <v>350</v>
       </c>
       <c r="AB10" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AC10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AD10" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AE10" t="n">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="AF10" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AG10" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AI10" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AJ10" t="n">
         <v>12</v>
@@ -2985,118 +2985,118 @@
         <v>14.5</v>
       </c>
       <c r="AL10" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AM10" t="n">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="AN10" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="AO10" t="n">
-        <v>180</v>
+        <v>140</v>
       </c>
       <c r="AP10" t="n">
-        <v>4.5</v>
+        <v>6.4</v>
       </c>
       <c r="AQ10" t="n">
-        <v>4.6</v>
+        <v>6.6</v>
       </c>
       <c r="AR10" t="n">
-        <v>4.9</v>
+        <v>7.2</v>
       </c>
       <c r="AS10" t="n">
-        <v>5</v>
+        <v>7.4</v>
       </c>
       <c r="AT10" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="AU10" t="n">
-        <v>3.95</v>
+        <v>14</v>
       </c>
       <c r="AV10" t="n">
-        <v>4.6</v>
+        <v>6.6</v>
       </c>
       <c r="AW10" t="n">
-        <v>4.9</v>
+        <v>7.2</v>
       </c>
       <c r="AX10" t="n">
-        <v>3.6</v>
+        <v>9.4</v>
       </c>
       <c r="AY10" t="n">
-        <v>3.9</v>
+        <v>10</v>
       </c>
       <c r="AZ10" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BI10" t="n">
         <v>4.4</v>
       </c>
-      <c r="BA10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>3</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BH10" t="n">
+      <c r="BJ10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK10" t="n">
         <v>5.5</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>12</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>5.8</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BN10" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BO10" t="n">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="BP10" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.3</v>
+        <v>5.6</v>
       </c>
       <c r="BR10" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BS10" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BT10" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BU10" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-15 09:14:49</t>
+          <t>2026-07-15 11:24:42</t>
         </is>
       </c>
     </row>
@@ -3146,13 +3146,13 @@
         <v>1.58</v>
       </c>
       <c r="G11" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="H11" t="n">
         <v>7.2</v>
       </c>
       <c r="I11" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="J11" t="n">
         <v>4</v>
@@ -3167,49 +3167,49 @@
         <v>1.08</v>
       </c>
       <c r="N11" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="O11" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P11" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S11" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="T11" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="U11" t="n">
-        <v>1.84</v>
+        <v>1.73</v>
       </c>
       <c r="V11" t="n">
         <v>1.15</v>
       </c>
       <c r="W11" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="X11" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Z11" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AA11" t="n">
-        <v>340</v>
+        <v>300</v>
       </c>
       <c r="AB11" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AC11" t="n">
         <v>10</v>
@@ -3230,10 +3230,10 @@
         <v>29</v>
       </c>
       <c r="AI11" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AJ11" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AK11" t="n">
         <v>22</v>
@@ -3242,88 +3242,88 @@
         <v>55</v>
       </c>
       <c r="AM11" t="n">
-        <v>190</v>
+        <v>240</v>
       </c>
       <c r="AN11" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AO11" t="n">
         <v>250</v>
       </c>
       <c r="AP11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ11" t="n">
         <v>18</v>
       </c>
       <c r="AR11" t="n">
-        <v>6.6</v>
+        <v>44</v>
       </c>
       <c r="AS11" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AT11" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="AU11" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AV11" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW11" t="n">
-        <v>7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX11" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AY11" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ11" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA11" t="n">
-        <v>7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB11" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BC11" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>6.4</v>
+        <v>29</v>
       </c>
       <c r="BE11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BF11" t="n">
         <v>9.4</v>
       </c>
       <c r="BG11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BH11" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BI11" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="BJ11" t="n">
         <v>12</v>
       </c>
       <c r="BK11" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>16.5</v>
+        <v>2.72</v>
       </c>
       <c r="BN11" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BO11" t="n">
         <v>3.55</v>
@@ -3332,41 +3332,41 @@
         <v>10.5</v>
       </c>
       <c r="BQ11" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BT11" t="n">
         <v>10.5</v>
       </c>
       <c r="BU11" t="n">
-        <v>6.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>3.05</v>
+        <v>2.7</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="BZ11" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="CA11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-15 09:14:49</t>
+          <t>2026-07-15 11:24:42</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-15.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-15.xlsx
@@ -857,151 +857,151 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="G2" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="J2" t="n">
         <v>3.25</v>
       </c>
-      <c r="H2" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="I2" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="J2" t="n">
-        <v>3.15</v>
-      </c>
       <c r="K2" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N2" t="n">
         <v>3.3</v>
       </c>
-      <c r="L2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N2" t="n">
-        <v>3.15</v>
-      </c>
       <c r="O2" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="P2" t="n">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="R2" t="n">
         <v>1.28</v>
       </c>
       <c r="S2" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="T2" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="U2" t="n">
-        <v>1.94</v>
+        <v>2.02</v>
       </c>
       <c r="V2" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="W2" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="X2" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z2" t="n">
         <v>16</v>
       </c>
       <c r="AA2" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AB2" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AC2" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AE2" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG2" t="n">
         <v>14.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI2" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ2" t="n">
         <v>60</v>
       </c>
       <c r="AK2" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN2" t="n">
         <v>44</v>
       </c>
-      <c r="AL2" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>55</v>
-      </c>
       <c r="AO2" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="AP2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>28</v>
+      </c>
+      <c r="AT2" t="n">
         <v>9.6</v>
       </c>
-      <c r="AQ2" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>30</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>9</v>
-      </c>
       <c r="AU2" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV2" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AX2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AY2" t="n">
         <v>12.5</v>
       </c>
       <c r="AZ2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="BB2" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BC2" t="n">
         <v>36</v>
@@ -1010,31 +1010,31 @@
         <v>46</v>
       </c>
       <c r="BE2" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="BF2" t="n">
         <v>36</v>
       </c>
       <c r="BG2" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BH2" t="n">
         <v>3.1</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="BJ2" t="n">
         <v>10.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.5</v>
+        <v>8.6</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BN2" t="n">
         <v>6.4</v>
@@ -1046,41 +1046,41 @@
         <v>28</v>
       </c>
       <c r="BQ2" t="n">
-        <v>8.199999999999999</v>
+        <v>18</v>
       </c>
       <c r="BR2" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BS2" t="n">
-        <v>9.199999999999999</v>
+        <v>13.5</v>
       </c>
       <c r="BT2" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BU2" t="n">
         <v>4.6</v>
       </c>
       <c r="BV2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BW2" t="n">
-        <v>7.6</v>
+        <v>14.5</v>
       </c>
       <c r="BX2" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BY2" t="n">
-        <v>9</v>
+        <v>18.5</v>
       </c>
       <c r="BZ2" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="CA2" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-15 11:24:42</t>
+          <t>2026-07-15 13:35:15</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="G3" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="H3" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="I3" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="J3" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="K3" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="L3" t="n">
         <v>1.35</v>
@@ -1144,37 +1144,37 @@
         <v>2.12</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="R3" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T3" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="U3" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="V3" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W3" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="X3" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Y3" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Z3" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AA3" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AB3" t="n">
         <v>8.4</v>
@@ -1183,10 +1183,10 @@
         <v>13</v>
       </c>
       <c r="AD3" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AE3" t="n">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="AF3" t="n">
         <v>7.6</v>
@@ -1198,7 +1198,7 @@
         <v>34</v>
       </c>
       <c r="AI3" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AJ3" t="n">
         <v>10.5</v>
@@ -1207,19 +1207,19 @@
         <v>16</v>
       </c>
       <c r="AL3" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AM3" t="n">
         <v>230</v>
       </c>
       <c r="AN3" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AO3" t="n">
-        <v>450</v>
+        <v>410</v>
       </c>
       <c r="AP3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AQ3" t="n">
         <v>24</v>
@@ -1228,7 +1228,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AS3" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AT3" t="n">
         <v>7</v>
@@ -1252,10 +1252,10 @@
         <v>16</v>
       </c>
       <c r="BA3" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BB3" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC3" t="n">
         <v>12.5</v>
@@ -1267,28 +1267,28 @@
         <v>9.6</v>
       </c>
       <c r="BF3" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BG3" t="n">
         <v>15</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BJ3" t="n">
         <v>13.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BN3" t="n">
         <v>3.8</v>
@@ -1297,19 +1297,19 @@
         <v>3.2</v>
       </c>
       <c r="BP3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BR3" t="n">
         <v>28</v>
       </c>
       <c r="BS3" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BT3" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BU3" t="n">
         <v>6</v>
@@ -1318,13 +1318,13 @@
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-15 11:24:42</t>
+          <t>2026-07-15 13:35:15</t>
         </is>
       </c>
     </row>
@@ -1365,178 +1365,178 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="G4" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="H4" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="I4" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="J4" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="K4" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="L4" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="M4" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N4" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="O4" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="P4" t="n">
-        <v>2.38</v>
+        <v>2.52</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="R4" t="n">
-        <v>1.55</v>
+        <v>1.63</v>
       </c>
       <c r="S4" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="T4" t="n">
         <v>1.69</v>
       </c>
       <c r="U4" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="V4" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="W4" t="n">
-        <v>2.34</v>
+        <v>2.68</v>
       </c>
       <c r="X4" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="Y4" t="n">
+        <v>29</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>200</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD4" t="n">
         <v>25</v>
       </c>
-      <c r="Z4" t="n">
-        <v>55</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>900</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>12</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>21</v>
-      </c>
       <c r="AE4" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AF4" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AG4" t="n">
         <v>10</v>
       </c>
       <c r="AH4" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AI4" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AJ4" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AK4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AL4" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AM4" t="n">
-        <v>200</v>
+        <v>580</v>
       </c>
       <c r="AN4" t="n">
-        <v>7.8</v>
+        <v>6.4</v>
       </c>
       <c r="AO4" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AP4" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AQ4" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="AR4" t="n">
+        <v>46</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>44</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>21</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>36</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA4" t="n">
         <v>34</v>
       </c>
-      <c r="AS4" t="n">
-        <v>11</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>17</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>40</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>23</v>
-      </c>
       <c r="BB4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BC4" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="BD4" t="n">
         <v>24</v>
       </c>
       <c r="BE4" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="BF4" t="n">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="BH4" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.35</v>
+        <v>3.95</v>
       </c>
       <c r="BJ4" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
@@ -1545,50 +1545,50 @@
         <v>10</v>
       </c>
       <c r="BN4" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BO4" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BP4" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BR4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BS4" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BT4" t="n">
+        <v>10</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>46</v>
+      </c>
+      <c r="BW4" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BU4" t="n">
-        <v>5</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>42</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BX4" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BY4" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ4" t="n">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="CA4" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-15 11:24:42</t>
+          <t>2026-07-15 13:35:15</t>
         </is>
       </c>
     </row>
@@ -1619,79 +1619,79 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="G5" t="n">
-        <v>2.52</v>
+        <v>2.42</v>
       </c>
       <c r="H5" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="I5" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="J5" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="K5" t="n">
         <v>2.94</v>
       </c>
       <c r="L5" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="M5" t="n">
         <v>1.15</v>
       </c>
       <c r="N5" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="O5" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="P5" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="R5" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="S5" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="T5" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="U5" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="V5" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="W5" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="X5" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y5" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AA5" t="n">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="AB5" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AC5" t="n">
         <v>6.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AE5" t="n">
         <v>160</v>
@@ -1700,19 +1700,19 @@
         <v>13</v>
       </c>
       <c r="AG5" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH5" t="n">
         <v>26</v>
       </c>
       <c r="AI5" t="n">
-        <v>210</v>
+        <v>120</v>
       </c>
       <c r="AJ5" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AK5" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AL5" t="n">
         <v>160</v>
@@ -1721,128 +1721,128 @@
         <v>500</v>
       </c>
       <c r="AN5" t="n">
-        <v>500</v>
+        <v>40</v>
       </c>
       <c r="AO5" t="n">
         <v>600</v>
       </c>
       <c r="AP5" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AQ5" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AR5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AS5" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="AT5" t="n">
         <v>6.4</v>
       </c>
       <c r="AU5" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="AV5" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AW5" t="n">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="AX5" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>22</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>28</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>28</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>29</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>48</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>17</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>32</v>
+      </c>
+      <c r="BG5" t="n">
         <v>11.5</v>
       </c>
-      <c r="AY5" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>55</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>27</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>26</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>44</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>28</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>30</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>10</v>
-      </c>
       <c r="BH5" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="BI5" t="n">
         <v>2.24</v>
       </c>
       <c r="BJ5" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BN5" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BO5" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BP5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BQ5" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR5" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="BS5" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BT5" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BU5" t="n">
-        <v>5.8</v>
+        <v>4.7</v>
       </c>
       <c r="BV5" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="BW5" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="CA5" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-15 11:24:42</t>
+          <t>2026-07-15 13:35:15</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
         <v>2.7</v>
       </c>
       <c r="I6" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="J6" t="n">
         <v>3.35</v>
@@ -1897,28 +1897,28 @@
         <v>1.07</v>
       </c>
       <c r="N6" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="O6" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="P6" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="Q6" t="n">
         <v>2.04</v>
       </c>
       <c r="R6" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S6" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="T6" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="U6" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V6" t="n">
         <v>1.54</v>
@@ -1927,7 +1927,7 @@
         <v>1.51</v>
       </c>
       <c r="X6" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y6" t="n">
         <v>12</v>
@@ -1936,13 +1936,13 @@
         <v>19</v>
       </c>
       <c r="AA6" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AB6" t="n">
         <v>12</v>
       </c>
       <c r="AC6" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AD6" t="n">
         <v>13.5</v>
@@ -1960,7 +1960,7 @@
         <v>17</v>
       </c>
       <c r="AI6" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ6" t="n">
         <v>48</v>
@@ -1972,13 +1972,13 @@
         <v>44</v>
       </c>
       <c r="AM6" t="n">
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="AN6" t="n">
         <v>29</v>
       </c>
       <c r="AO6" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AP6" t="n">
         <v>11.5</v>
@@ -2038,19 +2038,19 @@
         <v>3.45</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.74</v>
+        <v>2.82</v>
       </c>
       <c r="BJ6" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BN6" t="n">
         <v>6.2</v>
@@ -2062,13 +2062,13 @@
         <v>23</v>
       </c>
       <c r="BQ6" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BR6" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BS6" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BT6" t="n">
         <v>5.9</v>
@@ -2077,26 +2077,26 @@
         <v>4.9</v>
       </c>
       <c r="BV6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BW6" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BX6" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BY6" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BZ6" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="CA6" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-15 11:24:42</t>
+          <t>2026-07-15 13:35:15</t>
         </is>
       </c>
     </row>
@@ -2130,19 +2130,19 @@
         <v>2.84</v>
       </c>
       <c r="G7" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="H7" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="I7" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="J7" t="n">
         <v>3.45</v>
       </c>
       <c r="K7" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="L7" t="n">
         <v>1.39</v>
@@ -2151,34 +2151,34 @@
         <v>1.06</v>
       </c>
       <c r="N7" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O7" t="n">
         <v>1.28</v>
       </c>
       <c r="P7" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="R7" t="n">
         <v>1.42</v>
       </c>
       <c r="S7" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T7" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="U7" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="V7" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="W7" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="X7" t="n">
         <v>16.5</v>
@@ -2193,10 +2193,10 @@
         <v>38</v>
       </c>
       <c r="AB7" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AC7" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD7" t="n">
         <v>12.5</v>
@@ -2217,7 +2217,7 @@
         <v>38</v>
       </c>
       <c r="AJ7" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AK7" t="n">
         <v>32</v>
@@ -2229,31 +2229,31 @@
         <v>95</v>
       </c>
       <c r="AN7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO7" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AP7" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AQ7" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR7" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AS7" t="n">
         <v>27</v>
       </c>
       <c r="AT7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AU7" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV7" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AW7" t="n">
         <v>20</v>
@@ -2262,10 +2262,10 @@
         <v>17.5</v>
       </c>
       <c r="AY7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ7" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BA7" t="n">
         <v>27</v>
@@ -2283,49 +2283,49 @@
         <v>55</v>
       </c>
       <c r="BF7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BG7" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="BH7" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BJ7" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BK7" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BN7" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BO7" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BP7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BQ7" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BR7" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BT7" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BU7" t="n">
         <v>5</v>
@@ -2334,23 +2334,23 @@
         <v>19.5</v>
       </c>
       <c r="BW7" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BX7" t="n">
         <v>32</v>
       </c>
       <c r="BY7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>24</v>
+      </c>
+      <c r="CA7" t="n">
         <v>9.4</v>
       </c>
-      <c r="BZ7" t="n">
-        <v>25</v>
-      </c>
-      <c r="CA7" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-15 11:24:42</t>
+          <t>2026-07-15 13:35:15</t>
         </is>
       </c>
     </row>
@@ -2384,13 +2384,13 @@
         <v>1.68</v>
       </c>
       <c r="G8" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="H8" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="I8" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="J8" t="n">
         <v>4.1</v>
@@ -2399,7 +2399,7 @@
         <v>4.4</v>
       </c>
       <c r="L8" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="M8" t="n">
         <v>1.05</v>
@@ -2417,7 +2417,7 @@
         <v>1.79</v>
       </c>
       <c r="R8" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S8" t="n">
         <v>3</v>
@@ -2432,13 +2432,13 @@
         <v>1.2</v>
       </c>
       <c r="W8" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="X8" t="n">
         <v>18</v>
       </c>
       <c r="Y8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z8" t="n">
         <v>55</v>
@@ -2447,7 +2447,7 @@
         <v>160</v>
       </c>
       <c r="AB8" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC8" t="n">
         <v>10.5</v>
@@ -2492,13 +2492,13 @@
         <v>15.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AR8" t="n">
         <v>34</v>
       </c>
       <c r="AS8" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AT8" t="n">
         <v>8.4</v>
@@ -2510,7 +2510,7 @@
         <v>19</v>
       </c>
       <c r="AW8" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AX8" t="n">
         <v>9.6</v>
@@ -2522,7 +2522,7 @@
         <v>17.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BB8" t="n">
         <v>15</v>
@@ -2534,25 +2534,25 @@
         <v>24</v>
       </c>
       <c r="BE8" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BF8" t="n">
         <v>8</v>
       </c>
       <c r="BG8" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="BH8" t="n">
         <v>3.8</v>
       </c>
       <c r="BI8" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="BJ8" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BK8" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
@@ -2573,10 +2573,10 @@
         <v>8</v>
       </c>
       <c r="BR8" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BS8" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BT8" t="n">
         <v>9</v>
@@ -2588,7 +2588,7 @@
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
@@ -2597,14 +2597,14 @@
         <v>34</v>
       </c>
       <c r="BZ8" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="CA8" t="n">
         <v>13</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-15 11:24:42</t>
+          <t>2026-07-15 13:35:15</t>
         </is>
       </c>
     </row>
@@ -2638,13 +2638,13 @@
         <v>4.4</v>
       </c>
       <c r="G9" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="H9" t="n">
         <v>1.87</v>
       </c>
       <c r="I9" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="J9" t="n">
         <v>3.7</v>
@@ -2671,7 +2671,7 @@
         <v>2.04</v>
       </c>
       <c r="R9" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="S9" t="n">
         <v>3.7</v>
@@ -2680,10 +2680,10 @@
         <v>1.88</v>
       </c>
       <c r="U9" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V9" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="W9" t="n">
         <v>1.27</v>
@@ -2701,7 +2701,7 @@
         <v>23</v>
       </c>
       <c r="AB9" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AC9" t="n">
         <v>10.5</v>
@@ -2740,13 +2740,13 @@
         <v>85</v>
       </c>
       <c r="AO9" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AP9" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AQ9" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AR9" t="n">
         <v>10</v>
@@ -2767,7 +2767,7 @@
         <v>18</v>
       </c>
       <c r="AX9" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AY9" t="n">
         <v>15.5</v>
@@ -2776,22 +2776,22 @@
         <v>17.5</v>
       </c>
       <c r="BA9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BC9" t="n">
         <v>5</v>
       </c>
-      <c r="BB9" t="n">
+      <c r="BD9" t="n">
         <v>5</v>
       </c>
-      <c r="BC9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BE9" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BF9" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BG9" t="n">
         <v>12.5</v>
@@ -2806,7 +2806,7 @@
         <v>10.5</v>
       </c>
       <c r="BK9" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
@@ -2818,13 +2818,13 @@
         <v>8</v>
       </c>
       <c r="BO9" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BP9" t="n">
         <v>42</v>
       </c>
       <c r="BQ9" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BR9" t="n">
         <v>55</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-15 11:24:42</t>
+          <t>2026-07-15 13:35:15</t>
         </is>
       </c>
     </row>
@@ -2889,19 +2889,19 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="G10" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="H10" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="I10" t="n">
         <v>12.5</v>
       </c>
       <c r="J10" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="K10" t="n">
         <v>7.2</v>
@@ -2919,61 +2919,61 @@
         <v>1.13</v>
       </c>
       <c r="P10" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="Q10" t="n">
         <v>1.4</v>
       </c>
       <c r="R10" t="n">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="S10" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="T10" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="U10" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="V10" t="n">
         <v>1.09</v>
       </c>
       <c r="W10" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="X10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="Y10" t="n">
         <v>55</v>
       </c>
       <c r="Z10" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AA10" t="n">
-        <v>350</v>
+        <v>410</v>
       </c>
       <c r="AB10" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AC10" t="n">
         <v>19</v>
       </c>
       <c r="AD10" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AE10" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AF10" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH10" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AI10" t="n">
         <v>120</v>
@@ -2985,7 +2985,7 @@
         <v>14.5</v>
       </c>
       <c r="AL10" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AM10" t="n">
         <v>110</v>
@@ -2994,31 +2994,31 @@
         <v>3.55</v>
       </c>
       <c r="AO10" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AP10" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AQ10" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AR10" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AS10" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AT10" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AU10" t="n">
         <v>14</v>
       </c>
       <c r="AV10" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AW10" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AX10" t="n">
         <v>9.4</v>
@@ -3027,82 +3027,82 @@
         <v>10</v>
       </c>
       <c r="AZ10" t="n">
-        <v>21</v>
+        <v>6.2</v>
       </c>
       <c r="BA10" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BB10" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BC10" t="n">
         <v>11.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BE10" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BF10" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="BG10" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BH10" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BI10" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BJ10" t="n">
         <v>11.5</v>
       </c>
       <c r="BK10" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>9.6</v>
+        <v>15.5</v>
       </c>
       <c r="BN10" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BO10" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="BP10" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="BR10" t="n">
         <v>18.5</v>
       </c>
       <c r="BS10" t="n">
-        <v>6.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT10" t="n">
         <v>14.5</v>
       </c>
       <c r="BU10" t="n">
-        <v>6.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>9.4</v>
+        <v>3.35</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>9.199999999999999</v>
+        <v>14</v>
       </c>
       <c r="BZ10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-15 11:24:42</t>
+          <t>2026-07-15 13:35:15</t>
         </is>
       </c>
     </row>
@@ -3143,16 +3143,16 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="G11" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="H11" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="I11" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="J11" t="n">
         <v>4</v>
@@ -3167,43 +3167,43 @@
         <v>1.08</v>
       </c>
       <c r="N11" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="O11" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P11" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="R11" t="n">
         <v>1.31</v>
       </c>
       <c r="S11" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="T11" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="U11" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="V11" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="W11" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="X11" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y11" t="n">
         <v>23</v>
       </c>
       <c r="Z11" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AA11" t="n">
         <v>300</v>
@@ -3212,16 +3212,16 @@
         <v>7.6</v>
       </c>
       <c r="AC11" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD11" t="n">
         <v>34</v>
       </c>
       <c r="AE11" t="n">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="AF11" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AG11" t="n">
         <v>10.5</v>
@@ -3230,7 +3230,7 @@
         <v>29</v>
       </c>
       <c r="AI11" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AJ11" t="n">
         <v>17</v>
@@ -3242,13 +3242,13 @@
         <v>55</v>
       </c>
       <c r="AM11" t="n">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="AN11" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AO11" t="n">
-        <v>250</v>
+        <v>290</v>
       </c>
       <c r="AP11" t="n">
         <v>11</v>
@@ -3263,7 +3263,7 @@
         <v>8</v>
       </c>
       <c r="AT11" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AU11" t="n">
         <v>8.6</v>
@@ -3272,31 +3272,31 @@
         <v>22</v>
       </c>
       <c r="AW11" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AX11" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AY11" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ11" t="n">
         <v>22</v>
       </c>
       <c r="BA11" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB11" t="n">
         <v>13</v>
       </c>
       <c r="BC11" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="BE11" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BF11" t="n">
         <v>9.4</v>
@@ -3305,7 +3305,7 @@
         <v>8</v>
       </c>
       <c r="BH11" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BI11" t="n">
         <v>2.94</v>
@@ -3314,13 +3314,13 @@
         <v>12</v>
       </c>
       <c r="BK11" t="n">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>2.72</v>
+        <v>16.5</v>
       </c>
       <c r="BN11" t="n">
         <v>3.85</v>
@@ -3332,41 +3332,41 @@
         <v>10.5</v>
       </c>
       <c r="BQ11" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BT11" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BU11" t="n">
-        <v>9.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>2.7</v>
+        <v>14.5</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="BZ11" t="n">
         <v>30</v>
       </c>
       <c r="CA11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-15 11:24:42</t>
+          <t>2026-07-15 13:35:15</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-15.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-15.xlsx
@@ -857,230 +857,230 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.2</v>
+        <v>6.4</v>
       </c>
       <c r="G2" t="n">
-        <v>3.35</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>2.5</v>
+        <v>5.7</v>
       </c>
       <c r="I2" t="n">
-        <v>2.56</v>
+        <v>7.2</v>
       </c>
       <c r="J2" t="n">
-        <v>3.25</v>
+        <v>1.4</v>
       </c>
       <c r="K2" t="n">
-        <v>3.35</v>
+        <v>1.47</v>
       </c>
       <c r="L2" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1.09</v>
+        <v>2.84</v>
       </c>
       <c r="N2" t="n">
-        <v>3.3</v>
+        <v>1.06</v>
       </c>
       <c r="O2" t="n">
-        <v>1.41</v>
+        <v>16</v>
       </c>
       <c r="P2" t="n">
-        <v>1.78</v>
+        <v>1.01</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.22</v>
+        <v>110</v>
       </c>
       <c r="R2" t="n">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="S2" t="n">
-        <v>4.2</v>
+        <v>200</v>
       </c>
       <c r="T2" t="n">
-        <v>1.89</v>
+        <v>18</v>
       </c>
       <c r="U2" t="n">
-        <v>2.02</v>
+        <v>1.02</v>
       </c>
       <c r="V2" t="n">
-        <v>1.64</v>
+        <v>1.18</v>
       </c>
       <c r="W2" t="n">
-        <v>1.44</v>
+        <v>1.12</v>
       </c>
       <c r="X2" t="n">
-        <v>11.5</v>
+        <v>1.55</v>
       </c>
       <c r="Y2" t="n">
-        <v>9.800000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="Z2" t="n">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="AA2" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
         <v>11</v>
       </c>
       <c r="AC2" t="n">
-        <v>7.6</v>
+        <v>40</v>
       </c>
       <c r="AD2" t="n">
-        <v>12</v>
+        <v>530</v>
       </c>
       <c r="AE2" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>22</v>
+        <v>160</v>
       </c>
       <c r="AG2" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>30</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>65</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>20</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>190</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>46</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>65</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>210</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>46</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>28</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>28</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>80</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>28</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>46</v>
+      </c>
+      <c r="BF2" t="n">
         <v>50</v>
       </c>
-      <c r="AJ2" t="n">
-        <v>60</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>42</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>44</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>29</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>14</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>28</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>26</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>19</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>40</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>50</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>36</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>46</v>
-      </c>
-      <c r="BE2" t="n">
+      <c r="BG2" t="n">
         <v>85</v>
       </c>
-      <c r="BF2" t="n">
-        <v>36</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>24</v>
-      </c>
       <c r="BH2" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BK2" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="BL2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM2" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BN2" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BO2" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="BP2" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="BQ2" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="BR2" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="BS2" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="BT2" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="BU2" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BV2" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BW2" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="BY2" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="BZ2" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="CA2" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:35:15</t>
+          <t>2026-07-15 15:46:37</t>
         </is>
       </c>
     </row>
@@ -1111,55 +1111,55 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="G3" t="n">
         <v>1.39</v>
       </c>
       <c r="H3" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="I3" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="J3" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="K3" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="L3" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="M3" t="n">
         <v>1.05</v>
       </c>
       <c r="N3" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="O3" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P3" t="n">
         <v>2.12</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="R3" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S3" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="T3" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="U3" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="V3" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="W3" t="n">
         <v>3.55</v>
@@ -1174,10 +1174,10 @@
         <v>130</v>
       </c>
       <c r="AA3" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC3" t="n">
         <v>13</v>
@@ -1192,7 +1192,7 @@
         <v>7.6</v>
       </c>
       <c r="AG3" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH3" t="n">
         <v>34</v>
@@ -1213,7 +1213,7 @@
         <v>230</v>
       </c>
       <c r="AN3" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AO3" t="n">
         <v>410</v>
@@ -1222,16 +1222,16 @@
         <v>15</v>
       </c>
       <c r="AQ3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AR3" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS3" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AT3" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AU3" t="n">
         <v>10.5</v>
@@ -1240,10 +1240,10 @@
         <v>32</v>
       </c>
       <c r="AW3" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AX3" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AY3" t="n">
         <v>9.4</v>
@@ -1252,19 +1252,19 @@
         <v>16</v>
       </c>
       <c r="BA3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BB3" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BC3" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BD3" t="n">
-        <v>15.5</v>
+        <v>22</v>
       </c>
       <c r="BE3" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BF3" t="n">
         <v>5.5</v>
@@ -1273,58 +1273,58 @@
         <v>15</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="BJ3" t="n">
         <v>13.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BN3" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BP3" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BR3" t="n">
         <v>28</v>
       </c>
       <c r="BS3" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BT3" t="n">
         <v>14.5</v>
       </c>
       <c r="BU3" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-15 13:35:15</t>
+          <t>2026-07-15 15:46:37</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="G4" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="H4" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="I4" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="J4" t="n">
         <v>4.6</v>
       </c>
       <c r="K4" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="L4" t="n">
         <v>1.29</v>
@@ -1389,61 +1389,61 @@
         <v>1.04</v>
       </c>
       <c r="N4" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="O4" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P4" t="n">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="R4" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="S4" t="n">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="T4" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="U4" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="V4" t="n">
         <v>1.17</v>
       </c>
       <c r="W4" t="n">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="X4" t="n">
         <v>26</v>
       </c>
       <c r="Y4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Z4" t="n">
         <v>60</v>
       </c>
       <c r="AA4" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AB4" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AC4" t="n">
         <v>12</v>
       </c>
       <c r="AD4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE4" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AF4" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AG4" t="n">
         <v>10</v>
@@ -1452,13 +1452,13 @@
         <v>20</v>
       </c>
       <c r="AI4" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ4" t="n">
         <v>15.5</v>
       </c>
       <c r="AK4" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AL4" t="n">
         <v>30</v>
@@ -1467,46 +1467,46 @@
         <v>580</v>
       </c>
       <c r="AN4" t="n">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="AO4" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AP4" t="n">
         <v>21</v>
       </c>
       <c r="AQ4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AR4" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AS4" t="n">
         <v>44</v>
       </c>
       <c r="AT4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AU4" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AV4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW4" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AX4" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AY4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ4" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA4" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BB4" t="n">
         <v>13</v>
@@ -1515,16 +1515,16 @@
         <v>12.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="BE4" t="n">
         <v>42</v>
       </c>
       <c r="BF4" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BG4" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="BH4" t="n">
         <v>4.6</v>
@@ -1533,16 +1533,16 @@
         <v>3.95</v>
       </c>
       <c r="BJ4" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BN4" t="n">
         <v>4.6</v>
@@ -1557,38 +1557,38 @@
         <v>6.2</v>
       </c>
       <c r="BR4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BS4" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BT4" t="n">
         <v>10</v>
       </c>
       <c r="BU4" t="n">
-        <v>5.4</v>
+        <v>7.2</v>
       </c>
       <c r="BV4" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BW4" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BX4" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BY4" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BZ4" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="CA4" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-15 13:35:15</t>
+          <t>2026-07-15 15:46:37</t>
         </is>
       </c>
     </row>
@@ -1622,19 +1622,19 @@
         <v>2.38</v>
       </c>
       <c r="G5" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I5" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J5" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="K5" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="L5" t="n">
         <v>1.67</v>
@@ -1649,7 +1649,7 @@
         <v>1.61</v>
       </c>
       <c r="P5" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="Q5" t="n">
         <v>2.92</v>
@@ -1664,16 +1664,16 @@
         <v>2.14</v>
       </c>
       <c r="U5" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="V5" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W5" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="X5" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="Y5" t="n">
         <v>11.5</v>
@@ -1694,10 +1694,10 @@
         <v>18.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>160</v>
+        <v>85</v>
       </c>
       <c r="AF5" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG5" t="n">
         <v>12.5</v>
@@ -1715,7 +1715,7 @@
         <v>36</v>
       </c>
       <c r="AL5" t="n">
-        <v>160</v>
+        <v>85</v>
       </c>
       <c r="AM5" t="n">
         <v>500</v>
@@ -1724,7 +1724,7 @@
         <v>40</v>
       </c>
       <c r="AO5" t="n">
-        <v>600</v>
+        <v>140</v>
       </c>
       <c r="AP5" t="n">
         <v>7</v>
@@ -1736,7 +1736,7 @@
         <v>23</v>
       </c>
       <c r="AS5" t="n">
-        <v>23</v>
+        <v>75</v>
       </c>
       <c r="AT5" t="n">
         <v>6.4</v>
@@ -1748,7 +1748,7 @@
         <v>16</v>
       </c>
       <c r="AW5" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="AX5" t="n">
         <v>11</v>
@@ -1757,34 +1757,34 @@
         <v>11</v>
       </c>
       <c r="AZ5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA5" t="n">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="BB5" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BC5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BD5" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="BE5" t="n">
-        <v>17</v>
+        <v>80</v>
       </c>
       <c r="BF5" t="n">
         <v>32</v>
       </c>
       <c r="BG5" t="n">
-        <v>11.5</v>
+        <v>85</v>
       </c>
       <c r="BH5" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="BJ5" t="n">
         <v>12.5</v>
@@ -1796,7 +1796,7 @@
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BN5" t="n">
         <v>5</v>
@@ -1814,35 +1814,35 @@
         <v>55</v>
       </c>
       <c r="BS5" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BT5" t="n">
         <v>7.2</v>
       </c>
       <c r="BU5" t="n">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="BV5" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BW5" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BX5" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BY5" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BZ5" t="n">
         <v>65</v>
       </c>
       <c r="CA5" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-15 13:35:15</t>
+          <t>2026-07-15 15:46:37</t>
         </is>
       </c>
     </row>
@@ -1873,16 +1873,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.82</v>
+        <v>2.96</v>
       </c>
       <c r="G6" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="H6" t="n">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="I6" t="n">
-        <v>2.84</v>
+        <v>2.68</v>
       </c>
       <c r="J6" t="n">
         <v>3.35</v>
@@ -1897,16 +1897,16 @@
         <v>1.07</v>
       </c>
       <c r="N6" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="O6" t="n">
         <v>1.32</v>
       </c>
       <c r="P6" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="R6" t="n">
         <v>1.36</v>
@@ -1915,163 +1915,163 @@
         <v>3.6</v>
       </c>
       <c r="T6" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="U6" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="V6" t="n">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="W6" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="X6" t="n">
         <v>14.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AA6" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AB6" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AC6" t="n">
         <v>8</v>
       </c>
       <c r="AD6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG6" t="n">
         <v>13.5</v>
       </c>
-      <c r="AE6" t="n">
+      <c r="AH6" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN6" t="n">
         <v>32</v>
       </c>
-      <c r="AF6" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>17</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>48</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>29</v>
-      </c>
       <c r="AO6" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AP6" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AQ6" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AR6" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AS6" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AT6" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU6" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV6" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AW6" t="n">
         <v>24</v>
       </c>
       <c r="AX6" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AY6" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA6" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BB6" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="BC6" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="BD6" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BE6" t="n">
         <v>65</v>
       </c>
       <c r="BF6" t="n">
+        <v>27</v>
+      </c>
+      <c r="BG6" t="n">
         <v>21</v>
       </c>
-      <c r="BG6" t="n">
-        <v>18.5</v>
-      </c>
       <c r="BH6" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="BJ6" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BN6" t="n">
         <v>6.2</v>
       </c>
       <c r="BO6" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BP6" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BQ6" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BR6" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BS6" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BT6" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="BU6" t="n">
         <v>4.9</v>
@@ -2080,23 +2080,23 @@
         <v>21</v>
       </c>
       <c r="BW6" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BX6" t="n">
         <v>34</v>
       </c>
       <c r="BY6" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ6" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="CA6" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-15 13:35:15</t>
+          <t>2026-07-15 15:46:37</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2139,7 @@
         <v>2.68</v>
       </c>
       <c r="J7" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="K7" t="n">
         <v>3.85</v>
@@ -2193,7 +2193,7 @@
         <v>38</v>
       </c>
       <c r="AB7" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AC7" t="n">
         <v>9</v>
@@ -2223,7 +2223,7 @@
         <v>32</v>
       </c>
       <c r="AL7" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM7" t="n">
         <v>95</v>
@@ -2268,7 +2268,7 @@
         <v>14</v>
       </c>
       <c r="BA7" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BB7" t="n">
         <v>30</v>
@@ -2298,31 +2298,31 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK7" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BN7" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BO7" t="n">
         <v>5.4</v>
       </c>
       <c r="BP7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BQ7" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT7" t="n">
         <v>5.7</v>
@@ -2331,26 +2331,26 @@
         <v>5</v>
       </c>
       <c r="BV7" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BW7" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX7" t="n">
         <v>32</v>
       </c>
       <c r="BY7" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ7" t="n">
         <v>24</v>
       </c>
       <c r="CA7" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-15 13:35:15</t>
+          <t>2026-07-15 15:46:37</t>
         </is>
       </c>
     </row>
@@ -2384,13 +2384,13 @@
         <v>1.68</v>
       </c>
       <c r="G8" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="H8" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="I8" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J8" t="n">
         <v>4.1</v>
@@ -2405,7 +2405,7 @@
         <v>1.05</v>
       </c>
       <c r="N8" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O8" t="n">
         <v>1.27</v>
@@ -2414,10 +2414,10 @@
         <v>2.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="R8" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S8" t="n">
         <v>3</v>
@@ -2429,10 +2429,10 @@
         <v>2.1</v>
       </c>
       <c r="V8" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W8" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="X8" t="n">
         <v>18</v>
@@ -2447,7 +2447,7 @@
         <v>160</v>
       </c>
       <c r="AB8" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AC8" t="n">
         <v>10.5</v>
@@ -2474,7 +2474,7 @@
         <v>17.5</v>
       </c>
       <c r="AK8" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AL8" t="n">
         <v>42</v>
@@ -2483,13 +2483,13 @@
         <v>120</v>
       </c>
       <c r="AN8" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AO8" t="n">
         <v>95</v>
       </c>
       <c r="AP8" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AQ8" t="n">
         <v>18</v>
@@ -2522,7 +2522,7 @@
         <v>17.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BB8" t="n">
         <v>15</v>
@@ -2534,7 +2534,7 @@
         <v>24</v>
       </c>
       <c r="BE8" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF8" t="n">
         <v>8</v>
@@ -2543,16 +2543,16 @@
         <v>44</v>
       </c>
       <c r="BH8" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="BJ8" t="n">
         <v>10</v>
       </c>
       <c r="BK8" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
@@ -2573,10 +2573,10 @@
         <v>8</v>
       </c>
       <c r="BR8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BS8" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BT8" t="n">
         <v>9</v>
@@ -2585,26 +2585,26 @@
         <v>6.6</v>
       </c>
       <c r="BV8" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BW8" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BX8" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BY8" t="n">
         <v>34</v>
       </c>
       <c r="BZ8" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="CA8" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-15 13:35:15</t>
+          <t>2026-07-15 15:46:37</t>
         </is>
       </c>
     </row>
@@ -2641,13 +2641,13 @@
         <v>4.7</v>
       </c>
       <c r="H9" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="I9" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="J9" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K9" t="n">
         <v>4</v>
@@ -2659,7 +2659,7 @@
         <v>1.07</v>
       </c>
       <c r="N9" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="O9" t="n">
         <v>1.34</v>
@@ -2671,19 +2671,19 @@
         <v>2.04</v>
       </c>
       <c r="R9" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="S9" t="n">
         <v>3.7</v>
       </c>
       <c r="T9" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="U9" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V9" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="W9" t="n">
         <v>1.27</v>
@@ -2695,7 +2695,7 @@
         <v>10</v>
       </c>
       <c r="Z9" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AA9" t="n">
         <v>23</v>
@@ -2710,7 +2710,7 @@
         <v>12.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AF9" t="n">
         <v>42</v>
@@ -2746,7 +2746,7 @@
         <v>12</v>
       </c>
       <c r="AQ9" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AR9" t="n">
         <v>10</v>
@@ -2779,19 +2779,19 @@
         <v>5.2</v>
       </c>
       <c r="BB9" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BC9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BF9" t="n">
         <v>5</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>5.1</v>
       </c>
       <c r="BG9" t="n">
         <v>12.5</v>
@@ -2806,7 +2806,7 @@
         <v>10.5</v>
       </c>
       <c r="BK9" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
@@ -2818,7 +2818,7 @@
         <v>8</v>
       </c>
       <c r="BO9" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BP9" t="n">
         <v>42</v>
@@ -2833,7 +2833,7 @@
         <v>36</v>
       </c>
       <c r="BT9" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BU9" t="n">
         <v>3.5</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-15 13:35:15</t>
+          <t>2026-07-15 15:46:37</t>
         </is>
       </c>
     </row>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="G10" t="n">
         <v>1.31</v>
@@ -2898,13 +2898,13 @@
         <v>11</v>
       </c>
       <c r="I10" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="J10" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="K10" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="L10" t="n">
         <v>1.22</v>
@@ -2925,25 +2925,25 @@
         <v>1.4</v>
       </c>
       <c r="R10" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="S10" t="n">
         <v>1.97</v>
       </c>
       <c r="T10" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="U10" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="V10" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="W10" t="n">
         <v>4.2</v>
       </c>
       <c r="X10" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="Y10" t="n">
         <v>55</v>
@@ -2952,34 +2952,34 @@
         <v>120</v>
       </c>
       <c r="AA10" t="n">
-        <v>410</v>
+        <v>470</v>
       </c>
       <c r="AB10" t="n">
         <v>14.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AD10" t="n">
         <v>46</v>
       </c>
       <c r="AE10" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AF10" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG10" t="n">
         <v>14</v>
       </c>
       <c r="AH10" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AI10" t="n">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="AJ10" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AK10" t="n">
         <v>14.5</v>
@@ -2991,46 +2991,46 @@
         <v>110</v>
       </c>
       <c r="AN10" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="AO10" t="n">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="AP10" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AQ10" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AR10" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AS10" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT10" t="n">
         <v>11.5</v>
       </c>
       <c r="AU10" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="AV10" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AW10" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AX10" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AY10" t="n">
         <v>10</v>
       </c>
       <c r="AZ10" t="n">
-        <v>6.2</v>
+        <v>22</v>
       </c>
       <c r="BA10" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BB10" t="n">
         <v>9.6</v>
@@ -3039,19 +3039,19 @@
         <v>11.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BE10" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BF10" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BG10" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BH10" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BI10" t="n">
         <v>4.9</v>
@@ -3060,19 +3060,19 @@
         <v>11.5</v>
       </c>
       <c r="BK10" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BN10" t="n">
         <v>4.3</v>
       </c>
       <c r="BO10" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BP10" t="n">
         <v>7.2</v>
@@ -3084,25 +3084,25 @@
         <v>18.5</v>
       </c>
       <c r="BS10" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT10" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BU10" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>3.35</v>
+        <v>14</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BZ10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-15 13:35:15</t>
+          <t>2026-07-15 15:46:37</t>
         </is>
       </c>
     </row>
@@ -3149,13 +3149,13 @@
         <v>1.6</v>
       </c>
       <c r="H11" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="I11" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="J11" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K11" t="n">
         <v>4.3</v>
@@ -3173,13 +3173,13 @@
         <v>1.39</v>
       </c>
       <c r="P11" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="Q11" t="n">
         <v>2.14</v>
       </c>
       <c r="R11" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -3188,7 +3188,7 @@
         <v>2.18</v>
       </c>
       <c r="U11" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="V11" t="n">
         <v>1.14</v>
@@ -3197,7 +3197,7 @@
         <v>2.66</v>
       </c>
       <c r="X11" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Y11" t="n">
         <v>23</v>
@@ -3221,7 +3221,7 @@
         <v>170</v>
       </c>
       <c r="AF11" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AG11" t="n">
         <v>10.5</v>
@@ -3233,7 +3233,7 @@
         <v>160</v>
       </c>
       <c r="AJ11" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AK11" t="n">
         <v>22</v>
@@ -3260,19 +3260,19 @@
         <v>44</v>
       </c>
       <c r="AS11" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT11" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AU11" t="n">
         <v>8.6</v>
       </c>
       <c r="AV11" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW11" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AX11" t="n">
         <v>7.6</v>
@@ -3284,7 +3284,7 @@
         <v>22</v>
       </c>
       <c r="BA11" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BB11" t="n">
         <v>13</v>
@@ -3296,13 +3296,13 @@
         <v>36</v>
       </c>
       <c r="BE11" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BF11" t="n">
         <v>9.4</v>
       </c>
       <c r="BG11" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH11" t="n">
         <v>3.25</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-15 13:35:15</t>
+          <t>2026-07-15 15:46:37</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-15.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB11"/>
+  <dimension ref="A1:CB10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,7 +833,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Ecuadorian Serie B</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -843,180 +843,180 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Libertad FC</t>
+          <t>Vinotinto Ecuador</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Tecnico Universitario</t>
+          <t>El Nacional</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>6.4</v>
+        <v>1.14</v>
       </c>
       <c r="G2" t="n">
-        <v>8.199999999999999</v>
+        <v>1.17</v>
       </c>
       <c r="H2" t="n">
-        <v>5.7</v>
+        <v>26</v>
       </c>
       <c r="I2" t="n">
-        <v>7.2</v>
+        <v>200</v>
       </c>
       <c r="J2" t="n">
-        <v>1.4</v>
+        <v>7.6</v>
       </c>
       <c r="K2" t="n">
-        <v>1.47</v>
+        <v>10.5</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
         <v>1.01</v>
       </c>
-      <c r="Q2" t="n">
-        <v>110</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="S2" t="n">
-        <v>200</v>
-      </c>
-      <c r="T2" t="n">
-        <v>18</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.18</v>
-      </c>
       <c r="W2" t="n">
-        <v>1.12</v>
+        <v>6.8</v>
       </c>
       <c r="X2" t="n">
-        <v>1.55</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
         <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>530</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
         <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>1000</v>
+        <v>2.92</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AJ2" t="n">
         <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AM2" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="AO2" t="n">
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.49</v>
+        <v>12</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5.8</v>
+        <v>12</v>
       </c>
       <c r="AR2" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="AS2" t="n">
-        <v>65</v>
+        <v>12</v>
       </c>
       <c r="AT2" t="n">
-        <v>7.8</v>
+        <v>12</v>
       </c>
       <c r="AU2" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AV2" t="n">
-        <v>190</v>
+        <v>12</v>
       </c>
       <c r="AW2" t="n">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="AX2" t="n">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="AY2" t="n">
-        <v>210</v>
+        <v>2.72</v>
       </c>
       <c r="AZ2" t="n">
-        <v>46</v>
+        <v>8.6</v>
       </c>
       <c r="BA2" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="BB2" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="BC2" t="n">
-        <v>80</v>
+        <v>3.35</v>
       </c>
       <c r="BD2" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="BE2" t="n">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="BF2" t="n">
-        <v>50</v>
+        <v>5.9</v>
       </c>
       <c r="BG2" t="n">
-        <v>85</v>
+        <v>12</v>
       </c>
       <c r="BH2" t="n">
         <v>0</v>
@@ -1080,14 +1080,14 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-15 15:46:37</t>
+          <t>2026-07-15 17:58:21</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie B</t>
+          <t>Bolivian Liga de Futbol Profesional</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1097,251 +1097,251 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Vinotinto Ecuador</t>
+          <t>Real Potosi</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>El Nacional</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.35</v>
+        <v>1.54</v>
       </c>
       <c r="G3" t="n">
-        <v>1.39</v>
+        <v>1.58</v>
       </c>
       <c r="H3" t="n">
+        <v>6</v>
+      </c>
+      <c r="I3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N3" t="n">
+        <v>6</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="X3" t="n">
+        <v>26</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>32</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>180</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF3" t="n">
         <v>11.5</v>
       </c>
-      <c r="I3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="J3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="K3" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="P3" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S3" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W3" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="X3" t="n">
-        <v>19</v>
-      </c>
-      <c r="Y3" t="n">
+      <c r="AG3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>30</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>75</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>23</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>26</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>48</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>44</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AW3" t="n">
         <v>36</v>
       </c>
-      <c r="Z3" t="n">
-        <v>130</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AC3" t="n">
+      <c r="AX3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>55</v>
+      </c>
+      <c r="BB3" t="n">
         <v>13</v>
       </c>
-      <c r="AD3" t="n">
-        <v>48</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>260</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>34</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>210</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>16</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>230</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>410</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>25</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>32</v>
-      </c>
-      <c r="AW3" t="n">
+      <c r="BC3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>24</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>44</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>50</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ3" t="n">
         <v>10</v>
       </c>
-      <c r="AX3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>10</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>13</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>22</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>10</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>15</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>13.5</v>
-      </c>
       <c r="BK3" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BN3" t="n">
-        <v>3.75</v>
+        <v>4.6</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="BP3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BQ3" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BQ3" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BR3" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="BS3" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="BT3" t="n">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="BU3" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BV3" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BW3" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="BX3" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BY3" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="CA3" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-15 15:46:37</t>
+          <t>2026-07-15 17:58:21</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1356,239 +1356,239 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Real Potosi</t>
+          <t>CD Leones del Norte</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.57</v>
+        <v>2.44</v>
       </c>
       <c r="G4" t="n">
-        <v>1.61</v>
+        <v>2.5</v>
       </c>
       <c r="H4" t="n">
-        <v>5.9</v>
+        <v>3.95</v>
       </c>
       <c r="I4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S4" t="n">
         <v>6.6</v>
       </c>
-      <c r="J4" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="K4" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N4" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="P4" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="R4" t="n">
+      <c r="T4" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W4" t="n">
         <v>1.66</v>
       </c>
-      <c r="S4" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="U4" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="W4" t="n">
-        <v>2.62</v>
-      </c>
       <c r="X4" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>27</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>80</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>500</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>46</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>130</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>22</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>16</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>55</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>23</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>38</v>
+      </c>
+      <c r="BB4" t="n">
         <v>26</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="BC4" t="n">
         <v>30</v>
       </c>
-      <c r="Z4" t="n">
-        <v>60</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>190</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AC4" t="n">
+      <c r="BD4" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>28</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>38</v>
+      </c>
+      <c r="BG4" t="n">
         <v>12</v>
       </c>
-      <c r="AD4" t="n">
-        <v>24</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>70</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>30</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>60</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>21</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>26</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>48</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>44</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>20</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>38</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY4" t="n">
+      <c r="BH4" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BK4" t="n">
         <v>9.199999999999999</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>36</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>13</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>21</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>42</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>34</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>7</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
+        <v>14</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>23</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>9</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>55</v>
+      </c>
+      <c r="BS4" t="n">
         <v>11</v>
       </c>
-      <c r="BN4" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>21</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>8</v>
-      </c>
       <c r="BT4" t="n">
-        <v>10</v>
+        <v>7.2</v>
       </c>
       <c r="BU4" t="n">
-        <v>7.2</v>
+        <v>6</v>
       </c>
       <c r="BV4" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="BW4" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BX4" t="n">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="BY4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BZ4" t="n">
-        <v>12.5</v>
+        <v>65</v>
       </c>
       <c r="CA4" t="n">
-        <v>6.2</v>
+        <v>12</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-15 15:46:37</t>
+          <t>2026-07-15 17:58:21</t>
         </is>
       </c>
     </row>
@@ -1610,187 +1610,187 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CD Leones del Norte</t>
+          <t>Univ Catolica (Ecu)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>LDU</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.38</v>
+        <v>2.96</v>
       </c>
       <c r="G5" t="n">
-        <v>2.4</v>
+        <v>3.15</v>
       </c>
       <c r="H5" t="n">
-        <v>4.1</v>
+        <v>2.58</v>
       </c>
       <c r="I5" t="n">
-        <v>4.3</v>
+        <v>2.66</v>
       </c>
       <c r="J5" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="K5" t="n">
-        <v>2.98</v>
+        <v>3.5</v>
       </c>
       <c r="L5" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="M5" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="N5" t="n">
-        <v>2.56</v>
+        <v>3.9</v>
       </c>
       <c r="O5" t="n">
-        <v>1.61</v>
+        <v>1.32</v>
       </c>
       <c r="P5" t="n">
-        <v>1.5</v>
+        <v>1.98</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.92</v>
+        <v>1.99</v>
       </c>
       <c r="R5" t="n">
-        <v>1.17</v>
+        <v>1.37</v>
       </c>
       <c r="S5" t="n">
-        <v>6.2</v>
+        <v>3.55</v>
       </c>
       <c r="T5" t="n">
-        <v>2.14</v>
+        <v>1.78</v>
       </c>
       <c r="U5" t="n">
-        <v>1.77</v>
+        <v>2.18</v>
       </c>
       <c r="V5" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="W5" t="n">
-        <v>1.71</v>
+        <v>1.47</v>
       </c>
       <c r="X5" t="n">
-        <v>7.8</v>
+        <v>14</v>
       </c>
       <c r="Y5" t="n">
         <v>11.5</v>
       </c>
       <c r="Z5" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>40</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE5" t="n">
         <v>28</v>
       </c>
-      <c r="AA5" t="n">
-        <v>120</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>85</v>
-      </c>
       <c r="AF5" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>50</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>24</v>
+      </c>
+      <c r="AP5" t="n">
         <v>12.5</v>
       </c>
-      <c r="AG5" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH5" t="n">
+      <c r="AQ5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>32</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>25</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>18</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>34</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>44</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>28</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>40</v>
+      </c>
+      <c r="BF5" t="n">
         <v>26</v>
       </c>
-      <c r="AI5" t="n">
-        <v>120</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>34</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>36</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>85</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>40</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>140</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>7</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>23</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>75</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>16</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>46</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>23</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>60</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>26</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>30</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>55</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>80</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>32</v>
-      </c>
       <c r="BG5" t="n">
-        <v>85</v>
+        <v>20</v>
       </c>
       <c r="BH5" t="n">
-        <v>2.64</v>
+        <v>3.4</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.4</v>
+        <v>3.05</v>
       </c>
       <c r="BJ5" t="n">
-        <v>12.5</v>
+        <v>9.6</v>
       </c>
       <c r="BK5" t="n">
-        <v>9.199999999999999</v>
+        <v>5.8</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
@@ -1799,57 +1799,57 @@
         <v>12.5</v>
       </c>
       <c r="BN5" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.3</v>
+        <v>5.4</v>
       </c>
       <c r="BP5" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BQ5" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR5" t="n">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="BS5" t="n">
         <v>10</v>
       </c>
       <c r="BT5" t="n">
-        <v>7.2</v>
+        <v>5.6</v>
       </c>
       <c r="BU5" t="n">
-        <v>6</v>
+        <v>4.9</v>
       </c>
       <c r="BV5" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="BW5" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>34</v>
+      </c>
+      <c r="BY5" t="n">
         <v>10</v>
       </c>
-      <c r="BX5" t="n">
-        <v>70</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>11</v>
-      </c>
       <c r="BZ5" t="n">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="CA5" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-15 15:46:37</t>
+          <t>2026-07-15 17:58:21</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>US United Soccer League</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1859,24 +1859,24 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Univ Catolica (Ecu)</t>
+          <t>Miami FC</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>LDU</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F6" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="G6" t="n">
         <v>2.96</v>
-      </c>
-      <c r="G6" t="n">
-        <v>3.1</v>
       </c>
       <c r="H6" t="n">
         <v>2.56</v>
@@ -1885,218 +1885,218 @@
         <v>2.68</v>
       </c>
       <c r="J6" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="K6" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="L6" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="M6" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N6" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="O6" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="P6" t="n">
-        <v>1.94</v>
+        <v>2.08</v>
       </c>
       <c r="Q6" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="R6" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="S6" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="T6" t="n">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="U6" t="n">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="V6" t="n">
         <v>1.59</v>
       </c>
       <c r="W6" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="X6" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA6" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AB6" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AD6" t="n">
         <v>12.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AF6" t="n">
         <v>21</v>
       </c>
       <c r="AG6" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH6" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AI6" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AJ6" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AK6" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AL6" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AM6" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AN6" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="AO6" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AP6" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AQ6" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AS6" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AT6" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AU6" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AV6" t="n">
         <v>10.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AX6" t="n">
         <v>17.5</v>
       </c>
       <c r="AY6" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AZ6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA6" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="BB6" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="BC6" t="n">
+        <v>24</v>
+      </c>
+      <c r="BD6" t="n">
         <v>29</v>
       </c>
-      <c r="BD6" t="n">
-        <v>34</v>
-      </c>
       <c r="BE6" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="BF6" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="BG6" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="BI6" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="BJ6" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BN6" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BO6" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BP6" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="BQ6" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>32</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>10</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BW6" t="n">
         <v>8.4</v>
       </c>
-      <c r="BR6" t="n">
-        <v>38</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>21</v>
-      </c>
-      <c r="BW6" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BX6" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BY6" t="n">
+        <v>10</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>24</v>
+      </c>
+      <c r="CA6" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BZ6" t="n">
-        <v>30</v>
-      </c>
-      <c r="CA6" t="n">
-        <v>9</v>
-      </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-15 15:46:37</t>
+          <t>2026-07-15 17:58:21</t>
         </is>
       </c>
     </row>
@@ -2118,239 +2118,239 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Miami FC</t>
+          <t>Lexington SC</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.84</v>
+        <v>1.68</v>
       </c>
       <c r="G7" t="n">
-        <v>2.98</v>
+        <v>1.71</v>
       </c>
       <c r="H7" t="n">
-        <v>2.58</v>
+        <v>5.4</v>
       </c>
       <c r="I7" t="n">
-        <v>2.68</v>
+        <v>5.8</v>
       </c>
       <c r="J7" t="n">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="K7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W7" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="X7" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>160</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>90</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>17</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>17</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>95</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>18</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>36</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>48</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>19</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>44</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>40</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>15</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>24</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>65</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>40</v>
+      </c>
+      <c r="BH7" t="n">
         <v>3.85</v>
       </c>
-      <c r="L7" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N7" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="X7" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>19</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>38</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>38</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>48</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>95</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>25</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>21</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>14</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>16</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>27</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>20</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>29</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>30</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>23</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>29</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>55</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>21</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>3.65</v>
-      </c>
       <c r="BI7" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="BJ7" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK7" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>11</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>24</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>10</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>6</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>44</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>12</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>48</v>
+      </c>
+      <c r="BY7" t="n">
         <v>12.5</v>
       </c>
-      <c r="BN7" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>22</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>5</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>19</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BX7" t="n">
-        <v>32</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BZ7" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="CA7" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-15 15:46:37</t>
+          <t>2026-07-15 17:58:21</t>
         </is>
       </c>
     </row>
@@ -2367,192 +2367,192 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Lexington SC</t>
+          <t>Sporting Club Jacksonvil</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.68</v>
+        <v>4.4</v>
       </c>
       <c r="G8" t="n">
-        <v>1.73</v>
+        <v>4.9</v>
       </c>
       <c r="H8" t="n">
-        <v>5.3</v>
+        <v>1.88</v>
       </c>
       <c r="I8" t="n">
-        <v>5.9</v>
+        <v>1.93</v>
       </c>
       <c r="J8" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="K8" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="L8" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="M8" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="N8" t="n">
-        <v>4.4</v>
+        <v>3.75</v>
       </c>
       <c r="O8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="V8" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="W8" t="n">
         <v>1.27</v>
       </c>
-      <c r="P8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="W8" t="n">
-        <v>2.36</v>
-      </c>
       <c r="X8" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>23</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>42</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>120</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>85</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>16</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>14</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AX8" t="n">
         <v>18</v>
       </c>
-      <c r="Y8" t="n">
-        <v>23</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>55</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>160</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>90</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>85</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>17</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>9</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>95</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>16</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>18</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>34</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>19</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>46</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>9.6</v>
-      </c>
       <c r="AY8" t="n">
-        <v>8.800000000000001</v>
+        <v>15.5</v>
       </c>
       <c r="AZ8" t="n">
         <v>17.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>44</v>
+        <v>6.4</v>
       </c>
       <c r="BB8" t="n">
-        <v>15</v>
+        <v>7.2</v>
       </c>
       <c r="BC8" t="n">
-        <v>15</v>
+        <v>7.2</v>
       </c>
       <c r="BD8" t="n">
-        <v>24</v>
+        <v>7.2</v>
       </c>
       <c r="BE8" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BJ8" t="n">
         <v>10.5</v>
       </c>
-      <c r="BF8" t="n">
-        <v>8</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>44</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>3</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>10</v>
-      </c>
       <c r="BK8" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
@@ -2561,57 +2561,57 @@
         <v>1.01</v>
       </c>
       <c r="BN8" t="n">
-        <v>4.4</v>
+        <v>8</v>
       </c>
       <c r="BO8" t="n">
-        <v>3.4</v>
+        <v>6</v>
       </c>
       <c r="BP8" t="n">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="BQ8" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="BR8" t="n">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="BS8" t="n">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="BT8" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="BU8" t="n">
-        <v>6.6</v>
+        <v>3.5</v>
       </c>
       <c r="BV8" t="n">
-        <v>44</v>
+        <v>13.5</v>
       </c>
       <c r="BW8" t="n">
+        <v>10</v>
+      </c>
+      <c r="BX8" t="n">
         <v>30</v>
       </c>
-      <c r="BX8" t="n">
-        <v>48</v>
-      </c>
       <c r="BY8" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="BZ8" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="CA8" t="n">
-        <v>12.5</v>
+        <v>19</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-15 15:46:37</t>
+          <t>2026-07-15 17:58:21</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>US United Soccer League</t>
+          <t>Bolivian Liga de Futbol Profesional</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2621,251 +2621,251 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Sporting Club Jacksonvil</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4.4</v>
+        <v>1.26</v>
       </c>
       <c r="G9" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="J9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="K9" t="n">
+        <v>8</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N9" t="n">
+        <v>9</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="P9" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W9" t="n">
         <v>4.7</v>
       </c>
-      <c r="H9" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="J9" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="K9" t="n">
-        <v>4</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N9" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2</v>
-      </c>
-      <c r="V9" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.27</v>
-      </c>
       <c r="X9" t="n">
-        <v>16.5</v>
+        <v>50</v>
       </c>
       <c r="Y9" t="n">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="Z9" t="n">
-        <v>14</v>
+        <v>150</v>
       </c>
       <c r="AA9" t="n">
-        <v>23</v>
+        <v>530</v>
       </c>
       <c r="AB9" t="n">
         <v>17.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>10.5</v>
+        <v>19</v>
       </c>
       <c r="AD9" t="n">
-        <v>12.5</v>
+        <v>60</v>
       </c>
       <c r="AE9" t="n">
+        <v>190</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>28</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>120</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>40</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>24</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>22</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>13</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD9" t="n">
         <v>21</v>
       </c>
-      <c r="AF9" t="n">
-        <v>42</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>19</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>40</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>120</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>65</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>70</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>85</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>12</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>10</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AT9" t="n">
+      <c r="BE9" t="n">
+        <v>13</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BG9" t="n">
         <v>13.5</v>
       </c>
-      <c r="AU9" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>9</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>18</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>5</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>12.5</v>
-      </c>
       <c r="BH9" t="n">
-        <v>3.3</v>
+        <v>6</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.64</v>
+        <v>5.3</v>
       </c>
       <c r="BJ9" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BK9" t="n">
-        <v>7.6</v>
+        <v>5.9</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BN9" t="n">
-        <v>8</v>
+        <v>4.6</v>
       </c>
       <c r="BO9" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BQ9" t="n">
         <v>6</v>
       </c>
-      <c r="BP9" t="n">
-        <v>42</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>29</v>
-      </c>
       <c r="BR9" t="n">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="BS9" t="n">
-        <v>36</v>
+        <v>7.2</v>
       </c>
       <c r="BT9" t="n">
-        <v>4.5</v>
+        <v>15.5</v>
       </c>
       <c r="BU9" t="n">
-        <v>3.5</v>
+        <v>6.8</v>
       </c>
       <c r="BV9" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="BW9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>60</v>
+      </c>
+      <c r="BY9" t="n">
         <v>10</v>
       </c>
-      <c r="BX9" t="n">
-        <v>30</v>
-      </c>
-      <c r="BY9" t="n">
-        <v>21</v>
-      </c>
       <c r="BZ9" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="CA9" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-15 15:46:37</t>
+          <t>2026-07-15 17:58:21</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2875,222 +2875,222 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Barcelona (Ecu)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Guayaquil City</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.28</v>
+        <v>1.56</v>
       </c>
       <c r="G10" t="n">
-        <v>1.31</v>
+        <v>1.6</v>
       </c>
       <c r="H10" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="I10" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W10" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="X10" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>65</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>330</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>34</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>150</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>160</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>20</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>240</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>260</v>
+      </c>
+      <c r="AP10" t="n">
         <v>11</v>
       </c>
-      <c r="I10" t="n">
+      <c r="AQ10" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>50</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>14</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>26</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>70</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>25</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>70</v>
+      </c>
+      <c r="BB10" t="n">
         <v>13</v>
       </c>
-      <c r="J10" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K10" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N10" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="P10" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W10" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="X10" t="n">
-        <v>48</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>55</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>120</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>470</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AC10" t="n">
+      <c r="BC10" t="n">
         <v>17</v>
       </c>
-      <c r="AD10" t="n">
-        <v>46</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>160</v>
-      </c>
-      <c r="AF10" t="n">
+      <c r="BD10" t="n">
+        <v>42</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>16</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>10</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>16</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BJ10" t="n">
         <v>12</v>
       </c>
-      <c r="AG10" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>32</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>140</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>32</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>170</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>9</v>
-      </c>
-      <c r="AY10" t="n">
+      <c r="BK10" t="n">
         <v>10</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>22</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>6.8</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BN10" t="n">
-        <v>4.3</v>
+        <v>3.85</v>
       </c>
       <c r="BO10" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="BP10" t="n">
-        <v>7.2</v>
+        <v>10.5</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="BR10" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BT10" t="n">
-        <v>15.5</v>
+        <v>11</v>
       </c>
       <c r="BU10" t="n">
-        <v>8</v>
+        <v>6.6</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
@@ -3102,271 +3102,17 @@
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="CA10" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-15 15:46:37</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Ecuadorian Serie A</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>21:30:00</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Barcelona (Ecu)</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Guayaquil City</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="G11" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="H11" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="I11" t="n">
-        <v>8</v>
-      </c>
-      <c r="J11" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N11" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S11" t="n">
-        <v>4</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="W11" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="X11" t="n">
-        <v>15</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>23</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>80</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>300</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>34</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>170</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>29</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>160</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>15</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>220</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>11</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>290</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>18</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>44</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>6</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>21</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>22</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>13</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>36</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>9</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>12</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>10</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BO11" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BP11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BQ11" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BR11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS11" t="n">
-        <v>11</v>
-      </c>
-      <c r="BT11" t="n">
-        <v>11</v>
-      </c>
-      <c r="BU11" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BV11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW11" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BX11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY11" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BZ11" t="n">
-        <v>30</v>
-      </c>
-      <c r="CA11" t="n">
-        <v>10</v>
-      </c>
-      <c r="CB11" t="inlineStr">
-        <is>
-          <t>2026-07-15 15:46:37</t>
+          <t>2026-07-15 17:58:21</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-15.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB10"/>
+  <dimension ref="A1:CB9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,7 +833,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie B</t>
+          <t>Bolivian Liga de Futbol Profesional</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -843,72 +843,72 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Vinotinto Ecuador</t>
+          <t>Real Potosi</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>El Nacional</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="H2" t="n">
+        <v>340</v>
+      </c>
+      <c r="I2" t="n">
+        <v>570</v>
+      </c>
+      <c r="J2" t="n">
+        <v>60</v>
+      </c>
+      <c r="K2" t="n">
+        <v>75</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="Q2" t="n">
         <v>1.14</v>
       </c>
-      <c r="G2" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="H2" t="n">
-        <v>26</v>
-      </c>
-      <c r="I2" t="n">
-        <v>200</v>
-      </c>
-      <c r="J2" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="K2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
-        <v>2.8</v>
+        <v>2.46</v>
       </c>
       <c r="S2" t="n">
-        <v>1.54</v>
+        <v>1.66</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V2" t="n">
         <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>6.8</v>
+        <v>50</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -935,88 +935,88 @@
         <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.92</v>
+        <v>18</v>
       </c>
       <c r="AH2" t="n">
-        <v>10.5</v>
+        <v>100</v>
       </c>
       <c r="AI2" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="AK2" t="n">
-        <v>3.75</v>
+        <v>12</v>
       </c>
       <c r="AL2" t="n">
+        <v>80</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>650</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ2" t="n">
         <v>15</v>
       </c>
-      <c r="AM2" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>12</v>
-      </c>
       <c r="AR2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AS2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AT2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AU2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AV2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AW2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AX2" t="n">
-        <v>11</v>
+        <v>7.2</v>
       </c>
       <c r="AY2" t="n">
-        <v>2.72</v>
+        <v>15</v>
       </c>
       <c r="AZ2" t="n">
-        <v>8.6</v>
+        <v>60</v>
       </c>
       <c r="BA2" t="n">
-        <v>50</v>
+        <v>140</v>
       </c>
       <c r="BB2" t="n">
-        <v>11</v>
+        <v>4.3</v>
       </c>
       <c r="BC2" t="n">
-        <v>3.35</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BD2" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="BE2" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="BF2" t="n">
-        <v>5.9</v>
+        <v>2.08</v>
       </c>
       <c r="BG2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BH2" t="n">
         <v>0</v>
@@ -1080,14 +1080,14 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-15 17:58:21</t>
+          <t>2026-07-15 20:09:37</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1102,239 +1102,239 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Real Potosi</t>
+          <t>CD Leones del Norte</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.54</v>
+        <v>1.68</v>
       </c>
       <c r="G3" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="H3" t="n">
+        <v>11</v>
+      </c>
+      <c r="I3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="J3" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="R3" t="n">
         <v>1.58</v>
       </c>
-      <c r="H3" t="n">
-        <v>6</v>
-      </c>
-      <c r="I3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="J3" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="K3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N3" t="n">
-        <v>6</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="P3" t="n">
+      <c r="S3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.42</v>
-      </c>
       <c r="T3" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="W3" t="n">
-        <v>2.72</v>
+        <v>2.28</v>
       </c>
       <c r="X3" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="Z3" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AA3" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>200</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>150</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>29</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>300</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>110</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AZ3" t="n">
         <v>12.5</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="BA3" t="n">
+        <v>100</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>23</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>150</v>
+      </c>
+      <c r="BF3" t="n">
         <v>12</v>
       </c>
-      <c r="AD3" t="n">
-        <v>26</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>75</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>30</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>75</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>23</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>26</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>48</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>44</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>10</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>21</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>36</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>55</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>13</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>24</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>44</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>5.2</v>
-      </c>
       <c r="BG3" t="n">
-        <v>50</v>
+        <v>95</v>
       </c>
       <c r="BH3" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BI3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BJ3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BK3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BL3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM3" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BN3" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BO3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BP3" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="BQ3" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BR3" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BS3" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="BT3" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BU3" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="BV3" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="BW3" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="BY3" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BZ3" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="CA3" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-15 17:58:21</t>
+          <t>2026-07-15 20:09:37</t>
         </is>
       </c>
     </row>
@@ -1356,246 +1356,246 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CD Leones del Norte</t>
+          <t>Univ Catolica (Ecu)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>LDU</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.44</v>
+        <v>3.9</v>
       </c>
       <c r="G4" t="n">
-        <v>2.5</v>
+        <v>4.1</v>
       </c>
       <c r="H4" t="n">
-        <v>3.95</v>
+        <v>2.74</v>
       </c>
       <c r="I4" t="n">
-        <v>4.2</v>
+        <v>2.8</v>
       </c>
       <c r="J4" t="n">
-        <v>2.84</v>
+        <v>2.52</v>
       </c>
       <c r="K4" t="n">
-        <v>2.9</v>
+        <v>2.66</v>
       </c>
       <c r="L4" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>1.16</v>
+        <v>1.29</v>
       </c>
       <c r="N4" t="n">
-        <v>2.5</v>
+        <v>1.71</v>
       </c>
       <c r="O4" t="n">
-        <v>1.65</v>
+        <v>2.3</v>
       </c>
       <c r="P4" t="n">
-        <v>1.47</v>
+        <v>1.2</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.05</v>
+        <v>5.7</v>
       </c>
       <c r="R4" t="n">
-        <v>1.17</v>
+        <v>1.04</v>
       </c>
       <c r="S4" t="n">
+        <v>19</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>70</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>30</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>75</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>360</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>160</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>190</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>470</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>450</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>180</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>50</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU4" t="n">
         <v>6.6</v>
       </c>
-      <c r="T4" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="X4" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>27</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>110</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AD4" t="n">
+      <c r="AV4" t="n">
         <v>18.5</v>
       </c>
-      <c r="AE4" t="n">
-        <v>80</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>27</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>130</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>38</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>38</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>80</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>46</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>130</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AR4" t="n">
+      <c r="AW4" t="n">
+        <v>70</v>
+      </c>
+      <c r="AX4" t="n">
         <v>22</v>
       </c>
-      <c r="AS4" t="n">
+      <c r="AY4" t="n">
+        <v>24</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>50</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>12</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>100</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>100</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>12</v>
+      </c>
+      <c r="BE4" t="n">
         <v>12.5</v>
       </c>
-      <c r="AT4" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>16</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>55</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>23</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>38</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>26</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>30</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>50</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>28</v>
-      </c>
       <c r="BF4" t="n">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="BG4" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="BH4" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BK4" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BL4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM4" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="BN4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BO4" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="BP4" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="BQ4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BR4" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="BS4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BT4" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="BU4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BV4" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="BW4" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="BY4" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BZ4" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="CA4" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-15 17:58:21</t>
+          <t>2026-07-15 20:09:37</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>US United Soccer League</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1605,244 +1605,244 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Univ Catolica (Ecu)</t>
+          <t>Miami FC</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>LDU</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.96</v>
+        <v>2.74</v>
       </c>
       <c r="G5" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="I5" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="J5" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="K5" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="L5" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="M5" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="N5" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="O5" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="P5" t="n">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.99</v>
+        <v>1.76</v>
       </c>
       <c r="R5" t="n">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="S5" t="n">
-        <v>3.55</v>
+        <v>2.64</v>
       </c>
       <c r="T5" t="n">
-        <v>1.78</v>
+        <v>1.56</v>
       </c>
       <c r="U5" t="n">
-        <v>2.18</v>
+        <v>2.36</v>
       </c>
       <c r="V5" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="W5" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="X5" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="Y5" t="n">
-        <v>11.5</v>
+        <v>15</v>
       </c>
       <c r="Z5" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>85</v>
+      </c>
+      <c r="AB5" t="n">
         <v>17.5</v>
       </c>
-      <c r="AA5" t="n">
-        <v>40</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AC5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AD5" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AE5" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AF5" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="AG5" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AI5" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>95</v>
+      </c>
+      <c r="AK5" t="n">
         <v>42</v>
       </c>
-      <c r="AJ5" t="n">
-        <v>50</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>34</v>
-      </c>
       <c r="AL5" t="n">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="AM5" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AO5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AP5" t="n">
         <v>12.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>15.5</v>
+        <v>11</v>
       </c>
       <c r="AS5" t="n">
-        <v>32</v>
+        <v>4.2</v>
       </c>
       <c r="AT5" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AU5" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV5" t="n">
         <v>10.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>25</v>
+        <v>2.9</v>
       </c>
       <c r="AX5" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="AY5" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AZ5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BG5" t="n">
         <v>15.5</v>
       </c>
-      <c r="BA5" t="n">
-        <v>34</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>44</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>28</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>36</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>40</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>26</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>20</v>
-      </c>
       <c r="BH5" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="BJ5" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>5.8</v>
+        <v>7.6</v>
       </c>
       <c r="BL5" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="BM5" t="n">
-        <v>12.5</v>
+        <v>8.6</v>
       </c>
       <c r="BN5" t="n">
         <v>6.2</v>
       </c>
       <c r="BO5" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BP5" t="n">
         <v>24</v>
       </c>
       <c r="BQ5" t="n">
-        <v>8.800000000000001</v>
+        <v>19.5</v>
       </c>
       <c r="BR5" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BS5" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="BT5" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BU5" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BV5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BW5" t="n">
-        <v>8.199999999999999</v>
+        <v>16.5</v>
       </c>
       <c r="BX5" t="n">
         <v>34</v>
       </c>
       <c r="BY5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="BZ5" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="CA5" t="n">
-        <v>9.4</v>
+        <v>20</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-15 17:58:21</t>
+          <t>2026-07-15 20:09:37</t>
         </is>
       </c>
     </row>
@@ -1864,239 +1864,239 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Miami FC</t>
+          <t>Lexington SC</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.82</v>
+        <v>1.56</v>
       </c>
       <c r="G6" t="n">
-        <v>2.96</v>
+        <v>1.7</v>
       </c>
       <c r="H6" t="n">
-        <v>2.56</v>
+        <v>5.5</v>
       </c>
       <c r="I6" t="n">
-        <v>2.68</v>
+        <v>7</v>
       </c>
       <c r="J6" t="n">
-        <v>3.55</v>
+        <v>4.3</v>
       </c>
       <c r="K6" t="n">
-        <v>3.75</v>
+        <v>5.4</v>
       </c>
       <c r="L6" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="M6" t="n">
         <v>1.06</v>
       </c>
       <c r="N6" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="O6" t="n">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="P6" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.86</v>
+        <v>1.67</v>
       </c>
       <c r="R6" t="n">
         <v>1.42</v>
       </c>
       <c r="S6" t="n">
-        <v>3.2</v>
+        <v>2.68</v>
       </c>
       <c r="T6" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="U6" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="V6" t="n">
-        <v>1.59</v>
+        <v>1.12</v>
       </c>
       <c r="W6" t="n">
-        <v>1.51</v>
+        <v>2.42</v>
       </c>
       <c r="X6" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>42</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>990</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF6" t="n">
         <v>16.5</v>
       </c>
-      <c r="Y6" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>19</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>38</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>21</v>
-      </c>
       <c r="AG6" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>16.5</v>
+        <v>990</v>
       </c>
       <c r="AI6" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AK6" t="n">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="AL6" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>24</v>
+        <v>11.5</v>
       </c>
       <c r="AO6" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AQ6" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BC6" t="n">
         <v>10.5</v>
       </c>
-      <c r="AR6" t="n">
-        <v>16</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>27</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>21</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>29</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>32</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>24</v>
-      </c>
       <c r="BD6" t="n">
-        <v>29</v>
+        <v>2.18</v>
       </c>
       <c r="BE6" t="n">
-        <v>55</v>
+        <v>3.35</v>
       </c>
       <c r="BF6" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="BG6" t="n">
-        <v>17.5</v>
+        <v>4.5</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.25</v>
+        <v>1.27</v>
       </c>
       <c r="BJ6" t="n">
-        <v>9.199999999999999</v>
+        <v>970</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.8</v>
+        <v>1.84</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>13</v>
+        <v>1.33</v>
       </c>
       <c r="BN6" t="n">
-        <v>6</v>
+        <v>590</v>
       </c>
       <c r="BO6" t="n">
-        <v>5.3</v>
+        <v>1.33</v>
       </c>
       <c r="BP6" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>8.6</v>
+        <v>1.84</v>
       </c>
       <c r="BR6" t="n">
-        <v>32</v>
+        <v>860</v>
       </c>
       <c r="BS6" t="n">
-        <v>10</v>
+        <v>1.33</v>
       </c>
       <c r="BT6" t="n">
-        <v>5.8</v>
+        <v>690</v>
       </c>
       <c r="BU6" t="n">
-        <v>5.1</v>
+        <v>1.84</v>
       </c>
       <c r="BV6" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>8.4</v>
+        <v>1.33</v>
       </c>
       <c r="BX6" t="n">
-        <v>32</v>
+        <v>870</v>
       </c>
       <c r="BY6" t="n">
-        <v>10</v>
+        <v>1.33</v>
       </c>
       <c r="BZ6" t="n">
-        <v>24</v>
+        <v>960</v>
       </c>
       <c r="CA6" t="n">
-        <v>9.199999999999999</v>
+        <v>1.33</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-15 17:58:21</t>
+          <t>2026-07-15 20:09:37</t>
         </is>
       </c>
     </row>
@@ -2113,251 +2113,251 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Lexington SC</t>
+          <t>Sporting Club Jacksonvil</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.68</v>
+        <v>4.3</v>
       </c>
       <c r="G7" t="n">
-        <v>1.71</v>
+        <v>4.4</v>
       </c>
       <c r="H7" t="n">
-        <v>5.4</v>
+        <v>1.94</v>
       </c>
       <c r="I7" t="n">
-        <v>5.8</v>
+        <v>1.99</v>
       </c>
       <c r="J7" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="K7" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="L7" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="M7" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="N7" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="O7" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="P7" t="n">
-        <v>2.24</v>
+        <v>1.95</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="R7" t="n">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="S7" t="n">
-        <v>2.92</v>
+        <v>3.6</v>
       </c>
       <c r="T7" t="n">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="U7" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="V7" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="W7" t="n">
-        <v>2.4</v>
+        <v>1.29</v>
       </c>
       <c r="X7" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="Y7" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA7" t="n">
         <v>23</v>
       </c>
-      <c r="Z7" t="n">
-        <v>55</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>160</v>
-      </c>
       <c r="AB7" t="n">
-        <v>9.800000000000001</v>
+        <v>16</v>
       </c>
       <c r="AC7" t="n">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>22</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AE7" t="n">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="AF7" t="n">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="AG7" t="n">
-        <v>9.199999999999999</v>
+        <v>18</v>
       </c>
       <c r="AH7" t="n">
         <v>19.5</v>
       </c>
       <c r="AI7" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>180</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>60</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>70</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>30</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>32</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>26</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>28</v>
+      </c>
+      <c r="BE7" t="n">
         <v>85</v>
       </c>
-      <c r="AJ7" t="n">
-        <v>17</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>17</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>95</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>18</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>36</v>
-      </c>
-      <c r="AS7" t="n">
+      <c r="BF7" t="n">
+        <v>55</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>12</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>10</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>130</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>38</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>12</v>
+      </c>
+      <c r="BR7" t="n">
         <v>48</v>
       </c>
-      <c r="AT7" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>19</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>44</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>40</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>15</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>15</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>24</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>65</v>
-      </c>
-      <c r="BF7" t="n">
+      <c r="BS7" t="n">
+        <v>13</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>4</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>14</v>
+      </c>
+      <c r="BW7" t="n">
         <v>7.8</v>
       </c>
-      <c r="BG7" t="n">
-        <v>40</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BP7" t="n">
+      <c r="BX7" t="n">
+        <v>29</v>
+      </c>
+      <c r="BY7" t="n">
         <v>11</v>
       </c>
-      <c r="BQ7" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>24</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>10</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>6</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>44</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>12</v>
-      </c>
-      <c r="BX7" t="n">
-        <v>48</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>12.5</v>
-      </c>
       <c r="BZ7" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="CA7" t="n">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-15 17:58:21</t>
+          <t>2026-07-15 20:09:37</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>US United Soccer League</t>
+          <t>Bolivian Liga de Futbol Profesional</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2367,251 +2367,251 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Sporting Club Jacksonvil</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.4</v>
+        <v>1.22</v>
       </c>
       <c r="G8" t="n">
-        <v>4.9</v>
+        <v>1.24</v>
       </c>
       <c r="H8" t="n">
-        <v>1.88</v>
+        <v>13</v>
       </c>
       <c r="I8" t="n">
-        <v>1.93</v>
+        <v>16</v>
       </c>
       <c r="J8" t="n">
-        <v>3.75</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>3.9</v>
+        <v>9</v>
       </c>
       <c r="L8" t="n">
-        <v>1.43</v>
+        <v>1.18</v>
       </c>
       <c r="M8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N8" t="n">
+        <v>10</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="P8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V8" t="n">
         <v>1.07</v>
       </c>
-      <c r="N8" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="V8" t="n">
-        <v>2.06</v>
-      </c>
       <c r="W8" t="n">
-        <v>1.27</v>
+        <v>4.8</v>
       </c>
       <c r="X8" t="n">
-        <v>16.5</v>
+        <v>120</v>
       </c>
       <c r="Y8" t="n">
-        <v>9.800000000000001</v>
+        <v>85</v>
       </c>
       <c r="Z8" t="n">
+        <v>160</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>28</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>22</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>65</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>180</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG8" t="n">
         <v>13.5</v>
       </c>
-      <c r="AA8" t="n">
-        <v>23</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>21</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>42</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>19</v>
-      </c>
       <c r="AH8" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="AI8" t="n">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="AJ8" t="n">
-        <v>120</v>
+        <v>12</v>
       </c>
       <c r="AK8" t="n">
-        <v>65</v>
+        <v>13</v>
       </c>
       <c r="AL8" t="n">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="AM8" t="n">
         <v>140</v>
       </c>
       <c r="AN8" t="n">
-        <v>85</v>
+        <v>2.8</v>
       </c>
       <c r="AO8" t="n">
-        <v>16</v>
+        <v>150</v>
       </c>
       <c r="AP8" t="n">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="AQ8" t="n">
-        <v>7.8</v>
+        <v>11</v>
       </c>
       <c r="AR8" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AS8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>18</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>40</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ8" t="n">
         <v>18.5</v>
       </c>
-      <c r="AT8" t="n">
-        <v>14</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>18</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>17.5</v>
-      </c>
       <c r="BA8" t="n">
-        <v>6.4</v>
+        <v>11.5</v>
       </c>
       <c r="BB8" t="n">
-        <v>7.2</v>
+        <v>10.5</v>
       </c>
       <c r="BC8" t="n">
-        <v>7.2</v>
+        <v>11.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>7.2</v>
+        <v>18.5</v>
       </c>
       <c r="BE8" t="n">
-        <v>7.2</v>
+        <v>75</v>
       </c>
       <c r="BF8" t="n">
-        <v>7.2</v>
+        <v>2.48</v>
       </c>
       <c r="BG8" t="n">
         <v>11.5</v>
       </c>
       <c r="BH8" t="n">
-        <v>3.35</v>
+        <v>6.8</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.66</v>
+        <v>5.8</v>
       </c>
       <c r="BJ8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>90</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>4</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>17</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>7</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW8" t="n">
         <v>10.5</v>
       </c>
-      <c r="BK8" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>8</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>6</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>42</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>29</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>55</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>36</v>
-      </c>
-      <c r="BT8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BU8" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BV8" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BW8" t="n">
+      <c r="BX8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY8" t="n">
         <v>10</v>
       </c>
-      <c r="BX8" t="n">
-        <v>30</v>
-      </c>
-      <c r="BY8" t="n">
-        <v>21</v>
-      </c>
       <c r="BZ8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="CA8" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-15 17:58:21</t>
+          <t>2026-07-15 20:09:37</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2621,498 +2621,244 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Barcelona (Ecu)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Guayaquil City</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.26</v>
+        <v>1.53</v>
       </c>
       <c r="G9" t="n">
-        <v>1.27</v>
+        <v>1.56</v>
       </c>
       <c r="H9" t="n">
+        <v>8</v>
+      </c>
+      <c r="I9" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="J9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N9" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W9" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="X9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>75</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>350</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>980</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>400</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>34</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>330</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>970</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>240</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>260</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>20</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>25</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>25</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BB9" t="n">
         <v>12</v>
       </c>
-      <c r="I9" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="J9" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="K9" t="n">
-        <v>8</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N9" t="n">
-        <v>9</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="P9" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="R9" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="X9" t="n">
-        <v>50</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>80</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>150</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>530</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>19</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>60</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>190</v>
-      </c>
-      <c r="AF9" t="n">
+      <c r="BC9" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>38</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>130</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="BJ9" t="n">
         <v>12</v>
       </c>
-      <c r="AG9" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>27</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>120</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>12</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>13</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>28</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>120</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>40</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>24</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AU9" t="n">
+      <c r="BK9" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>160</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>11</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>32</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>15</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY9" t="n">
         <v>15.5</v>
       </c>
-      <c r="AV9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>14</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>22</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>13</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>10</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>11</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>21</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>13</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>6</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM9" t="n">
+      <c r="BZ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA9" t="n">
         <v>10.5</v>
       </c>
-      <c r="BN9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>6</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>18</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BV9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BX9" t="n">
-        <v>60</v>
-      </c>
-      <c r="BY9" t="n">
-        <v>10</v>
-      </c>
-      <c r="BZ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA9" t="n">
-        <v>0</v>
-      </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-15 17:58:21</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Ecuadorian Serie A</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>21:30:00</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Barcelona (Ecu)</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Guayaquil City</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="G10" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="H10" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="I10" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="J10" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N10" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S10" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="W10" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="X10" t="n">
-        <v>13</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>22</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>65</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>330</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>34</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>150</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>9</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>29</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>160</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>20</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>240</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>260</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>50</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>14</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>6</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>26</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>70</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>25</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>70</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>13</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>17</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>42</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>16</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>10</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>16</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>12</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>10</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>16</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>11</v>
-      </c>
-      <c r="BT10" t="n">
-        <v>11</v>
-      </c>
-      <c r="BU10" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BV10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW10" t="n">
-        <v>14</v>
-      </c>
-      <c r="BX10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY10" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BZ10" t="n">
-        <v>30</v>
-      </c>
-      <c r="CA10" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="CB10" t="inlineStr">
-        <is>
-          <t>2026-07-15 17:58:21</t>
+          <t>2026-07-15 20:09:37</t>
         </is>
       </c>
     </row>
